--- a/docs/handouts/chapter_1_4_handout_key.xlsx
+++ b/docs/handouts/chapter_1_4_handout_key.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DBC8CB2-6C7D-472C-8FC7-110453B7423D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A4EEFC-9D73-4E88-9FF3-34808BE5D8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
+    <workbookView xWindow="17745" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Key" sheetId="1" r:id="rId1"/>
+    <sheet name="Key" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
     <author>Tyson Brost</author>
   </authors>
   <commentList>
-    <comment ref="N143" authorId="0" shapeId="0" xr:uid="{7750667E-3700-42EC-9F0F-77593DC7D137}">
+    <comment ref="N71" authorId="0" shapeId="0" xr:uid="{7AB34930-2485-49E2-A678-E9A1E1596D84}">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A145" authorId="0" shapeId="0" xr:uid="{F2AF67EF-FA12-448D-9E94-0BE47A8552A4}">
+    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{CF60AC78-5442-4236-AECE-C0C7ACA4D6BF}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A146" authorId="0" shapeId="0" xr:uid="{189969D4-BB5C-4B8B-838C-0DE12626EB8B}">
+    <comment ref="A75" authorId="0" shapeId="0" xr:uid="{A19E4124-49FE-4496-96B5-9863E9772391}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="84">
   <si>
     <t>Month</t>
   </si>
@@ -303,9 +303,6 @@
     <t>2021 Dec</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Year</t>
   </si>
   <si>
@@ -343,13 +340,29 @@
   </si>
   <si>
     <t>Dec</t>
-  </si>
-  <si>
-    <t>Mean</t>
   </si>
   <si>
     <t>Overall
 Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Table 1: Computation of the 
+Centered Moving Average,      , and the Estimated Monthly Additive Effect,</t>
+  </si>
+  <si>
+    <t>Table 2: Computation of</t>
+  </si>
+  <si>
+    <t>Mean,</t>
+  </si>
+  <si>
+    <t>Table 3: Computation of        the Random Component and the Seasonally Adjusted Time Series</t>
   </si>
 </sst>
 </file>
@@ -359,7 +372,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,8 +394,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,8 +422,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -404,28 +443,278 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,19 +738,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>219234</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>251333</xdr:rowOff>
+      <xdr:colOff>295434</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>205613</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="2" name="TextBox 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7B35190-F665-26A2-FF8D-26FE16E40FA1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CC8CAD1-69B1-40D8-A713-188C4E07C8EC}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -469,7 +758,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="828834" y="251333"/>
+              <a:off x="1130459" y="15680563"/>
               <a:ext cx="196079" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -500,10 +789,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -537,13 +823,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="2" name="TextBox 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7B35190-F665-26A2-FF8D-26FE16E40FA1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CC8CAD1-69B1-40D8-A713-188C4E07C8EC}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -551,7 +837,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="828834" y="251333"/>
+              <a:off x="1130459" y="15680563"/>
               <a:ext cx="196079" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -579,6 +865,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -596,19 +883,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>211614</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>152273</xdr:rowOff>
+      <xdr:colOff>295434</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>137033</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187167" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="3" name="TextBox 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35AFF05F-2F87-8455-2D4E-1EB91A0BF9E3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9AD31EA-CC15-4A69-960C-6754060CB6BF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -616,7 +903,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1430814" y="152273"/>
+              <a:off x="1968659" y="15618333"/>
               <a:ext cx="187167" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -647,15 +934,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -677,13 +961,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="3" name="TextBox 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35AFF05F-2F87-8455-2D4E-1EB91A0BF9E3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9AD31EA-CC15-4A69-960C-6754060CB6BF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -691,7 +975,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1430814" y="152273"/>
+              <a:off x="1968659" y="15618333"/>
               <a:ext cx="187167" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -719,6 +1003,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -736,19 +1021,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>234474</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:colOff>341154</xdr:colOff>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>137033</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="4" name="TextBox 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E15B6B16-FC40-4BBF-8BCE-81636636916B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C504EC31-51CA-460B-8166-D7F15238DE95}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -756,7 +1041,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2063274" y="137033"/>
+              <a:off x="2865279" y="15618333"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -787,15 +1072,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -817,13 +1099,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="4" name="TextBox 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E15B6B16-FC40-4BBF-8BCE-81636636916B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C504EC31-51CA-460B-8166-D7F15238DE95}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -831,7 +1113,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2063274" y="137033"/>
+              <a:off x="2865279" y="15618333"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -859,6 +1141,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -876,19 +1159,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:colOff>320040</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="5" name="TextBox 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B250CA9E-0452-5FF7-2934-724E2D39D9F1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EFC7B1D-C8AE-4D78-A865-782604968F0C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -896,7 +1179,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2697480" y="118110"/>
+              <a:off x="3622040" y="15585440"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -927,15 +1210,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̅"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -957,13 +1237,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="5" name="TextBox 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B250CA9E-0452-5FF7-2934-724E2D39D9F1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EFC7B1D-C8AE-4D78-A865-782604968F0C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -971,7 +1251,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2697480" y="118110"/>
+              <a:off x="3622040" y="15585440"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -999,6 +1279,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1016,19 +1297,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>539274</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>251333</xdr:rowOff>
+      <xdr:colOff>569754</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>205613</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="6" name="TextBox 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3F05BD6-4581-4EE8-AB2E-48B2041474E6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A32157E4-DCFB-4DDE-B6A9-DBE37E97D611}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1036,7 +1317,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4196874" y="251333"/>
+              <a:off x="5437029" y="15680563"/>
               <a:ext cx="196079" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1067,10 +1348,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1104,13 +1382,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="6" name="TextBox 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3F05BD6-4581-4EE8-AB2E-48B2041474E6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A32157E4-DCFB-4DDE-B6A9-DBE37E97D611}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1118,7 +1396,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4196874" y="251333"/>
+              <a:off x="5437029" y="15680563"/>
               <a:ext cx="196079" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1146,6 +1424,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1164,16 +1443,16 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
+        <xdr:cNvPr id="7" name="TextBox 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D271CC1F-CB3F-E299-4DDF-19048A80E7DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4469D1B-4F9D-48F9-A217-21819DDE6DCA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1181,7 +1460,483 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="228600" y="14382750"/>
+          <a:off x="228600" y="22295485"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>318294</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>129413</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="196079" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="TextBox 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A3CE73D-B773-4E5F-9EB9-255DA17F8DF9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1153319" y="707263"/>
+              <a:ext cx="196079" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="TextBox 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A3CE73D-B773-4E5F-9EB9-255DA17F8DF9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1153319" y="707263"/>
+              <a:ext cx="196079" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥_𝑡</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>310674</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>83693</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="187167" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9" name="TextBox 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{264B5094-3F97-4063-9215-535779C2E08B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1990249" y="667893"/>
+              <a:ext cx="187167" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑚</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:acc>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9" name="TextBox 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{264B5094-3F97-4063-9215-535779C2E08B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1990249" y="667893"/>
+              <a:ext cx="187167" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑚 ̂</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>287814</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>83693</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="120161" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="TextBox 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D2F4E2-A2FE-4804-9411-C3150B626684}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2811939" y="667893"/>
+              <a:ext cx="120161" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑠</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:acc>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="TextBox 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D2F4E2-A2FE-4804-9411-C3150B626684}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2811939" y="667893"/>
+              <a:ext cx="120161" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑠 ̂</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDE906BF-6FB8-4A61-8A34-58A34E5C55C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="14389735"/>
           <a:ext cx="65" cy="172227"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1218,19 +1973,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:colOff>387985</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>153670</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45C58AF0-ECDC-98DE-0057-6C6A2334551C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C958AE0A-781D-4922-88BE-6EDE1C063529}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1238,7 +1993,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="14443710"/>
+              <a:off x="391160" y="13850620"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1269,10 +2024,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1286,7 +2038,7 @@
                           <m:accPr>
                             <m:chr m:val="̅"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -1318,13 +2070,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45C58AF0-ECDC-98DE-0057-6C6A2334551C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C958AE0A-781D-4922-88BE-6EDE1C063529}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1332,7 +2084,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="14443710"/>
+              <a:off x="391160" y="13850620"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1360,6 +2112,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1377,19 +2130,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>144</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="231923"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA9A77E-BE76-60D8-84F5-14D817DE041D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB7423EF-25AF-44F2-8D84-4CB37620AA58}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1397,7 +2150,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="403860" y="14237970"/>
+              <a:off x="381000" y="14151610"/>
               <a:ext cx="180819" cy="231923"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1428,10 +2181,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̅"/>
@@ -1455,7 +2205,7 @@
                               <m:accPr>
                                 <m:chr m:val="̂"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1400" i="1">
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
@@ -1489,13 +2239,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA9A77E-BE76-60D8-84F5-14D817DE041D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB7423EF-25AF-44F2-8D84-4CB37620AA58}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1503,7 +2253,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="403860" y="14237970"/>
+              <a:off x="381000" y="14151610"/>
               <a:ext cx="180819" cy="231923"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1531,6 +2281,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1554,19 +2305,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>142</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>152399</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="180819" cy="250903"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="379575" cy="250903"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B03E3A5F-D875-BA58-83F1-82DDE139B3BB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E0BD830-56EE-40D2-AF44-7F222E7FCEE3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1574,8 +2325,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9928860" y="13925550"/>
-              <a:ext cx="180819" cy="250903"/>
+              <a:off x="10001249" y="13916025"/>
+              <a:ext cx="379575" cy="250903"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1597,82 +2348,80 @@
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr/>
               <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̿"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:acc>
-                              <m:accPr>
-                                <m:chr m:val="̂"/>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1400" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:accPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑠</m:t>
-                                </m:r>
-                              </m:e>
-                            </m:acc>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑡</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
-                  </m:oMath>
-                </m:oMathPara>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:acc>
+                    <m:accPr>
+                      <m:chr m:val="̿"/>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:accPr>
+                    <m:e>
+                      <m:sSub>
+                        <m:sSubPr>
+                          <m:ctrlPr>
+                            <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                          </m:ctrlPr>
+                        </m:sSubPr>
+                        <m:e>
+                          <m:acc>
+                            <m:accPr>
+                              <m:chr m:val="̂"/>
+                              <m:ctrlPr>
+                                <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                </a:rPr>
+                              </m:ctrlPr>
+                            </m:accPr>
+                            <m:e>
+                              <m:r>
+                                <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                </a:rPr>
+                                <m:t>𝑠</m:t>
+                              </m:r>
+                            </m:e>
+                          </m:acc>
+                        </m:e>
+                        <m:sub>
+                          <m:r>
+                            <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>𝑡</m:t>
+                          </m:r>
+                        </m:sub>
+                      </m:sSub>
+                    </m:e>
+                  </m:acc>
+                </m:oMath>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1400"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400"/>
+                <a:t>=</a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B03E3A5F-D875-BA58-83F1-82DDE139B3BB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E0BD830-56EE-40D2-AF44-7F222E7FCEE3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1680,8 +2429,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9928860" y="13925550"/>
-              <a:ext cx="180819" cy="250903"/>
+              <a:off x="10001249" y="13916025"/>
+              <a:ext cx="379575" cy="250903"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1703,11 +2452,12 @@
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1720,7 +2470,10 @@
                 </a:rPr>
                 <a:t>𝑠 ̂_𝑡 ) ̿</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="1400"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400"/>
+                <a:t>=</a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1730,20 +2483,20 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>272574</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>114173</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>202565</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>77470</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="196079" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="320040" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="14" name="TextBox 13">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9857193F-8A17-4ACF-89AC-11A9A9E02C33}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA6F6110-F50F-4612-9089-D374F44DE0FF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1751,8 +2504,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="882174" y="114173"/>
-              <a:ext cx="196079" cy="221214"/>
+              <a:off x="1875790" y="15003145"/>
+              <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1774,7 +2527,7 @@
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
@@ -1782,10 +2535,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1799,7 +2549,7 @@
                           <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>𝑥</m:t>
+                          <m:t>𝑧</m:t>
                         </m:r>
                       </m:e>
                       <m:sub>
@@ -1819,13 +2569,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="14" name="TextBox 13">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9857193F-8A17-4ACF-89AC-11A9A9E02C33}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA6F6110-F50F-4612-9089-D374F44DE0FF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1833,8 +2583,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="882174" y="114173"/>
-              <a:ext cx="196079" cy="221214"/>
+              <a:off x="1875790" y="15003145"/>
+              <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1856,7 +2606,7 @@
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
@@ -1866,7 +2616,7 @@
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑥_𝑡</a:t>
+                <a:t>𝑧_𝑡</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
@@ -1878,20 +2628,20 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>333534</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>91313</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="187167" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="70147" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="TextBox 14">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A752D0DC-A104-4C1F-B033-043C949B118A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8F5DE10-A82B-4B09-AF60-27AF6DB36F4B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1899,8 +2649,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1712754" y="91313"/>
-              <a:ext cx="187167" cy="221214"/>
+              <a:off x="240665" y="20299045"/>
+              <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1930,15 +2680,140 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>⋮</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="TextBox 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8F5DE10-A82B-4B09-AF60-27AF6DB36F4B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="240665" y="20299045"/>
+              <a:ext cx="70147" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>⋮</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104934</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>197993</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="187167" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="TextBox 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E72C8FE-DB1B-4E1A-A047-91B9C677ADF4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1778159" y="201168"/>
+              <a:ext cx="187167" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1960,13 +2835,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="TextBox 14">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A752D0DC-A104-4C1F-B033-043C949B118A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E72C8FE-DB1B-4E1A-A047-91B9C677ADF4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1974,7 +2849,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1712754" y="91313"/>
+              <a:off x="1778159" y="201168"/>
               <a:ext cx="187167" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2019,20 +2894,20 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>325914</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>714534</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76073</xdr:rowOff>
+      <xdr:rowOff>388493</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="TextBox 15">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2705C83-4DE0-4129-BB4E-F81B34577A7B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB8BE1E2-3411-45BB-BC1E-728BD7C231AD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2040,7 +2915,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2543334" y="76073"/>
+              <a:off x="2387759" y="391668"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2071,15 +2946,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2101,13 +2973,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="TextBox 15">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2705C83-4DE0-4129-BB4E-F81B34577A7B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB8BE1E2-3411-45BB-BC1E-728BD7C231AD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2115,7 +2987,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2543334" y="76073"/>
+              <a:off x="2387759" y="391668"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2158,11 +3030,164 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="320040" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="TextBox 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC3DD181-E42E-4A0D-AEAE-9C6E42A5C33F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5781675" y="12468225"/>
+              <a:ext cx="320040" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑠</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="TextBox 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC3DD181-E42E-4A0D-AEAE-9C6E42A5C33F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5781675" y="12468225"/>
+              <a:ext cx="320040" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑠 ̅_𝑡</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2481,3064 +3506,3154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BEFD67-1FFC-4CEC-A668-9A144E8F85C9}">
-  <dimension ref="A1:N146"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F625CA8D-140F-4656-AD4A-A92BAB597FB2}">
+  <dimension ref="A1:N139"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.88671875" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.90625" customWidth="1"/>
+    <col min="14" max="14" width="9.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="10">
         <v>3034</v>
       </c>
-      <c r="C2" t="str">
-        <f>IFERROR(((0.5 *#REF!)+#REF!+#REF!+#REF!+#REF!+B1+B2+B3+B4+B5+B6+B7+(0.5*B8))/12, "NA")</f>
+      <c r="C3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10">
+        <v>2748</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="10">
+        <v>3164</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="10">
+        <v>3238</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="10">
+        <v>3416</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="10">
+        <v>3492</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="10">
+        <v>3730</v>
+      </c>
+      <c r="C9" s="12">
+        <f>(0.5*B3+SUM(B4:B14)+0.5*B15)/12</f>
+        <v>3351.5833333333335</v>
+      </c>
+      <c r="D9" s="13">
+        <v>378.41666666666652</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10">
+        <v>3409</v>
+      </c>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:C56" si="0">(0.5*B4+SUM(B5:B15)+0.5*B16)/12</f>
+        <v>3350</v>
+      </c>
+      <c r="D10" s="14">
+        <f>IFERROR(B10-C10, "NA")</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="10">
+        <v>3572</v>
+      </c>
+      <c r="C11" s="12">
+        <f t="shared" si="0"/>
+        <v>3343.2083333333335</v>
+      </c>
+      <c r="D11" s="14">
+        <f t="shared" ref="D11:D62" si="1">IFERROR(B11-C11, "NA")</f>
+        <v>228.79166666666652</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="10">
+        <v>3629</v>
+      </c>
+      <c r="C12" s="12">
+        <f t="shared" si="0"/>
+        <v>3326.2083333333335</v>
+      </c>
+      <c r="D12" s="14">
+        <f t="shared" si="1"/>
+        <v>302.79166666666652</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="10">
+        <v>3408</v>
+      </c>
+      <c r="C13" s="12">
+        <f t="shared" si="0"/>
+        <v>3316.5416666666665</v>
+      </c>
+      <c r="D13" s="14">
+        <f t="shared" si="1"/>
+        <v>91.458333333333485</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="10">
+        <v>3391</v>
+      </c>
+      <c r="C14" s="12">
+        <f t="shared" si="0"/>
+        <v>3318.5833333333335</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="1"/>
+        <v>72.416666666666515</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="10">
+        <v>3010</v>
+      </c>
+      <c r="C15" s="12">
+        <f t="shared" si="0"/>
+        <v>3312.0833333333335</v>
+      </c>
+      <c r="D15" s="14">
+        <f t="shared" si="1"/>
+        <v>-302.08333333333348</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="10">
+        <v>2734</v>
+      </c>
+      <c r="C16" s="12">
+        <f t="shared" si="0"/>
+        <v>3308.0416666666665</v>
+      </c>
+      <c r="D16" s="14">
+        <f t="shared" si="1"/>
+        <v>-574.04166666666652</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="10">
+        <v>3015</v>
+      </c>
+      <c r="C17" s="12">
+        <f t="shared" si="0"/>
+        <v>3311.7083333333335</v>
+      </c>
+      <c r="D17" s="14">
+        <f t="shared" si="1"/>
+        <v>-296.70833333333348</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2979</v>
+      </c>
+      <c r="C18" s="12">
+        <f t="shared" si="0"/>
+        <v>3313.1666666666665</v>
+      </c>
+      <c r="D18" s="14">
+        <f t="shared" si="1"/>
+        <v>-334.16666666666652</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="10">
+        <v>3443</v>
+      </c>
+      <c r="C19" s="12">
+        <f t="shared" si="0"/>
+        <v>3307.75</v>
+      </c>
+      <c r="D19" s="14">
+        <f t="shared" si="1"/>
+        <v>135.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="10">
+        <v>3514</v>
+      </c>
+      <c r="C20" s="12">
+        <f t="shared" si="0"/>
+        <v>3292.4166666666665</v>
+      </c>
+      <c r="D20" s="14">
+        <f t="shared" si="1"/>
+        <v>221.58333333333348</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="10">
+        <v>3552</v>
+      </c>
+      <c r="C21" s="12">
+        <f t="shared" si="0"/>
+        <v>3281.0833333333335</v>
+      </c>
+      <c r="D21" s="14">
+        <f t="shared" si="1"/>
+        <v>270.91666666666652</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="10">
+        <v>3490</v>
+      </c>
+      <c r="C22" s="12">
+        <f t="shared" si="0"/>
+        <v>3270.2083333333335</v>
+      </c>
+      <c r="D22" s="14">
+        <f t="shared" si="1"/>
+        <v>219.79166666666652</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="10">
+        <v>3579</v>
+      </c>
+      <c r="C23" s="12">
+        <f t="shared" si="0"/>
+        <v>3259.4583333333335</v>
+      </c>
+      <c r="D23" s="14">
+        <f t="shared" si="1"/>
+        <v>319.54166666666652</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="10">
+        <v>3657</v>
+      </c>
+      <c r="C24" s="12">
+        <f t="shared" si="0"/>
+        <v>3261.1666666666665</v>
+      </c>
+      <c r="D24" s="14">
+        <f t="shared" si="1"/>
+        <v>395.83333333333348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="10">
+        <v>3250</v>
+      </c>
+      <c r="C25" s="12">
+        <f t="shared" si="0"/>
+        <v>3264.25</v>
+      </c>
+      <c r="D25" s="14">
+        <f t="shared" si="1"/>
+        <v>-14.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="10">
+        <v>3181</v>
+      </c>
+      <c r="C26" s="12">
+        <f t="shared" si="0"/>
+        <v>3260.4583333333335</v>
+      </c>
+      <c r="D26" s="14">
+        <f t="shared" si="1"/>
+        <v>-79.458333333333485</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="10">
+        <v>2948</v>
+      </c>
+      <c r="C27" s="12">
+        <f t="shared" si="0"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D27" s="14">
+        <f t="shared" si="1"/>
+        <v>-308.70833333333348</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="10">
+        <v>2535</v>
+      </c>
+      <c r="C28" s="12">
+        <f t="shared" si="0"/>
+        <v>3262.125</v>
+      </c>
+      <c r="D28" s="14">
+        <f t="shared" si="1"/>
+        <v>-727.125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="10">
+        <v>2956</v>
+      </c>
+      <c r="C29" s="12">
+        <f t="shared" si="0"/>
+        <v>3267.0833333333335</v>
+      </c>
+      <c r="D29" s="14">
+        <f t="shared" si="1"/>
+        <v>-311.08333333333348</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="10">
+        <v>3079</v>
+      </c>
+      <c r="C30" s="12">
+        <f t="shared" si="0"/>
+        <v>3259.2916666666665</v>
+      </c>
+      <c r="D30" s="14">
+        <f t="shared" si="1"/>
+        <v>-180.29166666666652</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="10">
+        <v>3417</v>
+      </c>
+      <c r="C31" s="12">
+        <f t="shared" si="0"/>
+        <v>3254</v>
+      </c>
+      <c r="D31" s="14">
+        <f t="shared" si="1"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="10">
+        <v>3449</v>
+      </c>
+      <c r="C32" s="12">
+        <f t="shared" si="0"/>
+        <v>3256.9583333333335</v>
+      </c>
+      <c r="D32" s="14">
+        <f t="shared" si="1"/>
+        <v>192.04166666666652</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="10">
+        <v>3527</v>
+      </c>
+      <c r="C33" s="12">
+        <f t="shared" si="0"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D33" s="14">
+        <f t="shared" si="1"/>
+        <v>270.29166666666652</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="10">
+        <v>3645</v>
+      </c>
+      <c r="C34" s="12">
+        <f t="shared" si="0"/>
+        <v>3269</v>
+      </c>
+      <c r="D34" s="14">
+        <f t="shared" si="1"/>
+        <v>376</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="10">
+        <v>3543</v>
+      </c>
+      <c r="C35" s="12">
+        <f t="shared" si="0"/>
+        <v>3279.0833333333335</v>
+      </c>
+      <c r="D35" s="14">
+        <f t="shared" si="1"/>
+        <v>263.91666666666652</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="10">
+        <v>3506</v>
+      </c>
+      <c r="C36" s="12">
+        <f t="shared" si="0"/>
+        <v>3252.8333333333335</v>
+      </c>
+      <c r="D36" s="14">
+        <f t="shared" si="1"/>
+        <v>253.16666666666652</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="10">
+        <v>3274</v>
+      </c>
+      <c r="C37" s="12">
+        <f t="shared" si="0"/>
+        <v>3228.0416666666665</v>
+      </c>
+      <c r="D37" s="14">
+        <f t="shared" si="1"/>
+        <v>45.958333333333485</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="10">
+        <v>3228</v>
+      </c>
+      <c r="C38" s="12">
+        <f t="shared" si="0"/>
+        <v>3248.2083333333335</v>
+      </c>
+      <c r="D38" s="14">
+        <f t="shared" si="1"/>
+        <v>-20.208333333333485</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="10">
+        <v>2895</v>
+      </c>
+      <c r="C39" s="12">
+        <f t="shared" si="0"/>
+        <v>3294.2916666666665</v>
+      </c>
+      <c r="D39" s="14">
+        <f t="shared" si="1"/>
+        <v>-399.29166666666652</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="10">
+        <v>2883</v>
+      </c>
+      <c r="C40" s="12">
+        <f t="shared" si="0"/>
+        <v>3340.3333333333335</v>
+      </c>
+      <c r="D40" s="14">
+        <f t="shared" si="1"/>
+        <v>-457.33333333333348</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="10">
+        <v>2850</v>
+      </c>
+      <c r="C41" s="12">
+        <f t="shared" si="0"/>
+        <v>3384.6666666666665</v>
+      </c>
+      <c r="D41" s="14">
+        <f t="shared" si="1"/>
+        <v>-534.66666666666652</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="10">
+        <v>2555</v>
+      </c>
+      <c r="C42" s="12">
+        <f t="shared" si="0"/>
+        <v>3433.5416666666665</v>
+      </c>
+      <c r="D42" s="14">
+        <f t="shared" si="1"/>
+        <v>-878.54166666666652</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="10">
+        <v>3346</v>
+      </c>
+      <c r="C43" s="12">
+        <f t="shared" si="0"/>
+        <v>3481.2916666666665</v>
+      </c>
+      <c r="D43" s="14">
+        <f t="shared" si="1"/>
+        <v>-135.29166666666652</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="10">
+        <v>4004</v>
+      </c>
+      <c r="C44" s="12">
+        <f t="shared" si="0"/>
+        <v>3514.8333333333335</v>
+      </c>
+      <c r="D44" s="14">
+        <f t="shared" si="1"/>
+        <v>489.16666666666652</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="10">
+        <v>4078</v>
+      </c>
+      <c r="C45" s="12">
+        <f t="shared" si="0"/>
+        <v>3549.875</v>
+      </c>
+      <c r="D45" s="14">
+        <f t="shared" si="1"/>
+        <v>528.125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="10">
+        <v>4199</v>
+      </c>
+      <c r="C46" s="12">
+        <f t="shared" si="0"/>
+        <v>3567.7083333333335</v>
+      </c>
+      <c r="D46" s="14">
+        <f t="shared" si="1"/>
+        <v>631.29166666666652</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="10">
+        <v>4053</v>
+      </c>
+      <c r="C47" s="12">
+        <f t="shared" si="0"/>
+        <v>3590.6666666666665</v>
+      </c>
+      <c r="D47" s="14">
+        <f t="shared" si="1"/>
+        <v>462.33333333333348</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="10">
+        <v>4169</v>
+      </c>
+      <c r="C48" s="12">
+        <f t="shared" si="0"/>
+        <v>3672.125</v>
+      </c>
+      <c r="D48" s="14">
+        <f t="shared" si="1"/>
+        <v>496.875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="10">
+        <v>3757</v>
+      </c>
+      <c r="C49" s="12">
+        <f t="shared" si="0"/>
+        <v>3758.1666666666665</v>
+      </c>
+      <c r="D49" s="14">
+        <f t="shared" si="1"/>
+        <v>-1.1666666666665151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="10">
+        <v>3550</v>
+      </c>
+      <c r="C50" s="12">
+        <f t="shared" si="0"/>
+        <v>3793.7916666666665</v>
+      </c>
+      <c r="D50" s="14">
+        <f t="shared" si="1"/>
+        <v>-243.79166666666652</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="10">
+        <v>3414</v>
+      </c>
+      <c r="C51" s="12">
+        <f t="shared" si="0"/>
+        <v>3804.8333333333335</v>
+      </c>
+      <c r="D51" s="14">
+        <f t="shared" si="1"/>
+        <v>-390.83333333333348</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="10">
+        <v>2792</v>
+      </c>
+      <c r="C52" s="12">
+        <f t="shared" si="0"/>
+        <v>3816.625</v>
+      </c>
+      <c r="D52" s="14">
+        <f t="shared" si="1"/>
+        <v>-1024.625</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="10">
+        <v>3492</v>
+      </c>
+      <c r="C53" s="12">
+        <f t="shared" si="0"/>
+        <v>3830.9583333333335</v>
+      </c>
+      <c r="D53" s="14">
+        <f t="shared" si="1"/>
+        <v>-338.95833333333348</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="10">
+        <v>3868</v>
+      </c>
+      <c r="C54" s="12">
+        <f t="shared" si="0"/>
+        <v>3853.2916666666665</v>
+      </c>
+      <c r="D54" s="14">
+        <f t="shared" si="1"/>
+        <v>14.708333333333485</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="10">
+        <v>4098</v>
+      </c>
+      <c r="C55" s="12">
+        <f t="shared" si="0"/>
+        <v>3875.5</v>
+      </c>
+      <c r="D55" s="14">
+        <f t="shared" si="1"/>
+        <v>222.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="10">
+        <v>4107</v>
+      </c>
+      <c r="C56" s="12">
+        <f t="shared" si="0"/>
+        <v>3899.8333333333335</v>
+      </c>
+      <c r="D56" s="14">
+        <f t="shared" si="1"/>
+        <v>207.16666666666652</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="10">
+        <v>4240</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="D2" t="str">
-        <f t="shared" ref="D2:D7" si="0">IFERROR(B2-C2, "NA")</f>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="10">
+        <v>4320</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D58" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>NA</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>2748</v>
-      </c>
-      <c r="C3" t="str">
-        <f>IFERROR(((0.5 *#REF!)+#REF!+#REF!+#REF!+B1+B2+B3+B4+B5+B6+B7+B8+(0.5*B9))/12, "NA")</f>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="10">
+        <v>4276</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D59" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="D3" t="str">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="10">
+        <v>4482</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>NA</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>3164</v>
-      </c>
-      <c r="C4" t="str">
-        <f>IFERROR(((0.5 *#REF!)+#REF!+#REF!+B1+B2+B3+B4+B5+B6+B7+B8+B9+(0.5*B10))/12, "NA")</f>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="10">
+        <v>3977</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="D4" t="str">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="16">
+        <v>3914</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>NA</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>3238</v>
-      </c>
-      <c r="C5" t="str">
-        <f>IFERROR(((0.5 *#REF!)+#REF!+B1+B2+B3+B4+B5+B6+B7+B8+B9+B10+(0.5*B11))/12, "NA")</f>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="18"/>
+      <c r="N66" s="19"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A67" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="G67" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="H67" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="I67" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="J67" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="K67" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="L67" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="M67" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="N67" s="23"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A68" s="24">
+        <v>2017</v>
+      </c>
+      <c r="B68" s="10" t="str" cm="1">
+        <f t="array" ref="B68:M68">TRANSPOSE(D3:D14)</f>
         <v>NA</v>
       </c>
-      <c r="D5" t="str">
-        <f t="shared" si="0"/>
+      <c r="C68" s="10" t="str">
         <v>NA</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3416</v>
-      </c>
-      <c r="C6" t="str">
-        <f>IFERROR(((0.5 *#REF!)+B1+B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+(0.5*B12))/12, "NA")</f>
+      <c r="D68" s="10" t="str">
         <v>NA</v>
       </c>
-      <c r="D6" t="str">
-        <f t="shared" si="0"/>
+      <c r="E68" s="10" t="str">
         <v>NA</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>3492</v>
-      </c>
-      <c r="C7" t="str">
-        <f t="shared" ref="C7" si="1">IFERROR(((0.5 * B1)+B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+(0.5*B13))/12, "NA")</f>
+      <c r="F68" s="10" t="str">
         <v>NA</v>
       </c>
-      <c r="D7" t="str">
-        <f t="shared" si="0"/>
+      <c r="G68" s="10" t="str">
         <v>NA</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>3730</v>
-      </c>
-      <c r="C8" s="3">
-        <f>IFERROR(((0.5 * B2)+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+(0.5*B14))/12, "NA")</f>
-        <v>3351.5833333333335</v>
-      </c>
-      <c r="D8" s="3">
-        <f>IFERROR(B8-C8, "NA")</f>
+      <c r="H68" s="14">
         <v>378.41666666666652</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>3409</v>
-      </c>
-      <c r="C9" s="3">
-        <f>IFERROR(((0.5 * B3)+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+(0.5*B15))/12, "NA")</f>
-        <v>3350</v>
-      </c>
-      <c r="D9" s="3">
-        <f t="shared" ref="D9:D61" si="2">IFERROR(B9-C9, "NA")</f>
+      <c r="I68" s="14">
         <v>59</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>3572</v>
-      </c>
-      <c r="C10" s="3">
-        <f t="shared" ref="C10:C61" si="3">IFERROR(((0.5 * B4)+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+(0.5*B16))/12, "NA")</f>
-        <v>3343.2083333333335</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="J68" s="14">
+        <v>228.79166666666652</v>
+      </c>
+      <c r="K68" s="14">
+        <v>302.79166666666652</v>
+      </c>
+      <c r="L68" s="14">
+        <v>91.458333333333485</v>
+      </c>
+      <c r="M68" s="14">
+        <v>72.416666666666515</v>
+      </c>
+      <c r="N68" s="25"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A69" s="24">
+        <v>2018</v>
+      </c>
+      <c r="B69" s="14" cm="1">
+        <f t="array" ref="B69:M69">TRANSPOSE(D15:D26)</f>
+        <v>-302.08333333333348</v>
+      </c>
+      <c r="C69" s="14">
+        <v>-574.04166666666652</v>
+      </c>
+      <c r="D69" s="12">
+        <v>-296.70833333333348</v>
+      </c>
+      <c r="E69" s="12">
+        <v>-334.16666666666652</v>
+      </c>
+      <c r="F69" s="12">
+        <v>135.25</v>
+      </c>
+      <c r="G69" s="12">
+        <v>221.58333333333348</v>
+      </c>
+      <c r="H69" s="12">
+        <v>270.91666666666652</v>
+      </c>
+      <c r="I69" s="12">
+        <v>219.79166666666652</v>
+      </c>
+      <c r="J69" s="12">
+        <v>319.54166666666652</v>
+      </c>
+      <c r="K69" s="12">
+        <v>395.83333333333348</v>
+      </c>
+      <c r="L69" s="12">
+        <v>-14.25</v>
+      </c>
+      <c r="M69" s="13">
+        <v>-79.458333333333485</v>
+      </c>
+      <c r="N69" s="25"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A70" s="24">
+        <v>2019</v>
+      </c>
+      <c r="B70" s="12" cm="1">
+        <f t="array" ref="B70:M70">TRANSPOSE(D27:D38)</f>
+        <v>-308.70833333333348</v>
+      </c>
+      <c r="C70" s="12">
+        <v>-727.125</v>
+      </c>
+      <c r="D70" s="12">
+        <v>-311.08333333333348</v>
+      </c>
+      <c r="E70" s="12">
+        <v>-180.29166666666652</v>
+      </c>
+      <c r="F70" s="12">
+        <v>163</v>
+      </c>
+      <c r="G70" s="12">
+        <v>192.04166666666652</v>
+      </c>
+      <c r="H70" s="12">
+        <v>270.29166666666652</v>
+      </c>
+      <c r="I70" s="12">
+        <v>376</v>
+      </c>
+      <c r="J70" s="12">
+        <v>263.91666666666652</v>
+      </c>
+      <c r="K70" s="12">
+        <v>253.16666666666652</v>
+      </c>
+      <c r="L70" s="12">
+        <v>45.958333333333485</v>
+      </c>
+      <c r="M70" s="13">
+        <v>-20.208333333333485</v>
+      </c>
+      <c r="N70" s="25"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A71" s="24">
+        <v>2020</v>
+      </c>
+      <c r="B71" s="12" cm="1">
+        <f t="array" ref="B71:M71">TRANSPOSE(D39:D50)</f>
+        <v>-399.29166666666652</v>
+      </c>
+      <c r="C71" s="12">
+        <v>-457.33333333333348</v>
+      </c>
+      <c r="D71" s="12">
+        <v>-534.66666666666652</v>
+      </c>
+      <c r="E71" s="12">
+        <v>-878.54166666666652</v>
+      </c>
+      <c r="F71" s="12">
+        <v>-135.29166666666652</v>
+      </c>
+      <c r="G71" s="12">
+        <v>489.16666666666652</v>
+      </c>
+      <c r="H71" s="12">
+        <v>528.125</v>
+      </c>
+      <c r="I71" s="12">
+        <v>631.29166666666652</v>
+      </c>
+      <c r="J71" s="12">
+        <v>462.33333333333348</v>
+      </c>
+      <c r="K71" s="12">
+        <v>496.875</v>
+      </c>
+      <c r="L71" s="12">
+        <v>-1.1666666666665151</v>
+      </c>
+      <c r="M71" s="13">
+        <v>-243.79166666666652</v>
+      </c>
+      <c r="N71" s="26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A72" s="24">
+        <v>2021</v>
+      </c>
+      <c r="B72" s="12" cm="1">
+        <f t="array" ref="B72:M72">TRANSPOSE(D51:D62)</f>
+        <v>-390.83333333333348</v>
+      </c>
+      <c r="C72" s="12">
+        <v>-1024.625</v>
+      </c>
+      <c r="D72" s="12">
+        <v>-338.95833333333348</v>
+      </c>
+      <c r="E72" s="12">
+        <v>14.708333333333485</v>
+      </c>
+      <c r="F72" s="12">
+        <v>222.5</v>
+      </c>
+      <c r="G72" s="12">
+        <v>207.16666666666652</v>
+      </c>
+      <c r="H72" s="10" t="str">
+        <v>NA</v>
+      </c>
+      <c r="I72" s="10" t="str">
+        <v>NA</v>
+      </c>
+      <c r="J72" s="10" t="str">
+        <v>NA</v>
+      </c>
+      <c r="K72" s="10" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L72" s="10" t="str">
+        <v>NA</v>
+      </c>
+      <c r="M72" s="11" t="str">
+        <v>NA</v>
+      </c>
+      <c r="N72" s="27"/>
+    </row>
+    <row r="73" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73" s="12">
+        <f>AVERAGE(B68:B72)</f>
+        <v>-350.22916666666674</v>
+      </c>
+      <c r="C73" s="12">
+        <f>AVERAGE(C68:C72)</f>
+        <v>-695.78125</v>
+      </c>
+      <c r="D73" s="12">
+        <f>AVERAGE(D68:D72)</f>
+        <v>-370.35416666666674</v>
+      </c>
+      <c r="E73" s="14">
+        <f t="shared" ref="E73:M73" si="2">AVERAGE(E68:E72)</f>
+        <v>-344.57291666666652</v>
+      </c>
+      <c r="F73" s="14">
         <f t="shared" si="2"/>
-        <v>228.79166666666652</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>3629</v>
-      </c>
-      <c r="C11" s="3">
-        <f t="shared" si="3"/>
-        <v>3326.2083333333335</v>
-      </c>
-      <c r="D11" s="3">
+        <v>96.364583333333371</v>
+      </c>
+      <c r="G73" s="14">
         <f t="shared" si="2"/>
-        <v>302.79166666666652</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12">
-        <v>3408</v>
-      </c>
-      <c r="C12" s="3">
-        <f t="shared" si="3"/>
-        <v>3316.5416666666665</v>
-      </c>
-      <c r="D12" s="3">
+        <v>277.48958333333326</v>
+      </c>
+      <c r="H73" s="14">
         <f t="shared" si="2"/>
-        <v>91.458333333333485</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13">
-        <v>3391</v>
-      </c>
-      <c r="C13" s="3">
-        <f t="shared" si="3"/>
-        <v>3318.5833333333335</v>
-      </c>
-      <c r="D13" s="3">
+        <v>361.93749999999989</v>
+      </c>
+      <c r="I73" s="14">
         <f t="shared" si="2"/>
-        <v>72.416666666666515</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
-        <v>3010</v>
-      </c>
-      <c r="C14" s="3">
-        <f t="shared" si="3"/>
-        <v>3312.0833333333335</v>
-      </c>
-      <c r="D14" s="3">
+        <v>321.52083333333326</v>
+      </c>
+      <c r="J73" s="14">
         <f t="shared" si="2"/>
-        <v>-302.08333333333348</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15">
-        <v>2734</v>
-      </c>
-      <c r="C15" s="3">
-        <f t="shared" si="3"/>
-        <v>3308.0416666666665</v>
-      </c>
-      <c r="D15" s="3">
+        <v>318.64583333333326</v>
+      </c>
+      <c r="K73" s="14">
         <f t="shared" si="2"/>
-        <v>-574.04166666666652</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16">
-        <v>3015</v>
-      </c>
-      <c r="C16" s="3">
-        <f t="shared" si="3"/>
-        <v>3311.7083333333335</v>
-      </c>
-      <c r="D16" s="3">
+        <v>362.16666666666663</v>
+      </c>
+      <c r="L73" s="14">
         <f t="shared" si="2"/>
-        <v>-296.70833333333348</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17">
-        <v>2979</v>
-      </c>
-      <c r="C17" s="3">
-        <f t="shared" si="3"/>
-        <v>3313.1666666666665</v>
-      </c>
-      <c r="D17" s="3">
+        <v>30.500000000000114</v>
+      </c>
+      <c r="M73" s="14">
         <f t="shared" si="2"/>
-        <v>-334.16666666666652</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18">
-        <v>3443</v>
-      </c>
-      <c r="C18" s="3">
-        <f t="shared" si="3"/>
-        <v>3307.75</v>
-      </c>
-      <c r="D18" s="3">
-        <f t="shared" si="2"/>
-        <v>135.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19">
-        <v>3514</v>
-      </c>
-      <c r="C19" s="3">
-        <f t="shared" si="3"/>
-        <v>3292.4166666666665</v>
-      </c>
-      <c r="D19" s="3">
-        <f t="shared" si="2"/>
-        <v>221.58333333333348</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20">
-        <v>3552</v>
-      </c>
-      <c r="C20" s="3">
-        <f t="shared" si="3"/>
-        <v>3281.0833333333335</v>
-      </c>
-      <c r="D20" s="3">
-        <f t="shared" si="2"/>
-        <v>270.91666666666652</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21">
-        <v>3490</v>
-      </c>
-      <c r="C21" s="3">
-        <f t="shared" si="3"/>
-        <v>3270.2083333333335</v>
-      </c>
-      <c r="D21" s="3">
-        <f t="shared" si="2"/>
-        <v>219.79166666666652</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22">
-        <v>3579</v>
-      </c>
-      <c r="C22" s="3">
-        <f t="shared" si="3"/>
-        <v>3259.4583333333335</v>
-      </c>
-      <c r="D22" s="3">
-        <f t="shared" si="2"/>
-        <v>319.54166666666652</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23">
-        <v>3657</v>
-      </c>
-      <c r="C23" s="3">
-        <f t="shared" si="3"/>
-        <v>3261.1666666666665</v>
-      </c>
-      <c r="D23" s="3">
-        <f t="shared" si="2"/>
-        <v>395.83333333333348</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24">
-        <v>3250</v>
-      </c>
-      <c r="C24" s="3">
-        <f t="shared" si="3"/>
-        <v>3264.25</v>
-      </c>
-      <c r="D24" s="3">
-        <f t="shared" si="2"/>
-        <v>-14.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25">
-        <v>3181</v>
-      </c>
-      <c r="C25" s="3">
-        <f t="shared" si="3"/>
-        <v>3260.4583333333335</v>
-      </c>
-      <c r="D25" s="3">
-        <f t="shared" si="2"/>
-        <v>-79.458333333333485</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26">
-        <v>2948</v>
-      </c>
-      <c r="C26" s="3">
-        <f t="shared" si="3"/>
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D26" s="3">
-        <f t="shared" si="2"/>
-        <v>-308.70833333333348</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27">
-        <v>2535</v>
-      </c>
-      <c r="C27" s="3">
-        <f t="shared" si="3"/>
-        <v>3262.125</v>
-      </c>
-      <c r="D27" s="3">
-        <f t="shared" si="2"/>
-        <v>-727.125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28">
-        <v>2956</v>
-      </c>
-      <c r="C28" s="3">
-        <f t="shared" si="3"/>
-        <v>3267.0833333333335</v>
-      </c>
-      <c r="D28" s="3">
-        <f t="shared" si="2"/>
-        <v>-311.08333333333348</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29">
-        <v>3079</v>
-      </c>
-      <c r="C29" s="3">
-        <f t="shared" si="3"/>
-        <v>3259.2916666666665</v>
-      </c>
-      <c r="D29" s="3">
-        <f t="shared" si="2"/>
-        <v>-180.29166666666652</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30">
-        <v>3417</v>
-      </c>
-      <c r="C30" s="3">
-        <f t="shared" si="3"/>
-        <v>3254</v>
-      </c>
-      <c r="D30" s="3">
-        <f t="shared" si="2"/>
-        <v>163</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31">
-        <v>3449</v>
-      </c>
-      <c r="C31" s="3">
-        <f t="shared" si="3"/>
-        <v>3256.9583333333335</v>
-      </c>
-      <c r="D31" s="3">
-        <f t="shared" si="2"/>
-        <v>192.04166666666652</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32">
-        <v>3527</v>
-      </c>
-      <c r="C32" s="3">
-        <f t="shared" si="3"/>
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D32" s="3">
-        <f t="shared" si="2"/>
-        <v>270.29166666666652</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33">
-        <v>3645</v>
-      </c>
-      <c r="C33" s="3">
-        <f t="shared" si="3"/>
-        <v>3269</v>
-      </c>
-      <c r="D33" s="3">
-        <f t="shared" si="2"/>
-        <v>376</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34">
-        <v>3543</v>
-      </c>
-      <c r="C34" s="3">
-        <f t="shared" si="3"/>
-        <v>3279.0833333333335</v>
-      </c>
-      <c r="D34" s="3">
-        <f t="shared" si="2"/>
-        <v>263.91666666666652</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35">
-        <v>3506</v>
-      </c>
-      <c r="C35" s="3">
-        <f t="shared" si="3"/>
-        <v>3252.8333333333335</v>
-      </c>
-      <c r="D35" s="3">
-        <f t="shared" si="2"/>
-        <v>253.16666666666652</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36">
-        <v>3274</v>
-      </c>
-      <c r="C36" s="3">
-        <f t="shared" si="3"/>
-        <v>3228.0416666666665</v>
-      </c>
-      <c r="D36" s="3">
-        <f t="shared" si="2"/>
-        <v>45.958333333333485</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37">
-        <v>3228</v>
-      </c>
-      <c r="C37" s="3">
-        <f t="shared" si="3"/>
-        <v>3248.2083333333335</v>
-      </c>
-      <c r="D37" s="3">
-        <f t="shared" si="2"/>
-        <v>-20.208333333333485</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38">
-        <v>2895</v>
-      </c>
-      <c r="C38" s="3">
-        <f t="shared" si="3"/>
-        <v>3294.2916666666665</v>
-      </c>
-      <c r="D38" s="3">
-        <f t="shared" si="2"/>
-        <v>-399.29166666666652</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39">
-        <v>2883</v>
-      </c>
-      <c r="C39" s="3">
-        <f t="shared" si="3"/>
-        <v>3340.3333333333335</v>
-      </c>
-      <c r="D39" s="3">
-        <f t="shared" si="2"/>
-        <v>-457.33333333333348</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40">
-        <v>2850</v>
-      </c>
-      <c r="C40" s="3">
-        <f t="shared" si="3"/>
-        <v>3384.6666666666665</v>
-      </c>
-      <c r="D40" s="3">
-        <f t="shared" si="2"/>
-        <v>-534.66666666666652</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41">
-        <v>2555</v>
-      </c>
-      <c r="C41" s="3">
-        <f t="shared" si="3"/>
-        <v>3433.5416666666665</v>
-      </c>
-      <c r="D41" s="3">
-        <f t="shared" si="2"/>
-        <v>-878.54166666666652</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42">
-        <v>3346</v>
-      </c>
-      <c r="C42" s="3">
-        <f t="shared" si="3"/>
-        <v>3481.2916666666665</v>
-      </c>
-      <c r="D42" s="3">
-        <f t="shared" si="2"/>
-        <v>-135.29166666666652</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43">
-        <v>4004</v>
-      </c>
-      <c r="C43" s="3">
-        <f t="shared" si="3"/>
-        <v>3514.8333333333335</v>
-      </c>
-      <c r="D43" s="3">
-        <f t="shared" si="2"/>
-        <v>489.16666666666652</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44">
-        <v>4078</v>
-      </c>
-      <c r="C44" s="3">
-        <f t="shared" si="3"/>
-        <v>3549.875</v>
-      </c>
-      <c r="D44" s="3">
-        <f t="shared" si="2"/>
-        <v>528.125</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45">
-        <v>4199</v>
-      </c>
-      <c r="C45" s="3">
-        <f t="shared" si="3"/>
-        <v>3567.7083333333335</v>
-      </c>
-      <c r="D45" s="3">
-        <f t="shared" si="2"/>
-        <v>631.29166666666652</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46">
-        <v>4053</v>
-      </c>
-      <c r="C46" s="3">
-        <f t="shared" si="3"/>
-        <v>3590.6666666666665</v>
-      </c>
-      <c r="D46" s="3">
-        <f t="shared" si="2"/>
-        <v>462.33333333333348</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47">
-        <v>4169</v>
-      </c>
-      <c r="C47" s="3">
-        <f t="shared" si="3"/>
-        <v>3672.125</v>
-      </c>
-      <c r="D47" s="3">
-        <f t="shared" si="2"/>
-        <v>496.875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48">
-        <v>3757</v>
-      </c>
-      <c r="C48" s="3">
-        <f t="shared" si="3"/>
-        <v>3758.1666666666665</v>
-      </c>
-      <c r="D48" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.1666666666665151</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49">
-        <v>3550</v>
-      </c>
-      <c r="C49" s="3">
-        <f t="shared" si="3"/>
-        <v>3793.7916666666665</v>
-      </c>
-      <c r="D49" s="3">
-        <f t="shared" si="2"/>
-        <v>-243.79166666666652</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50">
-        <v>3414</v>
-      </c>
-      <c r="C50" s="3">
-        <f t="shared" si="3"/>
-        <v>3804.8333333333335</v>
-      </c>
-      <c r="D50" s="3">
-        <f t="shared" si="2"/>
-        <v>-390.83333333333348</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51">
-        <v>2792</v>
-      </c>
-      <c r="C51" s="3">
-        <f t="shared" si="3"/>
-        <v>3816.625</v>
-      </c>
-      <c r="D51" s="3">
-        <f t="shared" si="2"/>
-        <v>-1024.625</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52">
-        <v>3492</v>
-      </c>
-      <c r="C52" s="3">
-        <f t="shared" si="3"/>
-        <v>3830.9583333333335</v>
-      </c>
-      <c r="D52" s="3">
-        <f t="shared" si="2"/>
-        <v>-338.95833333333348</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53">
-        <v>3868</v>
-      </c>
-      <c r="C53" s="3">
-        <f t="shared" si="3"/>
-        <v>3853.2916666666665</v>
-      </c>
-      <c r="D53" s="3">
-        <f t="shared" si="2"/>
-        <v>14.708333333333485</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54">
-        <v>4098</v>
-      </c>
-      <c r="C54" s="3">
-        <f t="shared" si="3"/>
-        <v>3875.5</v>
-      </c>
-      <c r="D54" s="3">
-        <f t="shared" si="2"/>
-        <v>222.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>57</v>
-      </c>
-      <c r="B55">
-        <v>4107</v>
-      </c>
-      <c r="C55" s="3">
-        <f t="shared" si="3"/>
-        <v>3899.8333333333335</v>
-      </c>
-      <c r="D55" s="3">
-        <f t="shared" si="2"/>
-        <v>207.16666666666652</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>58</v>
-      </c>
-      <c r="B56">
-        <v>4240</v>
-      </c>
-      <c r="C56" t="str">
+        <v>-67.760416666666742</v>
+      </c>
+      <c r="N73" s="29">
+        <v>-5.0060763888889142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="30"/>
+      <c r="B74" s="31">
+        <f>B73-$N73</f>
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="C74" s="14">
+        <f>C73-$N73</f>
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="D74" s="14">
+        <f>D73-$N73</f>
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="E74" s="14">
+        <f>E73-$N73</f>
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F74" s="14">
+        <f>F73-$N73</f>
+        <v>101.37065972222229</v>
+      </c>
+      <c r="G74" s="14">
+        <f>G73-$N73</f>
+        <v>282.49565972222217</v>
+      </c>
+      <c r="H74" s="14">
+        <f>H73-$N73</f>
+        <v>366.9435763888888</v>
+      </c>
+      <c r="I74" s="14">
+        <f>I73-$N73</f>
+        <v>326.52690972222217</v>
+      </c>
+      <c r="J74" s="14">
+        <f>J73-$N73</f>
+        <v>323.65190972222217</v>
+      </c>
+      <c r="K74" s="14">
+        <f>K73-$N73</f>
+        <v>367.17274305555554</v>
+      </c>
+      <c r="L74" s="14">
+        <f>L73-$N73</f>
+        <v>35.506076388889028</v>
+      </c>
+      <c r="M74" s="14">
+        <f>M73-$N73</f>
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="N74" s="32"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:14" ht="43.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="34"/>
+      <c r="C78" s="34"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="34"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="35"/>
+    </row>
+    <row r="79" spans="1:14" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A80" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="10">
+        <f>B3</f>
+        <v>3034</v>
+      </c>
+      <c r="C80" s="10" t="str">
+        <f t="shared" ref="C80:D80" si="3">C3</f>
+        <v>NA</v>
+      </c>
+      <c r="D80" s="10" t="str">
         <f t="shared" si="3"/>
         <v>NA</v>
       </c>
-      <c r="D56" t="str">
-        <f t="shared" si="2"/>
+      <c r="E80" s="14" cm="1">
+        <f t="array" ref="E80:E91">TRANSPOSE(B$74:M$74)</f>
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="F80" s="10" t="str">
+        <f>IFERROR(B3-C3-E80, "NA")</f>
         <v>NA</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>59</v>
-      </c>
-      <c r="B57">
-        <v>4320</v>
-      </c>
-      <c r="C57" t="str">
-        <f t="shared" si="3"/>
-        <v>NA</v>
-      </c>
-      <c r="D57" t="str">
-        <f t="shared" si="2"/>
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>60</v>
-      </c>
-      <c r="B58">
-        <v>4276</v>
-      </c>
-      <c r="C58" t="str">
-        <f t="shared" si="3"/>
-        <v>NA</v>
-      </c>
-      <c r="D58" t="str">
-        <f t="shared" si="2"/>
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59">
-        <v>4482</v>
-      </c>
-      <c r="C59" t="str">
-        <f t="shared" si="3"/>
-        <v>NA</v>
-      </c>
-      <c r="D59" t="str">
-        <f t="shared" si="2"/>
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>62</v>
-      </c>
-      <c r="B60">
-        <v>3977</v>
-      </c>
-      <c r="C60" t="str">
-        <f t="shared" si="3"/>
-        <v>NA</v>
-      </c>
-      <c r="D60" t="str">
-        <f t="shared" si="2"/>
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61">
-        <v>3914</v>
-      </c>
-      <c r="C61" t="str">
-        <f t="shared" si="3"/>
-        <v>NA</v>
-      </c>
-      <c r="D61" t="str">
-        <f t="shared" si="2"/>
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B62" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>4</v>
-      </c>
-      <c r="B70">
-        <v>3034</v>
-      </c>
-      <c r="C70" t="str">
-        <f>IFERROR(((0.5 *#REF!)+#REF!+#REF!+#REF!+#REF!+B69+B70+B71+B72+B73+B74+B75+(0.5*B76))/12, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="D70" t="str">
-        <f t="shared" ref="D70:D75" si="4">IFERROR(B70-C70, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="E70" s="3" cm="1">
-        <f t="array" ref="E70:E81">TRANSPOSE(B$146:M$146)</f>
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="F70" t="str">
-        <f>IFERROR(B70-C70-E70, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="G70" s="3">
-        <f>B70-E70</f>
+      <c r="G80" s="14">
+        <f>B80-E80</f>
         <v>3379.2230902777778</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B71">
+      <c r="B81" s="10">
+        <f t="shared" ref="B81:D96" si="4">B4</f>
         <v>2748</v>
       </c>
-      <c r="C71" t="str">
-        <f>IFERROR(((0.5 *#REF!)+#REF!+#REF!+#REF!+B69+B70+B71+B72+B73+B74+B75+B76+(0.5*B77))/12, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="D71" t="str">
+      <c r="C81" s="10" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E71" s="3">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F71" t="str">
-        <f t="shared" ref="F71:F129" si="5">IFERROR(B71-C71-E71, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="G71" s="3">
-        <f t="shared" ref="G71:G129" si="6">B71-E71</f>
-        <v>3438.7751736111113</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72">
-        <v>3164</v>
-      </c>
-      <c r="C72" t="str">
-        <f>IFERROR(((0.5 *#REF!)+#REF!+#REF!+B69+B70+B71+B72+B73+B74+B75+B76+B77+(0.5*B78))/12, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="D72" t="str">
+      <c r="D81" s="13" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E81" s="14">
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="F81" s="10" t="str">
+        <f t="shared" ref="F81:F139" si="5">IFERROR(B4-C4-E81, "NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="G81" s="14">
+        <f t="shared" ref="G81:G139" si="6">B81-E81</f>
+        <v>3438.7751736111113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="10">
+        <f t="shared" si="4"/>
+        <v>3164</v>
+      </c>
+      <c r="C82" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="D82" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="E82" s="14">
         <v>-365.34809027777783</v>
       </c>
-      <c r="F72" t="str">
+      <c r="F82" s="10" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G82" s="14">
         <f t="shared" si="6"/>
         <v>3529.3480902777778</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B73">
+      <c r="B83" s="10">
+        <f t="shared" si="4"/>
         <v>3238</v>
       </c>
-      <c r="C73" t="str">
-        <f>IFERROR(((0.5 *#REF!)+#REF!+B69+B70+B71+B72+B73+B74+B75+B76+B77+B78+(0.5*B79))/12, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="D73" t="str">
+      <c r="C83" s="10" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E73" s="3">
+      <c r="D83" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="E83" s="14">
         <v>-339.5668402777776</v>
       </c>
-      <c r="F73" t="str">
+      <c r="F83" s="10" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G83" s="14">
         <f t="shared" si="6"/>
         <v>3577.5668402777774</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B74">
+      <c r="B84" s="10">
+        <f t="shared" si="4"/>
         <v>3416</v>
       </c>
-      <c r="C74" t="str">
-        <f>IFERROR(((0.5 *#REF!)+B69+B70+B71+B72+B73+B74+B75+B76+B77+B78+B79+(0.5*B80))/12, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="D74" t="str">
+      <c r="C84" s="10" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E74" s="3">
+      <c r="D84" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="E84" s="14">
         <v>101.37065972222229</v>
       </c>
-      <c r="F74" t="str">
+      <c r="F84" s="10" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G84" s="14">
         <f t="shared" si="6"/>
         <v>3314.6293402777778</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B75">
+      <c r="B85" s="10">
+        <f t="shared" si="4"/>
         <v>3492</v>
       </c>
-      <c r="C75" t="str">
-        <f t="shared" ref="C75:C76" si="7">IFERROR(((0.5 * B69)+B70+B71+B72+B73+B74+B75+B76+B77+B78+B79+B80+(0.5*B81))/12, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="D75" t="str">
+      <c r="C85" s="10" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E75" s="3">
+      <c r="D85" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="E85" s="14">
         <v>282.49565972222217</v>
       </c>
-      <c r="F75" t="str">
+      <c r="F85" s="10" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G85" s="14">
         <f t="shared" si="6"/>
         <v>3209.5043402777778</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B76">
+      <c r="B86" s="10">
+        <f t="shared" si="4"/>
         <v>3730</v>
       </c>
-      <c r="C76" s="3">
-        <f t="shared" si="7"/>
+      <c r="C86" s="12">
+        <f t="shared" si="4"/>
         <v>3351.5833333333335</v>
       </c>
-      <c r="D76" s="3">
-        <f>IFERROR(B76-C76, "NA")</f>
+      <c r="D86" s="13">
+        <f t="shared" si="4"/>
         <v>378.41666666666652</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E86" s="14">
         <v>366.9435763888888</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F86" s="14">
         <f t="shared" si="5"/>
         <v>11.473090277777715</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G86" s="14">
         <f t="shared" si="6"/>
         <v>3363.0564236111113</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B77">
+      <c r="B87" s="10">
+        <f t="shared" si="4"/>
         <v>3409</v>
       </c>
-      <c r="C77" s="3">
-        <f>IFERROR(((0.5 * B71)+B72+B73+B74+B75+B76+B77+B78+B79+B80+B81+B82+(0.5*B83))/12, "NA")</f>
+      <c r="C87" s="12">
+        <f t="shared" si="4"/>
         <v>3350</v>
       </c>
-      <c r="D77" s="3">
-        <f t="shared" ref="D77:D129" si="8">IFERROR(B77-C77, "NA")</f>
+      <c r="D87" s="13">
+        <f t="shared" si="4"/>
         <v>59</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E87" s="14">
         <v>326.52690972222217</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F87" s="14">
         <f t="shared" si="5"/>
         <v>-267.52690972222217</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G87" s="14">
         <f t="shared" si="6"/>
         <v>3082.4730902777778</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B78">
+      <c r="B88" s="10">
+        <f t="shared" si="4"/>
         <v>3572</v>
       </c>
-      <c r="C78" s="3">
-        <f t="shared" ref="C78:C129" si="9">IFERROR(((0.5 * B72)+B73+B74+B75+B76+B77+B78+B79+B80+B81+B82+B83+(0.5*B84))/12, "NA")</f>
+      <c r="C88" s="12">
+        <f t="shared" si="4"/>
         <v>3343.2083333333335</v>
       </c>
-      <c r="D78" s="3">
-        <f t="shared" si="8"/>
+      <c r="D88" s="13">
+        <f t="shared" si="4"/>
         <v>228.79166666666652</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E88" s="14">
         <v>323.65190972222217</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F88" s="14">
         <f t="shared" si="5"/>
         <v>-94.860243055555657</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G88" s="14">
         <f t="shared" si="6"/>
         <v>3248.3480902777778</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B79">
+      <c r="B89" s="10">
+        <f t="shared" si="4"/>
         <v>3629</v>
       </c>
-      <c r="C79" s="3">
-        <f t="shared" si="9"/>
+      <c r="C89" s="12">
+        <f t="shared" si="4"/>
         <v>3326.2083333333335</v>
       </c>
-      <c r="D79" s="3">
-        <f t="shared" si="8"/>
+      <c r="D89" s="13">
+        <f t="shared" si="4"/>
         <v>302.79166666666652</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E89" s="14">
         <v>367.17274305555554</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F89" s="14">
         <f t="shared" si="5"/>
         <v>-64.381076388889028</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G89" s="14">
         <f t="shared" si="6"/>
         <v>3261.8272569444443</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B80">
+      <c r="B90" s="10">
+        <f t="shared" si="4"/>
         <v>3408</v>
       </c>
-      <c r="C80" s="3">
-        <f t="shared" si="9"/>
+      <c r="C90" s="12">
+        <f t="shared" si="4"/>
         <v>3316.5416666666665</v>
       </c>
-      <c r="D80" s="3">
-        <f t="shared" si="8"/>
+      <c r="D90" s="13">
+        <f t="shared" si="4"/>
         <v>91.458333333333485</v>
       </c>
-      <c r="E80" s="3">
+      <c r="E90" s="14">
         <v>35.506076388889028</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F90" s="14">
         <f t="shared" si="5"/>
         <v>55.952256944444457</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G90" s="14">
         <f t="shared" si="6"/>
         <v>3372.4939236111109</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B81">
+      <c r="B91" s="10">
+        <f t="shared" si="4"/>
         <v>3391</v>
       </c>
-      <c r="C81" s="3">
-        <f t="shared" si="9"/>
+      <c r="C91" s="12">
+        <f t="shared" si="4"/>
         <v>3318.5833333333335</v>
       </c>
-      <c r="D81" s="3">
-        <f t="shared" si="8"/>
+      <c r="D91" s="13">
+        <f t="shared" si="4"/>
         <v>72.416666666666515</v>
       </c>
-      <c r="E81" s="3">
+      <c r="E91" s="14">
         <v>-62.754340277777828</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F91" s="14">
         <f t="shared" si="5"/>
         <v>135.17100694444434</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G91" s="14">
         <f t="shared" si="6"/>
         <v>3453.7543402777778</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B82">
+      <c r="B92" s="10">
+        <f t="shared" si="4"/>
         <v>3010</v>
       </c>
-      <c r="C82" s="3">
-        <f t="shared" si="9"/>
+      <c r="C92" s="12">
+        <f t="shared" si="4"/>
         <v>3312.0833333333335</v>
       </c>
-      <c r="D82" s="3">
-        <f t="shared" si="8"/>
+      <c r="D92" s="13">
+        <f t="shared" si="4"/>
         <v>-302.08333333333348</v>
       </c>
-      <c r="E82" s="3" cm="1">
-        <f t="array" ref="E82:E93">TRANSPOSE(B$146:M$146)</f>
+      <c r="E92" s="14" cm="1">
+        <f t="array" ref="E92:E103">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F92" s="14">
         <f t="shared" si="5"/>
         <v>43.139756944444343</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G92" s="14">
         <f t="shared" si="6"/>
         <v>3355.2230902777778</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B83">
+      <c r="B93" s="10">
+        <f t="shared" si="4"/>
         <v>2734</v>
       </c>
-      <c r="C83" s="3">
-        <f t="shared" si="9"/>
+      <c r="C93" s="12">
+        <f t="shared" si="4"/>
         <v>3308.0416666666665</v>
       </c>
-      <c r="D83" s="3">
-        <f t="shared" si="8"/>
+      <c r="D93" s="13">
+        <f t="shared" si="4"/>
         <v>-574.04166666666652</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E93" s="14">
         <v>-690.77517361111109</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F93" s="14">
         <f t="shared" si="5"/>
         <v>116.73350694444457</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G93" s="14">
         <f t="shared" si="6"/>
         <v>3424.7751736111113</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B84">
+      <c r="B94" s="10">
+        <f t="shared" si="4"/>
         <v>3015</v>
       </c>
-      <c r="C84" s="3">
-        <f t="shared" si="9"/>
+      <c r="C94" s="12">
+        <f t="shared" si="4"/>
         <v>3311.7083333333335</v>
       </c>
-      <c r="D84" s="3">
-        <f t="shared" si="8"/>
+      <c r="D94" s="13">
+        <f t="shared" si="4"/>
         <v>-296.70833333333348</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E94" s="14">
         <v>-365.34809027777783</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F94" s="14">
         <f t="shared" si="5"/>
         <v>68.639756944444343</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G94" s="14">
         <f t="shared" si="6"/>
         <v>3380.3480902777778</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B85">
+      <c r="B95" s="10">
+        <f t="shared" si="4"/>
         <v>2979</v>
       </c>
-      <c r="C85" s="3">
-        <f t="shared" si="9"/>
+      <c r="C95" s="12">
+        <f t="shared" si="4"/>
         <v>3313.1666666666665</v>
       </c>
-      <c r="D85" s="3">
-        <f t="shared" si="8"/>
+      <c r="D95" s="13">
+        <f t="shared" si="4"/>
         <v>-334.16666666666652</v>
       </c>
-      <c r="E85" s="3">
+      <c r="E95" s="14">
         <v>-339.5668402777776</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F95" s="14">
         <f t="shared" si="5"/>
         <v>5.4001736111110858</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G95" s="14">
         <f t="shared" si="6"/>
         <v>3318.5668402777774</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B86">
+      <c r="B96" s="10">
+        <f t="shared" si="4"/>
         <v>3443</v>
       </c>
-      <c r="C86" s="3">
-        <f t="shared" si="9"/>
+      <c r="C96" s="12">
+        <f t="shared" si="4"/>
         <v>3307.75</v>
       </c>
-      <c r="D86" s="3">
-        <f t="shared" si="8"/>
+      <c r="D96" s="13">
+        <f t="shared" si="4"/>
         <v>135.25</v>
       </c>
-      <c r="E86" s="3">
+      <c r="E96" s="14">
         <v>101.37065972222229</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F96" s="14">
         <f t="shared" si="5"/>
         <v>33.879340277777715</v>
       </c>
-      <c r="G86" s="3">
+      <c r="G96" s="14">
         <f t="shared" si="6"/>
         <v>3341.6293402777778</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A97" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B87">
+      <c r="B97" s="10">
+        <f t="shared" ref="B97:D112" si="7">B20</f>
         <v>3514</v>
       </c>
-      <c r="C87" s="3">
-        <f t="shared" si="9"/>
+      <c r="C97" s="12">
+        <f t="shared" si="7"/>
         <v>3292.4166666666665</v>
       </c>
-      <c r="D87" s="3">
-        <f t="shared" si="8"/>
+      <c r="D97" s="13">
+        <f t="shared" si="7"/>
         <v>221.58333333333348</v>
       </c>
-      <c r="E87" s="3">
+      <c r="E97" s="14">
         <v>282.49565972222217</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F97" s="14">
         <f t="shared" si="5"/>
         <v>-60.912326388888687</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G97" s="14">
         <f t="shared" si="6"/>
         <v>3231.5043402777778</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A98" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B88">
+      <c r="B98" s="10">
+        <f t="shared" si="7"/>
         <v>3552</v>
       </c>
-      <c r="C88" s="3">
-        <f t="shared" si="9"/>
+      <c r="C98" s="12">
+        <f t="shared" si="7"/>
         <v>3281.0833333333335</v>
       </c>
-      <c r="D88" s="3">
-        <f t="shared" si="8"/>
+      <c r="D98" s="13">
+        <f t="shared" si="7"/>
         <v>270.91666666666652</v>
       </c>
-      <c r="E88" s="3">
+      <c r="E98" s="14">
         <v>366.9435763888888</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F98" s="14">
         <f t="shared" si="5"/>
         <v>-96.026909722222285</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G98" s="14">
         <f t="shared" si="6"/>
         <v>3185.0564236111113</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A99" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B89">
+      <c r="B99" s="10">
+        <f t="shared" si="7"/>
         <v>3490</v>
       </c>
-      <c r="C89" s="3">
-        <f t="shared" si="9"/>
+      <c r="C99" s="12">
+        <f t="shared" si="7"/>
         <v>3270.2083333333335</v>
       </c>
-      <c r="D89" s="3">
-        <f t="shared" si="8"/>
+      <c r="D99" s="13">
+        <f t="shared" si="7"/>
         <v>219.79166666666652</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E99" s="14">
         <v>326.52690972222217</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F99" s="14">
         <f t="shared" si="5"/>
         <v>-106.73524305555566</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G99" s="14">
         <f t="shared" si="6"/>
         <v>3163.4730902777778</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A100" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B90">
+      <c r="B100" s="10">
+        <f t="shared" si="7"/>
         <v>3579</v>
       </c>
-      <c r="C90" s="3">
-        <f t="shared" si="9"/>
+      <c r="C100" s="12">
+        <f t="shared" si="7"/>
         <v>3259.4583333333335</v>
       </c>
-      <c r="D90" s="3">
-        <f t="shared" si="8"/>
+      <c r="D100" s="13">
+        <f t="shared" si="7"/>
         <v>319.54166666666652</v>
       </c>
-      <c r="E90" s="3">
+      <c r="E100" s="14">
         <v>323.65190972222217</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F100" s="14">
         <f t="shared" si="5"/>
         <v>-4.1102430555556566</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G100" s="14">
         <f t="shared" si="6"/>
         <v>3255.3480902777778</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A101" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B91">
+      <c r="B101" s="10">
+        <f t="shared" si="7"/>
         <v>3657</v>
       </c>
-      <c r="C91" s="3">
-        <f t="shared" si="9"/>
+      <c r="C101" s="12">
+        <f t="shared" si="7"/>
         <v>3261.1666666666665</v>
       </c>
-      <c r="D91" s="3">
-        <f t="shared" si="8"/>
+      <c r="D101" s="13">
+        <f t="shared" si="7"/>
         <v>395.83333333333348</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E101" s="14">
         <v>367.17274305555554</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F101" s="14">
         <f t="shared" si="5"/>
         <v>28.660590277777942</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G101" s="14">
         <f t="shared" si="6"/>
         <v>3289.8272569444443</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A102" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B92">
+      <c r="B102" s="10">
+        <f t="shared" si="7"/>
         <v>3250</v>
       </c>
-      <c r="C92" s="3">
-        <f t="shared" si="9"/>
+      <c r="C102" s="12">
+        <f t="shared" si="7"/>
         <v>3264.25</v>
       </c>
-      <c r="D92" s="3">
-        <f t="shared" si="8"/>
+      <c r="D102" s="13">
+        <f t="shared" si="7"/>
         <v>-14.25</v>
       </c>
-      <c r="E92" s="3">
+      <c r="E102" s="14">
         <v>35.506076388889028</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F102" s="14">
         <f t="shared" si="5"/>
         <v>-49.756076388889028</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G102" s="14">
         <f t="shared" si="6"/>
         <v>3214.4939236111109</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A103" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B93">
+      <c r="B103" s="10">
+        <f t="shared" si="7"/>
         <v>3181</v>
       </c>
-      <c r="C93" s="3">
-        <f t="shared" si="9"/>
+      <c r="C103" s="12">
+        <f t="shared" si="7"/>
         <v>3260.4583333333335</v>
       </c>
-      <c r="D93" s="3">
-        <f t="shared" si="8"/>
+      <c r="D103" s="13">
+        <f t="shared" si="7"/>
         <v>-79.458333333333485</v>
       </c>
-      <c r="E93" s="3">
+      <c r="E103" s="14">
         <v>-62.754340277777828</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F103" s="14">
         <f t="shared" si="5"/>
         <v>-16.703993055555657</v>
       </c>
-      <c r="G93" s="3">
+      <c r="G103" s="14">
         <f t="shared" si="6"/>
         <v>3243.7543402777778</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A104" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B94">
+      <c r="B104" s="10">
+        <f t="shared" si="7"/>
         <v>2948</v>
       </c>
-      <c r="C94" s="3">
-        <f t="shared" si="9"/>
+      <c r="C104" s="12">
+        <f t="shared" si="7"/>
         <v>3256.7083333333335</v>
       </c>
-      <c r="D94" s="3">
-        <f t="shared" si="8"/>
+      <c r="D104" s="13">
+        <f t="shared" si="7"/>
         <v>-308.70833333333348</v>
       </c>
-      <c r="E94" s="3" cm="1">
-        <f t="array" ref="E94:E105">TRANSPOSE(B$146:M$146)</f>
+      <c r="E104" s="14" cm="1">
+        <f t="array" ref="E104:E115">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F104" s="14">
         <f t="shared" si="5"/>
         <v>36.514756944444343</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G104" s="14">
         <f t="shared" si="6"/>
         <v>3293.2230902777778</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A105" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B95">
+      <c r="B105" s="10">
+        <f t="shared" si="7"/>
         <v>2535</v>
       </c>
-      <c r="C95" s="3">
-        <f t="shared" si="9"/>
+      <c r="C105" s="12">
+        <f t="shared" si="7"/>
         <v>3262.125</v>
       </c>
-      <c r="D95" s="3">
-        <f t="shared" si="8"/>
+      <c r="D105" s="13">
+        <f t="shared" si="7"/>
         <v>-727.125</v>
       </c>
-      <c r="E95" s="3">
+      <c r="E105" s="14">
         <v>-690.77517361111109</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F105" s="14">
         <f t="shared" si="5"/>
         <v>-36.349826388888914</v>
       </c>
-      <c r="G95" s="3">
+      <c r="G105" s="14">
         <f t="shared" si="6"/>
         <v>3225.7751736111113</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A106" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B96">
+      <c r="B106" s="10">
+        <f t="shared" si="7"/>
         <v>2956</v>
       </c>
-      <c r="C96" s="3">
-        <f t="shared" si="9"/>
+      <c r="C106" s="12">
+        <f t="shared" si="7"/>
         <v>3267.0833333333335</v>
       </c>
-      <c r="D96" s="3">
-        <f t="shared" si="8"/>
+      <c r="D106" s="13">
+        <f t="shared" si="7"/>
         <v>-311.08333333333348</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E106" s="14">
         <v>-365.34809027777783</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F106" s="14">
         <f t="shared" si="5"/>
         <v>54.264756944444343</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G106" s="14">
         <f t="shared" si="6"/>
         <v>3321.3480902777778</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A107" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B97">
+      <c r="B107" s="10">
+        <f t="shared" si="7"/>
         <v>3079</v>
       </c>
-      <c r="C97" s="3">
-        <f t="shared" si="9"/>
+      <c r="C107" s="12">
+        <f t="shared" si="7"/>
         <v>3259.2916666666665</v>
       </c>
-      <c r="D97" s="3">
-        <f t="shared" si="8"/>
+      <c r="D107" s="13">
+        <f t="shared" si="7"/>
         <v>-180.29166666666652</v>
       </c>
-      <c r="E97" s="3">
+      <c r="E107" s="14">
         <v>-339.5668402777776</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F107" s="14">
         <f t="shared" si="5"/>
         <v>159.27517361111109</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G107" s="14">
         <f t="shared" si="6"/>
         <v>3418.5668402777774</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A108" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B98">
+      <c r="B108" s="10">
+        <f t="shared" si="7"/>
         <v>3417</v>
       </c>
-      <c r="C98" s="3">
-        <f t="shared" si="9"/>
+      <c r="C108" s="12">
+        <f t="shared" si="7"/>
         <v>3254</v>
       </c>
-      <c r="D98" s="3">
-        <f t="shared" si="8"/>
+      <c r="D108" s="13">
+        <f t="shared" si="7"/>
         <v>163</v>
       </c>
-      <c r="E98" s="3">
+      <c r="E108" s="14">
         <v>101.37065972222229</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F108" s="14">
         <f t="shared" si="5"/>
         <v>61.629340277777715</v>
       </c>
-      <c r="G98" s="3">
+      <c r="G108" s="14">
         <f t="shared" si="6"/>
         <v>3315.6293402777778</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A109" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B99">
+      <c r="B109" s="10">
+        <f t="shared" si="7"/>
         <v>3449</v>
       </c>
-      <c r="C99" s="3">
-        <f t="shared" si="9"/>
+      <c r="C109" s="12">
+        <f t="shared" si="7"/>
         <v>3256.9583333333335</v>
       </c>
-      <c r="D99" s="3">
-        <f t="shared" si="8"/>
+      <c r="D109" s="13">
+        <f t="shared" si="7"/>
         <v>192.04166666666652</v>
       </c>
-      <c r="E99" s="3">
+      <c r="E109" s="14">
         <v>282.49565972222217</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F109" s="14">
         <f t="shared" si="5"/>
         <v>-90.453993055555657</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G109" s="14">
         <f t="shared" si="6"/>
         <v>3166.5043402777778</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A110" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B100">
+      <c r="B110" s="10">
+        <f t="shared" si="7"/>
         <v>3527</v>
       </c>
-      <c r="C100" s="3">
-        <f t="shared" si="9"/>
+      <c r="C110" s="12">
+        <f t="shared" si="7"/>
         <v>3256.7083333333335</v>
       </c>
-      <c r="D100" s="3">
-        <f t="shared" si="8"/>
+      <c r="D110" s="13">
+        <f t="shared" si="7"/>
         <v>270.29166666666652</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E110" s="14">
         <v>366.9435763888888</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F110" s="14">
         <f t="shared" si="5"/>
         <v>-96.651909722222285</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G110" s="14">
         <f t="shared" si="6"/>
         <v>3160.0564236111113</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A111" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B101">
+      <c r="B111" s="10">
+        <f t="shared" si="7"/>
         <v>3645</v>
       </c>
-      <c r="C101" s="3">
-        <f t="shared" si="9"/>
+      <c r="C111" s="12">
+        <f t="shared" si="7"/>
         <v>3269</v>
       </c>
-      <c r="D101" s="3">
-        <f t="shared" si="8"/>
+      <c r="D111" s="13">
+        <f t="shared" si="7"/>
         <v>376</v>
       </c>
-      <c r="E101" s="3">
+      <c r="E111" s="14">
         <v>326.52690972222217</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F111" s="14">
         <f t="shared" si="5"/>
         <v>49.473090277777828</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G111" s="14">
         <f t="shared" si="6"/>
         <v>3318.4730902777778</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A112" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B102">
+      <c r="B112" s="10">
+        <f t="shared" si="7"/>
         <v>3543</v>
       </c>
-      <c r="C102" s="3">
-        <f t="shared" si="9"/>
+      <c r="C112" s="12">
+        <f t="shared" si="7"/>
         <v>3279.0833333333335</v>
       </c>
-      <c r="D102" s="3">
-        <f t="shared" si="8"/>
+      <c r="D112" s="13">
+        <f t="shared" si="7"/>
         <v>263.91666666666652</v>
       </c>
-      <c r="E102" s="3">
+      <c r="E112" s="14">
         <v>323.65190972222217</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F112" s="14">
         <f t="shared" si="5"/>
         <v>-59.735243055555657</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G112" s="14">
         <f t="shared" si="6"/>
         <v>3219.3480902777778</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A113" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B103">
+      <c r="B113" s="10">
+        <f t="shared" ref="B113:D128" si="8">B36</f>
         <v>3506</v>
       </c>
-      <c r="C103" s="3">
-        <f t="shared" si="9"/>
+      <c r="C113" s="12">
+        <f t="shared" si="8"/>
         <v>3252.8333333333335</v>
       </c>
-      <c r="D103" s="3">
+      <c r="D113" s="13">
         <f t="shared" si="8"/>
         <v>253.16666666666652</v>
       </c>
-      <c r="E103" s="3">
+      <c r="E113" s="14">
         <v>367.17274305555554</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F113" s="14">
         <f t="shared" si="5"/>
         <v>-114.00607638888903</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G113" s="14">
         <f t="shared" si="6"/>
         <v>3138.8272569444443</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A114" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B104">
+      <c r="B114" s="10">
+        <f t="shared" si="8"/>
         <v>3274</v>
       </c>
-      <c r="C104" s="3">
-        <f t="shared" si="9"/>
+      <c r="C114" s="12">
+        <f t="shared" si="8"/>
         <v>3228.0416666666665</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D114" s="13">
         <f t="shared" si="8"/>
         <v>45.958333333333485</v>
       </c>
-      <c r="E104" s="3">
+      <c r="E114" s="14">
         <v>35.506076388889028</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F114" s="14">
         <f t="shared" si="5"/>
         <v>10.452256944444457</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G114" s="14">
         <f t="shared" si="6"/>
         <v>3238.4939236111109</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A115" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B105">
+      <c r="B115" s="10">
+        <f t="shared" si="8"/>
         <v>3228</v>
       </c>
-      <c r="C105" s="3">
-        <f t="shared" si="9"/>
+      <c r="C115" s="12">
+        <f t="shared" si="8"/>
         <v>3248.2083333333335</v>
       </c>
-      <c r="D105" s="3">
+      <c r="D115" s="13">
         <f t="shared" si="8"/>
         <v>-20.208333333333485</v>
       </c>
-      <c r="E105" s="3">
+      <c r="E115" s="14">
         <v>-62.754340277777828</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F115" s="14">
         <f t="shared" si="5"/>
         <v>42.546006944444343</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G115" s="14">
         <f t="shared" si="6"/>
         <v>3290.7543402777778</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1"/>
+      <c r="N115" s="1"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A116" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B106">
+      <c r="B116" s="10">
+        <f t="shared" si="8"/>
         <v>2895</v>
       </c>
-      <c r="C106" s="3">
-        <f t="shared" si="9"/>
+      <c r="C116" s="12">
+        <f t="shared" si="8"/>
         <v>3294.2916666666665</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D116" s="13">
         <f t="shared" si="8"/>
         <v>-399.29166666666652</v>
       </c>
-      <c r="E106" s="3" cm="1">
-        <f t="array" ref="E106:E117">TRANSPOSE(B$146:M$146)</f>
+      <c r="E116" s="14" cm="1">
+        <f t="array" ref="E116:E127">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F116" s="14">
         <f t="shared" si="5"/>
         <v>-54.068576388888687</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G116" s="14">
         <f t="shared" si="6"/>
         <v>3240.2230902777778</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A117" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B107">
+      <c r="B117" s="10">
+        <f t="shared" si="8"/>
         <v>2883</v>
       </c>
-      <c r="C107" s="3">
-        <f t="shared" si="9"/>
+      <c r="C117" s="12">
+        <f t="shared" si="8"/>
         <v>3340.3333333333335</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D117" s="13">
         <f t="shared" si="8"/>
         <v>-457.33333333333348</v>
       </c>
-      <c r="E107" s="3">
+      <c r="E117" s="14">
         <v>-690.77517361111109</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F117" s="14">
         <f t="shared" si="5"/>
         <v>233.4418402777776</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G117" s="14">
         <f t="shared" si="6"/>
         <v>3573.7751736111113</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A118" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B108">
+      <c r="B118" s="10">
+        <f t="shared" si="8"/>
         <v>2850</v>
       </c>
-      <c r="C108" s="3">
-        <f t="shared" si="9"/>
+      <c r="C118" s="12">
+        <f t="shared" si="8"/>
         <v>3384.6666666666665</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D118" s="13">
         <f t="shared" si="8"/>
         <v>-534.66666666666652</v>
       </c>
-      <c r="E108" s="3">
+      <c r="E118" s="14">
         <v>-365.34809027777783</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F118" s="14">
         <f t="shared" si="5"/>
         <v>-169.31857638888869</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G118" s="14">
         <f t="shared" si="6"/>
         <v>3215.3480902777778</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A119" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B109">
+      <c r="B119" s="10">
+        <f t="shared" si="8"/>
         <v>2555</v>
       </c>
-      <c r="C109" s="3">
-        <f t="shared" si="9"/>
+      <c r="C119" s="12">
+        <f t="shared" si="8"/>
         <v>3433.5416666666665</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D119" s="13">
         <f t="shared" si="8"/>
         <v>-878.54166666666652</v>
       </c>
-      <c r="E109" s="3">
+      <c r="E119" s="14">
         <v>-339.5668402777776</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F119" s="14">
         <f t="shared" si="5"/>
         <v>-538.97482638888891</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G119" s="14">
         <f t="shared" si="6"/>
         <v>2894.5668402777774</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A120" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B110">
+      <c r="B120" s="10">
+        <f t="shared" si="8"/>
         <v>3346</v>
       </c>
-      <c r="C110" s="3">
-        <f t="shared" si="9"/>
+      <c r="C120" s="12">
+        <f t="shared" si="8"/>
         <v>3481.2916666666665</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D120" s="13">
         <f t="shared" si="8"/>
         <v>-135.29166666666652</v>
       </c>
-      <c r="E110" s="3">
+      <c r="E120" s="14">
         <v>101.37065972222229</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F120" s="14">
         <f t="shared" si="5"/>
         <v>-236.6623263888888</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G120" s="14">
         <f t="shared" si="6"/>
         <v>3244.6293402777778</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A121" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B111">
+      <c r="B121" s="10">
+        <f t="shared" si="8"/>
         <v>4004</v>
       </c>
-      <c r="C111" s="3">
-        <f t="shared" si="9"/>
+      <c r="C121" s="12">
+        <f t="shared" si="8"/>
         <v>3514.8333333333335</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D121" s="13">
         <f t="shared" si="8"/>
         <v>489.16666666666652</v>
       </c>
-      <c r="E111" s="3">
+      <c r="E121" s="14">
         <v>282.49565972222217</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F121" s="14">
         <f t="shared" si="5"/>
         <v>206.67100694444434</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G121" s="14">
         <f t="shared" si="6"/>
         <v>3721.5043402777778</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A122" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B112">
+      <c r="B122" s="10">
+        <f t="shared" si="8"/>
         <v>4078</v>
       </c>
-      <c r="C112" s="3">
-        <f t="shared" si="9"/>
+      <c r="C122" s="12">
+        <f t="shared" si="8"/>
         <v>3549.875</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D122" s="13">
         <f t="shared" si="8"/>
         <v>528.125</v>
       </c>
-      <c r="E112" s="3">
+      <c r="E122" s="14">
         <v>366.9435763888888</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F122" s="14">
         <f t="shared" si="5"/>
         <v>161.1814236111112</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G122" s="14">
         <f t="shared" si="6"/>
         <v>3711.0564236111113</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A123" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B113">
+      <c r="B123" s="10">
+        <f t="shared" si="8"/>
         <v>4199</v>
       </c>
-      <c r="C113" s="3">
-        <f t="shared" si="9"/>
+      <c r="C123" s="12">
+        <f t="shared" si="8"/>
         <v>3567.7083333333335</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D123" s="13">
         <f t="shared" si="8"/>
         <v>631.29166666666652</v>
       </c>
-      <c r="E113" s="3">
+      <c r="E123" s="14">
         <v>326.52690972222217</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F123" s="14">
         <f t="shared" si="5"/>
         <v>304.76475694444434</v>
       </c>
-      <c r="G113" s="3">
+      <c r="G123" s="14">
         <f t="shared" si="6"/>
         <v>3872.4730902777778</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A124" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B114">
+      <c r="B124" s="10">
+        <f t="shared" si="8"/>
         <v>4053</v>
       </c>
-      <c r="C114" s="3">
-        <f t="shared" si="9"/>
+      <c r="C124" s="12">
+        <f t="shared" si="8"/>
         <v>3590.6666666666665</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D124" s="13">
         <f t="shared" si="8"/>
         <v>462.33333333333348</v>
       </c>
-      <c r="E114" s="3">
+      <c r="E124" s="14">
         <v>323.65190972222217</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F124" s="14">
         <f t="shared" si="5"/>
         <v>138.68142361111131</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G124" s="14">
         <f t="shared" si="6"/>
         <v>3729.3480902777778</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A125" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B115">
+      <c r="B125" s="10">
+        <f t="shared" si="8"/>
         <v>4169</v>
       </c>
-      <c r="C115" s="3">
-        <f t="shared" si="9"/>
+      <c r="C125" s="12">
+        <f t="shared" si="8"/>
         <v>3672.125</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D125" s="13">
         <f t="shared" si="8"/>
         <v>496.875</v>
       </c>
-      <c r="E115" s="3">
+      <c r="E125" s="14">
         <v>367.17274305555554</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F125" s="14">
         <f t="shared" si="5"/>
         <v>129.70225694444446</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G125" s="14">
         <f t="shared" si="6"/>
         <v>3801.8272569444443</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A126" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B116">
+      <c r="B126" s="10">
+        <f t="shared" si="8"/>
         <v>3757</v>
       </c>
-      <c r="C116" s="3">
-        <f t="shared" si="9"/>
+      <c r="C126" s="12">
+        <f t="shared" si="8"/>
         <v>3758.1666666666665</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D126" s="13">
         <f t="shared" si="8"/>
         <v>-1.1666666666665151</v>
       </c>
-      <c r="E116" s="3">
+      <c r="E126" s="14">
         <v>35.506076388889028</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F126" s="14">
         <f t="shared" si="5"/>
         <v>-36.672743055555543</v>
       </c>
-      <c r="G116" s="3">
+      <c r="G126" s="14">
         <f t="shared" si="6"/>
         <v>3721.4939236111109</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A127" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B117">
+      <c r="B127" s="10">
+        <f t="shared" si="8"/>
         <v>3550</v>
       </c>
-      <c r="C117" s="3">
-        <f t="shared" si="9"/>
+      <c r="C127" s="12">
+        <f t="shared" si="8"/>
         <v>3793.7916666666665</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D127" s="13">
         <f t="shared" si="8"/>
         <v>-243.79166666666652</v>
       </c>
-      <c r="E117" s="3">
+      <c r="E127" s="14">
         <v>-62.754340277777828</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F127" s="14">
         <f t="shared" si="5"/>
         <v>-181.03732638888869</v>
       </c>
-      <c r="G117" s="3">
+      <c r="G127" s="14">
         <f t="shared" si="6"/>
         <v>3612.7543402777778</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A128" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B118">
+      <c r="B128" s="10">
+        <f t="shared" si="8"/>
         <v>3414</v>
       </c>
-      <c r="C118" s="3">
-        <f t="shared" si="9"/>
+      <c r="C128" s="12">
+        <f t="shared" si="8"/>
         <v>3804.8333333333335</v>
       </c>
-      <c r="D118" s="3">
+      <c r="D128" s="13">
         <f t="shared" si="8"/>
         <v>-390.83333333333348</v>
       </c>
-      <c r="E118" s="3" cm="1">
-        <f t="array" ref="E118:E129">TRANSPOSE(B$146:M$146)</f>
+      <c r="E128" s="14" cm="1">
+        <f t="array" ref="E128:E139">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F128" s="14">
         <f t="shared" si="5"/>
         <v>-45.610243055555657</v>
       </c>
-      <c r="G118" s="3">
+      <c r="G128" s="14">
         <f t="shared" si="6"/>
         <v>3759.2230902777778</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B119">
+      <c r="B129" s="10">
+        <f t="shared" ref="B129:D139" si="9">B52</f>
         <v>2792</v>
       </c>
-      <c r="C119" s="3">
+      <c r="C129" s="12">
         <f t="shared" si="9"/>
         <v>3816.625</v>
       </c>
-      <c r="D119" s="3">
-        <f t="shared" si="8"/>
+      <c r="D129" s="13">
+        <f t="shared" si="9"/>
         <v>-1024.625</v>
       </c>
-      <c r="E119" s="3">
+      <c r="E129" s="14">
         <v>-690.77517361111109</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F129" s="14">
         <f t="shared" si="5"/>
         <v>-333.84982638888891</v>
       </c>
-      <c r="G119" s="3">
+      <c r="G129" s="14">
         <f t="shared" si="6"/>
         <v>3482.7751736111113</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A130" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B120">
+      <c r="B130" s="10">
+        <f t="shared" si="9"/>
         <v>3492</v>
       </c>
-      <c r="C120" s="3">
+      <c r="C130" s="12">
         <f t="shared" si="9"/>
         <v>3830.9583333333335</v>
       </c>
-      <c r="D120" s="3">
-        <f t="shared" si="8"/>
+      <c r="D130" s="13">
+        <f t="shared" si="9"/>
         <v>-338.95833333333348</v>
       </c>
-      <c r="E120" s="3">
+      <c r="E130" s="14">
         <v>-365.34809027777783</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F130" s="14">
         <f t="shared" si="5"/>
         <v>26.389756944444343</v>
       </c>
-      <c r="G120" s="3">
+      <c r="G130" s="14">
         <f t="shared" si="6"/>
         <v>3857.3480902777778</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A131" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B121">
+      <c r="B131" s="10">
+        <f t="shared" si="9"/>
         <v>3868</v>
       </c>
-      <c r="C121" s="3">
+      <c r="C131" s="12">
         <f t="shared" si="9"/>
         <v>3853.2916666666665</v>
       </c>
-      <c r="D121" s="3">
-        <f t="shared" si="8"/>
+      <c r="D131" s="13">
+        <f t="shared" si="9"/>
         <v>14.708333333333485</v>
       </c>
-      <c r="E121" s="3">
+      <c r="E131" s="14">
         <v>-339.5668402777776</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F131" s="14">
         <f t="shared" si="5"/>
         <v>354.27517361111109</v>
       </c>
-      <c r="G121" s="3">
+      <c r="G131" s="14">
         <f t="shared" si="6"/>
         <v>4207.5668402777774</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B122">
+      <c r="B132" s="10">
+        <f t="shared" si="9"/>
         <v>4098</v>
       </c>
-      <c r="C122" s="3">
+      <c r="C132" s="12">
         <f t="shared" si="9"/>
         <v>3875.5</v>
       </c>
-      <c r="D122" s="3">
-        <f t="shared" si="8"/>
+      <c r="D132" s="13">
+        <f t="shared" si="9"/>
         <v>222.5</v>
       </c>
-      <c r="E122" s="3">
+      <c r="E132" s="14">
         <v>101.37065972222229</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F132" s="14">
         <f t="shared" si="5"/>
         <v>121.12934027777771</v>
       </c>
-      <c r="G122" s="3">
+      <c r="G132" s="14">
         <f t="shared" si="6"/>
         <v>3996.6293402777778</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A133" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B123">
+      <c r="B133" s="10">
+        <f t="shared" si="9"/>
         <v>4107</v>
       </c>
-      <c r="C123" s="3">
+      <c r="C133" s="12">
         <f t="shared" si="9"/>
         <v>3899.8333333333335</v>
       </c>
-      <c r="D123" s="3">
-        <f t="shared" si="8"/>
+      <c r="D133" s="13">
+        <f t="shared" si="9"/>
         <v>207.16666666666652</v>
       </c>
-      <c r="E123" s="3">
+      <c r="E133" s="14">
         <v>282.49565972222217</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F133" s="14">
         <f t="shared" si="5"/>
         <v>-75.328993055555657</v>
       </c>
-      <c r="G123" s="3">
+      <c r="G133" s="14">
         <f t="shared" si="6"/>
         <v>3824.5043402777778</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A134" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B124">
+      <c r="B134" s="10">
+        <f t="shared" si="9"/>
         <v>4240</v>
       </c>
-      <c r="C124" t="str">
+      <c r="C134" s="10" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D124" t="str">
-        <f t="shared" si="8"/>
+      <c r="D134" s="11" t="str">
+        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="E124" s="3">
+      <c r="E134" s="14">
         <v>366.9435763888888</v>
       </c>
-      <c r="F124" t="str">
+      <c r="F134" s="14" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G124" s="3">
+      <c r="G134" s="14">
         <f t="shared" si="6"/>
         <v>3873.0564236111113</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B125">
+      <c r="B135" s="10">
+        <f t="shared" si="9"/>
         <v>4320</v>
       </c>
-      <c r="C125" t="str">
+      <c r="C135" s="10" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D125" t="str">
-        <f t="shared" si="8"/>
+      <c r="D135" s="11" t="str">
+        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="E125" s="3">
+      <c r="E135" s="14">
         <v>326.52690972222217</v>
       </c>
-      <c r="F125" t="str">
+      <c r="F135" s="14" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G125" s="3">
+      <c r="G135" s="14">
         <f t="shared" si="6"/>
         <v>3993.4730902777778</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B126">
+      <c r="B136" s="10">
+        <f t="shared" si="9"/>
         <v>4276</v>
       </c>
-      <c r="C126" t="str">
+      <c r="C136" s="10" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D126" t="str">
-        <f t="shared" si="8"/>
+      <c r="D136" s="11" t="str">
+        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="E126" s="3">
+      <c r="E136" s="14">
         <v>323.65190972222217</v>
       </c>
-      <c r="F126" t="str">
+      <c r="F136" s="14" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G126" s="3">
+      <c r="G136" s="14">
         <f t="shared" si="6"/>
         <v>3952.3480902777778</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B127">
+      <c r="B137" s="10">
+        <f t="shared" si="9"/>
         <v>4482</v>
       </c>
-      <c r="C127" t="str">
+      <c r="C137" s="10" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D127" t="str">
-        <f t="shared" si="8"/>
+      <c r="D137" s="11" t="str">
+        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="E127" s="3">
+      <c r="E137" s="14">
         <v>367.17274305555554</v>
       </c>
-      <c r="F127" t="str">
+      <c r="F137" s="14" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G127" s="3">
+      <c r="G137" s="14">
         <f t="shared" si="6"/>
         <v>4114.8272569444443</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A138" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B128">
+      <c r="B138" s="10">
+        <f t="shared" si="9"/>
         <v>3977</v>
       </c>
-      <c r="C128" t="str">
+      <c r="C138" s="10" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D128" t="str">
-        <f t="shared" si="8"/>
+      <c r="D138" s="11" t="str">
+        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="E128" s="3">
+      <c r="E138" s="14">
         <v>35.506076388889028</v>
       </c>
-      <c r="F128" t="str">
+      <c r="F138" s="14" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G128" s="3">
+      <c r="G138" s="14">
         <f t="shared" si="6"/>
         <v>3941.4939236111109</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A139" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B129">
+      <c r="B139" s="16">
+        <f t="shared" si="9"/>
         <v>3914</v>
       </c>
-      <c r="C129" t="str">
+      <c r="C139" s="16" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D129" t="str">
-        <f t="shared" si="8"/>
+      <c r="D139" s="40" t="str">
+        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="E129" s="3">
+      <c r="E139" s="14">
         <v>-62.754340277777828</v>
       </c>
-      <c r="F129" t="str">
+      <c r="F139" s="14" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G129" s="3">
+      <c r="G139" s="14">
         <f t="shared" si="6"/>
         <v>3976.7543402777778</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B130" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B131" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B132" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B133" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B134" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B135" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>65</v>
-      </c>
-      <c r="B139" t="s">
-        <v>66</v>
-      </c>
-      <c r="C139" t="s">
-        <v>67</v>
-      </c>
-      <c r="D139" t="s">
-        <v>68</v>
-      </c>
-      <c r="E139" t="s">
-        <v>69</v>
-      </c>
-      <c r="F139" t="s">
-        <v>70</v>
-      </c>
-      <c r="G139" t="s">
-        <v>71</v>
-      </c>
-      <c r="H139" t="s">
-        <v>72</v>
-      </c>
-      <c r="I139" t="s">
-        <v>73</v>
-      </c>
-      <c r="J139" t="s">
-        <v>74</v>
-      </c>
-      <c r="K139" t="s">
-        <v>75</v>
-      </c>
-      <c r="L139" t="s">
-        <v>76</v>
-      </c>
-      <c r="M139" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A140">
-        <v>2017</v>
-      </c>
-      <c r="B140" t="str" cm="1">
-        <f t="array" ref="B140:M140">TRANSPOSE(D70:D81)</f>
-        <v>NA</v>
-      </c>
-      <c r="C140" t="str">
-        <v>NA</v>
-      </c>
-      <c r="D140" t="str">
-        <v>NA</v>
-      </c>
-      <c r="E140" t="str">
-        <v>NA</v>
-      </c>
-      <c r="F140" t="str">
-        <v>NA</v>
-      </c>
-      <c r="G140" t="str">
-        <v>NA</v>
-      </c>
-      <c r="H140" s="3">
-        <v>378.41666666666652</v>
-      </c>
-      <c r="I140" s="3">
-        <v>59</v>
-      </c>
-      <c r="J140" s="3">
-        <v>228.79166666666652</v>
-      </c>
-      <c r="K140" s="3">
-        <v>302.79166666666652</v>
-      </c>
-      <c r="L140" s="3">
-        <v>91.458333333333485</v>
-      </c>
-      <c r="M140" s="3">
-        <v>72.416666666666515</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A141">
-        <v>2018</v>
-      </c>
-      <c r="B141" s="3" cm="1">
-        <f t="array" ref="B141:M141">TRANSPOSE(D82:D93)</f>
-        <v>-302.08333333333348</v>
-      </c>
-      <c r="C141" s="3">
-        <v>-574.04166666666652</v>
-      </c>
-      <c r="D141" s="3">
-        <v>-296.70833333333348</v>
-      </c>
-      <c r="E141" s="3">
-        <v>-334.16666666666652</v>
-      </c>
-      <c r="F141" s="3">
-        <v>135.25</v>
-      </c>
-      <c r="G141" s="3">
-        <v>221.58333333333348</v>
-      </c>
-      <c r="H141" s="3">
-        <v>270.91666666666652</v>
-      </c>
-      <c r="I141" s="3">
-        <v>219.79166666666652</v>
-      </c>
-      <c r="J141" s="3">
-        <v>319.54166666666652</v>
-      </c>
-      <c r="K141" s="3">
-        <v>395.83333333333348</v>
-      </c>
-      <c r="L141" s="3">
-        <v>-14.25</v>
-      </c>
-      <c r="M141" s="3">
-        <v>-79.458333333333485</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A142">
-        <v>2019</v>
-      </c>
-      <c r="B142" s="3" cm="1">
-        <f t="array" ref="B142:M142">TRANSPOSE(D94:D105)</f>
-        <v>-308.70833333333348</v>
-      </c>
-      <c r="C142" s="3">
-        <v>-727.125</v>
-      </c>
-      <c r="D142" s="3">
-        <v>-311.08333333333348</v>
-      </c>
-      <c r="E142" s="3">
-        <v>-180.29166666666652</v>
-      </c>
-      <c r="F142" s="3">
-        <v>163</v>
-      </c>
-      <c r="G142" s="3">
-        <v>192.04166666666652</v>
-      </c>
-      <c r="H142" s="3">
-        <v>270.29166666666652</v>
-      </c>
-      <c r="I142" s="3">
-        <v>376</v>
-      </c>
-      <c r="J142" s="3">
-        <v>263.91666666666652</v>
-      </c>
-      <c r="K142" s="3">
-        <v>253.16666666666652</v>
-      </c>
-      <c r="L142" s="3">
-        <v>45.958333333333485</v>
-      </c>
-      <c r="M142" s="3">
-        <v>-20.208333333333485</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A143">
-        <v>2020</v>
-      </c>
-      <c r="B143" s="3" cm="1">
-        <f t="array" ref="B143:M143">TRANSPOSE(D106:D117)</f>
-        <v>-399.29166666666652</v>
-      </c>
-      <c r="C143" s="3">
-        <v>-457.33333333333348</v>
-      </c>
-      <c r="D143" s="3">
-        <v>-534.66666666666652</v>
-      </c>
-      <c r="E143" s="3">
-        <v>-878.54166666666652</v>
-      </c>
-      <c r="F143" s="3">
-        <v>-135.29166666666652</v>
-      </c>
-      <c r="G143" s="3">
-        <v>489.16666666666652</v>
-      </c>
-      <c r="H143" s="3">
-        <v>528.125</v>
-      </c>
-      <c r="I143" s="3">
-        <v>631.29166666666652</v>
-      </c>
-      <c r="J143" s="3">
-        <v>462.33333333333348</v>
-      </c>
-      <c r="K143" s="3">
-        <v>496.875</v>
-      </c>
-      <c r="L143" s="3">
-        <v>-1.1666666666665151</v>
-      </c>
-      <c r="M143" s="3">
-        <v>-243.79166666666652</v>
-      </c>
-      <c r="N143" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A144">
-        <v>2021</v>
-      </c>
-      <c r="B144" s="3" cm="1">
-        <f t="array" ref="B144:M144">TRANSPOSE(D118:D129)</f>
-        <v>-390.83333333333348</v>
-      </c>
-      <c r="C144" s="3">
-        <v>-1024.625</v>
-      </c>
-      <c r="D144" s="3">
-        <v>-338.95833333333348</v>
-      </c>
-      <c r="E144" s="3">
-        <v>14.708333333333485</v>
-      </c>
-      <c r="F144" s="3">
-        <v>222.5</v>
-      </c>
-      <c r="G144" s="3">
-        <v>207.16666666666652</v>
-      </c>
-      <c r="H144" t="str">
-        <v>NA</v>
-      </c>
-      <c r="I144" t="str">
-        <v>NA</v>
-      </c>
-      <c r="J144" t="str">
-        <v>NA</v>
-      </c>
-      <c r="K144" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L144" t="str">
-        <v>NA</v>
-      </c>
-      <c r="M144" t="str">
-        <v>NA</v>
-      </c>
-      <c r="N144" s="7"/>
-    </row>
-    <row r="145" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B145" s="3">
-        <f>AVERAGE(B140:B144)</f>
-        <v>-350.22916666666674</v>
-      </c>
-      <c r="C145" s="3">
-        <f>AVERAGE(C140:C144)</f>
-        <v>-695.78125</v>
-      </c>
-      <c r="D145" s="3">
-        <f>AVERAGE(D140:D144)</f>
-        <v>-370.35416666666674</v>
-      </c>
-      <c r="E145" s="3">
-        <f t="shared" ref="E145:M145" si="10">AVERAGE(E140:E144)</f>
-        <v>-344.57291666666652</v>
-      </c>
-      <c r="F145" s="3">
-        <f t="shared" si="10"/>
-        <v>96.364583333333371</v>
-      </c>
-      <c r="G145" s="3">
-        <f t="shared" si="10"/>
-        <v>277.48958333333326</v>
-      </c>
-      <c r="H145" s="3">
-        <f t="shared" si="10"/>
-        <v>361.93749999999989</v>
-      </c>
-      <c r="I145" s="3">
-        <f t="shared" si="10"/>
-        <v>321.52083333333326</v>
-      </c>
-      <c r="J145" s="3">
-        <f t="shared" si="10"/>
-        <v>318.64583333333326</v>
-      </c>
-      <c r="K145" s="3">
-        <f t="shared" si="10"/>
-        <v>362.16666666666663</v>
-      </c>
-      <c r="L145" s="3">
-        <f t="shared" si="10"/>
-        <v>30.500000000000114</v>
-      </c>
-      <c r="M145" s="3">
-        <f t="shared" si="10"/>
-        <v>-67.760416666666742</v>
-      </c>
-      <c r="N145" s="5">
-        <f>AVERAGE(B145:M145)</f>
-        <v>-5.0060763888889142</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B146" s="3">
-        <f>B145-$N145</f>
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="C146" s="3">
-        <f t="shared" ref="C146:M146" si="11">C145-$N145</f>
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="D146" s="3">
-        <f t="shared" si="11"/>
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="E146" s="3">
-        <f t="shared" si="11"/>
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F146" s="3">
-        <f t="shared" si="11"/>
-        <v>101.37065972222229</v>
-      </c>
-      <c r="G146" s="3">
-        <f t="shared" si="11"/>
-        <v>282.49565972222217</v>
-      </c>
-      <c r="H146" s="3">
-        <f t="shared" si="11"/>
-        <v>366.9435763888888</v>
-      </c>
-      <c r="I146" s="3">
-        <f t="shared" si="11"/>
-        <v>326.52690972222217</v>
-      </c>
-      <c r="J146" s="3">
-        <f t="shared" si="11"/>
-        <v>323.65190972222217</v>
-      </c>
-      <c r="K146" s="3">
-        <f t="shared" si="11"/>
-        <v>367.17274305555554</v>
-      </c>
-      <c r="L146" s="3">
-        <f t="shared" si="11"/>
-        <v>35.506076388889028</v>
-      </c>
-      <c r="M146" s="3">
-        <f t="shared" si="11"/>
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="N146" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="N143:N144"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A66:M66"/>
+    <mergeCell ref="N71:N72"/>
+    <mergeCell ref="A78:G78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -5733,24 +6848,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5767,29 +6890,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/handouts/chapter_1_4_handout_key.xlsx
+++ b/docs/handouts/chapter_1_4_handout_key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A4EEFC-9D73-4E88-9FF3-34808BE5D8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BF4CA8-18C5-43EE-9812-55BD45BEF5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17745" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -435,7 +435,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -601,33 +601,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -660,12 +640,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -677,12 +651,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -692,15 +660,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -713,8 +672,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -743,8 +729,8 @@
       <xdr:rowOff>205613</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -823,7 +809,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -888,8 +874,8 @@
       <xdr:rowOff>137033</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187167" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -961,7 +947,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1026,8 +1012,8 @@
       <xdr:rowOff>137033</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -1099,7 +1085,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -1164,8 +1150,8 @@
       <xdr:rowOff>110490</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -1237,7 +1223,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -1302,8 +1288,8 @@
       <xdr:rowOff>205613</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -1382,7 +1368,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -1502,8 +1488,8 @@
       <xdr:rowOff>129413</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -1582,7 +1568,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -1647,8 +1633,8 @@
       <xdr:rowOff>83693</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187167" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -1720,7 +1706,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -1785,8 +1771,8 @@
       <xdr:rowOff>83693</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -1858,7 +1844,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -1978,8 +1964,8 @@
       <xdr:rowOff>153670</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -2028,7 +2014,7 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2070,7 +2056,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -2135,8 +2121,8 @@
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="231923"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -2195,7 +2181,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -2239,7 +2225,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -2310,8 +2296,8 @@
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="379575" cy="250903"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -2353,7 +2339,6 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:acc>
@@ -2369,7 +2354,7 @@
                       <m:sSub>
                         <m:sSubPr>
                           <m:ctrlPr>
-                            <a:rPr lang="en-US" sz="1400" i="1">
+                            <a:rPr lang="en-US" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                           </m:ctrlPr>
@@ -2415,7 +2400,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -2489,8 +2474,8 @@
       <xdr:rowOff>77470</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -2569,7 +2554,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -2634,8 +2619,8 @@
       <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -2696,7 +2681,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -2762,8 +2747,8 @@
       <xdr:rowOff>197993</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187167" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -2835,7 +2820,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -2900,8 +2885,8 @@
       <xdr:rowOff>388493</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -2973,7 +2958,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -3038,8 +3023,8 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="TextBox 18">
@@ -3088,7 +3073,7 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -3130,7 +3115,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="TextBox 18">
@@ -3518,960 +3503,960 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>3034</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>2748</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>3164</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>3238</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>3416</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>3492</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>3730</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="9">
         <f>(0.5*B3+SUM(B4:B14)+0.5*B15)/12</f>
         <v>3351.5833333333335</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="10">
         <v>378.41666666666652</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>3409</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="9">
         <f t="shared" ref="C10:C56" si="0">(0.5*B4+SUM(B5:B15)+0.5*B16)/12</f>
         <v>3350</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="11">
         <f>IFERROR(B10-C10, "NA")</f>
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>3572</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="9">
         <f t="shared" si="0"/>
         <v>3343.2083333333335</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="11">
         <f t="shared" ref="D11:D62" si="1">IFERROR(B11-C11, "NA")</f>
         <v>228.79166666666652</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>3629</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="9">
         <f t="shared" si="0"/>
         <v>3326.2083333333335</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="11">
         <f t="shared" si="1"/>
         <v>302.79166666666652</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>3408</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="9">
         <f t="shared" si="0"/>
         <v>3316.5416666666665</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="11">
         <f t="shared" si="1"/>
         <v>91.458333333333485</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>3391</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="9">
         <f t="shared" si="0"/>
         <v>3318.5833333333335</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="11">
         <f t="shared" si="1"/>
         <v>72.416666666666515</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>3010</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="9">
         <f t="shared" si="0"/>
         <v>3312.0833333333335</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="11">
         <f t="shared" si="1"/>
         <v>-302.08333333333348</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>2734</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="9">
         <f t="shared" si="0"/>
         <v>3308.0416666666665</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="11">
         <f t="shared" si="1"/>
         <v>-574.04166666666652</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>3015</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="9">
         <f t="shared" si="0"/>
         <v>3311.7083333333335</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="11">
         <f t="shared" si="1"/>
         <v>-296.70833333333348</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>2979</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="9">
         <f t="shared" si="0"/>
         <v>3313.1666666666665</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="11">
         <f t="shared" si="1"/>
         <v>-334.16666666666652</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>3443</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="9">
         <f t="shared" si="0"/>
         <v>3307.75</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="11">
         <f t="shared" si="1"/>
         <v>135.25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>3514</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="9">
         <f t="shared" si="0"/>
         <v>3292.4166666666665</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="11">
         <f t="shared" si="1"/>
         <v>221.58333333333348</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>3552</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="9">
         <f t="shared" si="0"/>
         <v>3281.0833333333335</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="11">
         <f t="shared" si="1"/>
         <v>270.91666666666652</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>3490</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="9">
         <f t="shared" si="0"/>
         <v>3270.2083333333335</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="11">
         <f t="shared" si="1"/>
         <v>219.79166666666652</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>3579</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="9">
         <f t="shared" si="0"/>
         <v>3259.4583333333335</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="11">
         <f t="shared" si="1"/>
         <v>319.54166666666652</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>3657</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="9">
         <f t="shared" si="0"/>
         <v>3261.1666666666665</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="11">
         <f t="shared" si="1"/>
         <v>395.83333333333348</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>3250</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="9">
         <f t="shared" si="0"/>
         <v>3264.25</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="11">
         <f t="shared" si="1"/>
         <v>-14.25</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="7">
         <v>3181</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="9">
         <f t="shared" si="0"/>
         <v>3260.4583333333335</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="11">
         <f t="shared" si="1"/>
         <v>-79.458333333333485</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="7">
         <v>2948</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="9">
         <f t="shared" si="0"/>
         <v>3256.7083333333335</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="11">
         <f t="shared" si="1"/>
         <v>-308.70833333333348</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="7">
         <v>2535</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="9">
         <f t="shared" si="0"/>
         <v>3262.125</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="11">
         <f t="shared" si="1"/>
         <v>-727.125</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="7">
         <v>2956</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="9">
         <f t="shared" si="0"/>
         <v>3267.0833333333335</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="11">
         <f t="shared" si="1"/>
         <v>-311.08333333333348</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="7">
         <v>3079</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="9">
         <f t="shared" si="0"/>
         <v>3259.2916666666665</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="11">
         <f t="shared" si="1"/>
         <v>-180.29166666666652</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="7">
         <v>3417</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="9">
         <f t="shared" si="0"/>
         <v>3254</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="11">
         <f t="shared" si="1"/>
         <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="7">
         <v>3449</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="9">
         <f t="shared" si="0"/>
         <v>3256.9583333333335</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="11">
         <f t="shared" si="1"/>
         <v>192.04166666666652</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="7">
         <v>3527</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="9">
         <f t="shared" si="0"/>
         <v>3256.7083333333335</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="11">
         <f t="shared" si="1"/>
         <v>270.29166666666652</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="7">
         <v>3645</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="9">
         <f t="shared" si="0"/>
         <v>3269</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="11">
         <f t="shared" si="1"/>
         <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="7">
         <v>3543</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="9">
         <f t="shared" si="0"/>
         <v>3279.0833333333335</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="11">
         <f t="shared" si="1"/>
         <v>263.91666666666652</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="7">
         <v>3506</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="9">
         <f t="shared" si="0"/>
         <v>3252.8333333333335</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="11">
         <f t="shared" si="1"/>
         <v>253.16666666666652</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="7">
         <v>3274</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="9">
         <f t="shared" si="0"/>
         <v>3228.0416666666665</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="11">
         <f t="shared" si="1"/>
         <v>45.958333333333485</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="7">
         <v>3228</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="9">
         <f t="shared" si="0"/>
         <v>3248.2083333333335</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="11">
         <f t="shared" si="1"/>
         <v>-20.208333333333485</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="7">
         <v>2895</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="9">
         <f t="shared" si="0"/>
         <v>3294.2916666666665</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="11">
         <f t="shared" si="1"/>
         <v>-399.29166666666652</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="7">
         <v>2883</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="9">
         <f t="shared" si="0"/>
         <v>3340.3333333333335</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="11">
         <f t="shared" si="1"/>
         <v>-457.33333333333348</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="7">
         <v>2850</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="9">
         <f t="shared" si="0"/>
         <v>3384.6666666666665</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="11">
         <f t="shared" si="1"/>
         <v>-534.66666666666652</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="7">
         <v>2555</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="9">
         <f t="shared" si="0"/>
         <v>3433.5416666666665</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="11">
         <f t="shared" si="1"/>
         <v>-878.54166666666652</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="7">
         <v>3346</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="9">
         <f t="shared" si="0"/>
         <v>3481.2916666666665</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="11">
         <f t="shared" si="1"/>
         <v>-135.29166666666652</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="7">
         <v>4004</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="9">
         <f t="shared" si="0"/>
         <v>3514.8333333333335</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="11">
         <f t="shared" si="1"/>
         <v>489.16666666666652</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="7">
         <v>4078</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="9">
         <f t="shared" si="0"/>
         <v>3549.875</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="11">
         <f t="shared" si="1"/>
         <v>528.125</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="7">
         <v>4199</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="9">
         <f t="shared" si="0"/>
         <v>3567.7083333333335</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="11">
         <f t="shared" si="1"/>
         <v>631.29166666666652</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="7">
         <v>4053</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="9">
         <f t="shared" si="0"/>
         <v>3590.6666666666665</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="11">
         <f t="shared" si="1"/>
         <v>462.33333333333348</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="7">
         <v>4169</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="9">
         <f t="shared" si="0"/>
         <v>3672.125</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="11">
         <f t="shared" si="1"/>
         <v>496.875</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="7">
         <v>3757</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="9">
         <f t="shared" si="0"/>
         <v>3758.1666666666665</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D49" s="11">
         <f t="shared" si="1"/>
         <v>-1.1666666666665151</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="7">
         <v>3550</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="9">
         <f t="shared" si="0"/>
         <v>3793.7916666666665</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="11">
         <f t="shared" si="1"/>
         <v>-243.79166666666652</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="7">
         <v>3414</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="9">
         <f t="shared" si="0"/>
         <v>3804.8333333333335</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D51" s="11">
         <f t="shared" si="1"/>
         <v>-390.83333333333348</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="7">
         <v>2792</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="9">
         <f t="shared" si="0"/>
         <v>3816.625</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="11">
         <f t="shared" si="1"/>
         <v>-1024.625</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="7">
         <v>3492</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="9">
         <f t="shared" si="0"/>
         <v>3830.9583333333335</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D53" s="11">
         <f t="shared" si="1"/>
         <v>-338.95833333333348</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="7">
         <v>3868</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="9">
         <f t="shared" si="0"/>
         <v>3853.2916666666665</v>
       </c>
-      <c r="D54" s="14">
+      <c r="D54" s="11">
         <f t="shared" si="1"/>
         <v>14.708333333333485</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="7">
         <v>4098</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="9">
         <f t="shared" si="0"/>
         <v>3875.5</v>
       </c>
-      <c r="D55" s="14">
+      <c r="D55" s="11">
         <f t="shared" si="1"/>
         <v>222.5</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="7">
         <v>4107</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="9">
         <f t="shared" si="0"/>
         <v>3899.8333333333335</v>
       </c>
-      <c r="D56" s="14">
+      <c r="D56" s="11">
         <f t="shared" si="1"/>
         <v>207.16666666666652</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="7">
         <v>4240</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D57" s="14" t="str">
+      <c r="D57" s="11" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="7">
         <v>4320</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="14" t="str">
+      <c r="D58" s="11" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="7">
         <v>4276</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D59" s="14" t="str">
+      <c r="D59" s="11" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="7">
         <v>4482</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D60" s="14" t="str">
+      <c r="D60" s="11" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="7">
         <v>3977</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D61" s="14" t="str">
+      <c r="D61" s="11" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="13">
         <v>3914</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D62" s="14" t="str">
+      <c r="D62" s="11" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
@@ -4487,1260 +4472,1260 @@
       </c>
     </row>
     <row r="66" spans="1:14" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="17" t="s">
+      <c r="A66" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-      <c r="N66" s="19"/>
+      <c r="B66" s="34"/>
+      <c r="C66" s="34"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="34"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="34"/>
+      <c r="K66" s="34"/>
+      <c r="L66" s="34"/>
+      <c r="M66" s="34"/>
+      <c r="N66" s="14"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B67" s="21" t="s">
+      <c r="B67" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C67" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E67" s="21" t="s">
+      <c r="E67" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F67" s="21" t="s">
+      <c r="F67" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G67" s="21" t="s">
+      <c r="G67" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H67" s="21" t="s">
+      <c r="H67" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="I67" s="21" t="s">
+      <c r="I67" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="J67" s="21" t="s">
+      <c r="J67" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="K67" s="21" t="s">
+      <c r="K67" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L67" s="21" t="s">
+      <c r="L67" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="M67" s="22" t="s">
+      <c r="M67" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="N67" s="23"/>
+      <c r="N67" s="18"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="24">
+      <c r="A68" s="19">
         <v>2017</v>
       </c>
-      <c r="B68" s="10" t="str" cm="1">
+      <c r="B68" s="7" t="str" cm="1">
         <f t="array" ref="B68:M68">TRANSPOSE(D3:D14)</f>
         <v>NA</v>
       </c>
-      <c r="C68" s="10" t="str">
+      <c r="C68" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="D68" s="10" t="str">
+      <c r="D68" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="E68" s="10" t="str">
+      <c r="E68" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="F68" s="10" t="str">
+      <c r="F68" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="G68" s="10" t="str">
+      <c r="G68" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="H68" s="14">
+      <c r="H68" s="11">
         <v>378.41666666666652</v>
       </c>
-      <c r="I68" s="14">
+      <c r="I68" s="11">
         <v>59</v>
       </c>
-      <c r="J68" s="14">
+      <c r="J68" s="11">
         <v>228.79166666666652</v>
       </c>
-      <c r="K68" s="14">
+      <c r="K68" s="11">
         <v>302.79166666666652</v>
       </c>
-      <c r="L68" s="14">
+      <c r="L68" s="11">
         <v>91.458333333333485</v>
       </c>
-      <c r="M68" s="14">
+      <c r="M68" s="11">
         <v>72.416666666666515</v>
       </c>
-      <c r="N68" s="25"/>
+      <c r="N68" s="20"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="24">
+      <c r="A69" s="19">
         <v>2018</v>
       </c>
-      <c r="B69" s="14" cm="1">
+      <c r="B69" s="11" cm="1">
         <f t="array" ref="B69:M69">TRANSPOSE(D15:D26)</f>
         <v>-302.08333333333348</v>
       </c>
-      <c r="C69" s="14">
+      <c r="C69" s="11">
         <v>-574.04166666666652</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="9">
         <v>-296.70833333333348</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="9">
         <v>-334.16666666666652</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="9">
         <v>135.25</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="9">
         <v>221.58333333333348</v>
       </c>
-      <c r="H69" s="12">
+      <c r="H69" s="9">
         <v>270.91666666666652</v>
       </c>
-      <c r="I69" s="12">
+      <c r="I69" s="9">
         <v>219.79166666666652</v>
       </c>
-      <c r="J69" s="12">
+      <c r="J69" s="9">
         <v>319.54166666666652</v>
       </c>
-      <c r="K69" s="12">
+      <c r="K69" s="9">
         <v>395.83333333333348</v>
       </c>
-      <c r="L69" s="12">
+      <c r="L69" s="9">
         <v>-14.25</v>
       </c>
-      <c r="M69" s="13">
+      <c r="M69" s="10">
         <v>-79.458333333333485</v>
       </c>
-      <c r="N69" s="25"/>
+      <c r="N69" s="20"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="24">
+      <c r="A70" s="19">
         <v>2019</v>
       </c>
-      <c r="B70" s="12" cm="1">
+      <c r="B70" s="9" cm="1">
         <f t="array" ref="B70:M70">TRANSPOSE(D27:D38)</f>
         <v>-308.70833333333348</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="9">
         <v>-727.125</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="9">
         <v>-311.08333333333348</v>
       </c>
-      <c r="E70" s="12">
+      <c r="E70" s="9">
         <v>-180.29166666666652</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="9">
         <v>163</v>
       </c>
-      <c r="G70" s="12">
+      <c r="G70" s="9">
         <v>192.04166666666652</v>
       </c>
-      <c r="H70" s="12">
+      <c r="H70" s="9">
         <v>270.29166666666652</v>
       </c>
-      <c r="I70" s="12">
+      <c r="I70" s="9">
         <v>376</v>
       </c>
-      <c r="J70" s="12">
+      <c r="J70" s="9">
         <v>263.91666666666652</v>
       </c>
-      <c r="K70" s="12">
+      <c r="K70" s="9">
         <v>253.16666666666652</v>
       </c>
-      <c r="L70" s="12">
+      <c r="L70" s="9">
         <v>45.958333333333485</v>
       </c>
-      <c r="M70" s="13">
+      <c r="M70" s="10">
         <v>-20.208333333333485</v>
       </c>
-      <c r="N70" s="25"/>
+      <c r="N70" s="20"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="24">
+      <c r="A71" s="19">
         <v>2020</v>
       </c>
-      <c r="B71" s="12" cm="1">
+      <c r="B71" s="9" cm="1">
         <f t="array" ref="B71:M71">TRANSPOSE(D39:D50)</f>
         <v>-399.29166666666652</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="9">
         <v>-457.33333333333348</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="9">
         <v>-534.66666666666652</v>
       </c>
-      <c r="E71" s="12">
+      <c r="E71" s="9">
         <v>-878.54166666666652</v>
       </c>
-      <c r="F71" s="12">
+      <c r="F71" s="9">
         <v>-135.29166666666652</v>
       </c>
-      <c r="G71" s="12">
+      <c r="G71" s="9">
         <v>489.16666666666652</v>
       </c>
-      <c r="H71" s="12">
+      <c r="H71" s="9">
         <v>528.125</v>
       </c>
-      <c r="I71" s="12">
+      <c r="I71" s="9">
         <v>631.29166666666652</v>
       </c>
-      <c r="J71" s="12">
+      <c r="J71" s="9">
         <v>462.33333333333348</v>
       </c>
-      <c r="K71" s="12">
+      <c r="K71" s="9">
         <v>496.875</v>
       </c>
-      <c r="L71" s="12">
+      <c r="L71" s="9">
         <v>-1.1666666666665151</v>
       </c>
-      <c r="M71" s="13">
+      <c r="M71" s="10">
         <v>-243.79166666666652</v>
       </c>
-      <c r="N71" s="26" t="s">
+      <c r="N71" s="35" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="24">
+      <c r="A72" s="19">
         <v>2021</v>
       </c>
-      <c r="B72" s="12" cm="1">
+      <c r="B72" s="9" cm="1">
         <f t="array" ref="B72:M72">TRANSPOSE(D51:D62)</f>
         <v>-390.83333333333348</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="9">
         <v>-1024.625</v>
       </c>
-      <c r="D72" s="12">
+      <c r="D72" s="9">
         <v>-338.95833333333348</v>
       </c>
-      <c r="E72" s="12">
+      <c r="E72" s="9">
         <v>14.708333333333485</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="9">
         <v>222.5</v>
       </c>
-      <c r="G72" s="12">
+      <c r="G72" s="9">
         <v>207.16666666666652</v>
       </c>
-      <c r="H72" s="10" t="str">
+      <c r="H72" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="I72" s="10" t="str">
+      <c r="I72" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="J72" s="10" t="str">
+      <c r="J72" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="K72" s="10" t="str">
+      <c r="K72" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="L72" s="10" t="str">
+      <c r="L72" s="7" t="str">
         <v>NA</v>
       </c>
-      <c r="M72" s="11" t="str">
+      <c r="M72" s="8" t="str">
         <v>NA</v>
       </c>
-      <c r="N72" s="27"/>
+      <c r="N72" s="36"/>
     </row>
     <row r="73" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="28" t="s">
+      <c r="A73" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B73" s="12">
+      <c r="B73" s="9">
         <f>AVERAGE(B68:B72)</f>
         <v>-350.22916666666674</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="9">
         <f>AVERAGE(C68:C72)</f>
         <v>-695.78125</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="9">
         <f>AVERAGE(D68:D72)</f>
         <v>-370.35416666666674</v>
       </c>
-      <c r="E73" s="14">
+      <c r="E73" s="11">
         <f t="shared" ref="E73:M73" si="2">AVERAGE(E68:E72)</f>
         <v>-344.57291666666652</v>
       </c>
-      <c r="F73" s="14">
+      <c r="F73" s="11">
         <f t="shared" si="2"/>
         <v>96.364583333333371</v>
       </c>
-      <c r="G73" s="14">
+      <c r="G73" s="11">
         <f t="shared" si="2"/>
         <v>277.48958333333326</v>
       </c>
-      <c r="H73" s="14">
+      <c r="H73" s="11">
         <f t="shared" si="2"/>
         <v>361.93749999999989</v>
       </c>
-      <c r="I73" s="14">
+      <c r="I73" s="11">
         <f t="shared" si="2"/>
         <v>321.52083333333326</v>
       </c>
-      <c r="J73" s="14">
+      <c r="J73" s="11">
         <f t="shared" si="2"/>
         <v>318.64583333333326</v>
       </c>
-      <c r="K73" s="14">
+      <c r="K73" s="11">
         <f t="shared" si="2"/>
         <v>362.16666666666663</v>
       </c>
-      <c r="L73" s="14">
+      <c r="L73" s="11">
         <f t="shared" si="2"/>
         <v>30.500000000000114</v>
       </c>
-      <c r="M73" s="14">
+      <c r="M73" s="11">
         <f t="shared" si="2"/>
         <v>-67.760416666666742</v>
       </c>
-      <c r="N73" s="29">
+      <c r="N73" s="22">
         <v>-5.0060763888889142</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="30"/>
-      <c r="B74" s="31">
-        <f>B73-$N73</f>
+      <c r="A74" s="23"/>
+      <c r="B74" s="24">
+        <f t="shared" ref="B74:M74" si="3">B73-$N73</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="C74" s="14">
-        <f>C73-$N73</f>
+      <c r="C74" s="11">
+        <f t="shared" si="3"/>
         <v>-690.77517361111109</v>
       </c>
-      <c r="D74" s="14">
-        <f>D73-$N73</f>
+      <c r="D74" s="11">
+        <f t="shared" si="3"/>
         <v>-365.34809027777783</v>
       </c>
-      <c r="E74" s="14">
-        <f>E73-$N73</f>
+      <c r="E74" s="11">
+        <f t="shared" si="3"/>
         <v>-339.5668402777776</v>
       </c>
-      <c r="F74" s="14">
-        <f>F73-$N73</f>
+      <c r="F74" s="11">
+        <f t="shared" si="3"/>
         <v>101.37065972222229</v>
       </c>
-      <c r="G74" s="14">
-        <f>G73-$N73</f>
+      <c r="G74" s="11">
+        <f t="shared" si="3"/>
         <v>282.49565972222217</v>
       </c>
-      <c r="H74" s="14">
-        <f>H73-$N73</f>
+      <c r="H74" s="11">
+        <f t="shared" si="3"/>
         <v>366.9435763888888</v>
       </c>
-      <c r="I74" s="14">
-        <f>I73-$N73</f>
+      <c r="I74" s="11">
+        <f t="shared" si="3"/>
         <v>326.52690972222217</v>
       </c>
-      <c r="J74" s="14">
-        <f>J73-$N73</f>
+      <c r="J74" s="11">
+        <f t="shared" si="3"/>
         <v>323.65190972222217</v>
       </c>
-      <c r="K74" s="14">
-        <f>K73-$N73</f>
+      <c r="K74" s="11">
+        <f t="shared" si="3"/>
         <v>367.17274305555554</v>
       </c>
-      <c r="L74" s="14">
-        <f>L73-$N73</f>
+      <c r="L74" s="11">
+        <f t="shared" si="3"/>
         <v>35.506076388889028</v>
       </c>
-      <c r="M74" s="14">
-        <f>M73-$N73</f>
+      <c r="M74" s="11">
+        <f t="shared" si="3"/>
         <v>-62.754340277777828</v>
       </c>
-      <c r="N74" s="32"/>
+      <c r="N74" s="25"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35"/>
     <row r="78" spans="1:14" ht="43.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="33" t="s">
+      <c r="A78" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="34"/>
-      <c r="C78" s="34"/>
-      <c r="D78" s="34"/>
-      <c r="E78" s="34"/>
-      <c r="F78" s="34"/>
-      <c r="G78" s="35"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="39"/>
     </row>
     <row r="79" spans="1:14" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="36" t="s">
+      <c r="A79" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B79" s="37" t="s">
+      <c r="B79" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38" t="s">
+      <c r="C79" s="28"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="G79" s="39" t="s">
+      <c r="G79" s="29" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="7">
         <f>B3</f>
         <v>3034</v>
       </c>
-      <c r="C80" s="10" t="str">
-        <f t="shared" ref="C80:D80" si="3">C3</f>
+      <c r="C80" s="7" t="str">
+        <f t="shared" ref="C80:D80" si="4">C3</f>
         <v>NA</v>
       </c>
-      <c r="D80" s="10" t="str">
-        <f t="shared" si="3"/>
+      <c r="D80" s="8" t="str">
+        <f>IF(LEN(D3)&gt;0,D3,"")</f>
         <v>NA</v>
       </c>
-      <c r="E80" s="14" cm="1">
+      <c r="E80" s="11" cm="1">
         <f t="array" ref="E80:E91">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F80" s="10" t="str">
+      <c r="F80" s="7" t="str">
         <f>IFERROR(B3-C3-E80, "NA")</f>
         <v>NA</v>
       </c>
-      <c r="G80" s="14">
+      <c r="G80" s="11">
         <f>B80-E80</f>
         <v>3379.2230902777778</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B81" s="10">
-        <f t="shared" ref="B81:D96" si="4">B4</f>
+      <c r="B81" s="7">
+        <f t="shared" ref="B81:D96" si="5">B4</f>
         <v>2748</v>
       </c>
-      <c r="C81" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>NA</v>
-      </c>
-      <c r="D81" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v>NA</v>
-      </c>
-      <c r="E81" s="14">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F81" s="10" t="str">
-        <f t="shared" ref="F81:F139" si="5">IFERROR(B4-C4-E81, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="G81" s="14">
-        <f t="shared" ref="G81:G139" si="6">B81-E81</f>
-        <v>3438.7751736111113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82" s="10">
-        <f t="shared" si="4"/>
-        <v>3164</v>
-      </c>
-      <c r="C82" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>NA</v>
-      </c>
-      <c r="D82" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v>NA</v>
-      </c>
-      <c r="E82" s="14">
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="F82" s="10" t="str">
+      <c r="C81" s="7" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G82" s="14">
-        <f t="shared" si="6"/>
-        <v>3529.3480902777778</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" s="10">
-        <f t="shared" si="4"/>
-        <v>3238</v>
-      </c>
-      <c r="C83" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="D81" s="8" t="str">
+        <f t="shared" ref="D81:D139" si="6">IF(LEN(D4)&gt;0,D4,"")</f>
         <v>NA</v>
       </c>
-      <c r="D83" s="13" t="str">
-        <f t="shared" si="4"/>
+      <c r="E81" s="11">
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="F81" s="7" t="str">
+        <f t="shared" ref="F81:F139" si="7">IFERROR(B4-C4-E81, "NA")</f>
         <v>NA</v>
       </c>
-      <c r="E83" s="14">
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F83" s="10" t="str">
+      <c r="G81" s="11">
+        <f t="shared" ref="G81:G139" si="8">B81-E81</f>
+        <v>3438.7751736111113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="7">
+        <f t="shared" si="5"/>
+        <v>3164</v>
+      </c>
+      <c r="C82" s="7" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G83" s="14">
+      <c r="D82" s="8" t="str">
         <f t="shared" si="6"/>
-        <v>3577.5668402777774</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B84" s="10">
-        <f t="shared" si="4"/>
-        <v>3416</v>
-      </c>
-      <c r="C84" s="10" t="str">
-        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="D84" s="13" t="str">
-        <f t="shared" si="4"/>
+      <c r="E82" s="11">
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="F82" s="7" t="str">
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
-      <c r="E84" s="14">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F84" s="10" t="str">
+      <c r="G82" s="11">
+        <f t="shared" si="8"/>
+        <v>3529.3480902777778</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="7">
+        <f t="shared" si="5"/>
+        <v>3238</v>
+      </c>
+      <c r="C83" s="7" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G84" s="14">
+      <c r="D83" s="8" t="str">
         <f t="shared" si="6"/>
-        <v>3314.6293402777778</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" s="10">
-        <f t="shared" si="4"/>
-        <v>3492</v>
-      </c>
-      <c r="C85" s="10" t="str">
-        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="D85" s="13" t="str">
-        <f t="shared" si="4"/>
+      <c r="E83" s="11">
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F83" s="7" t="str">
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
-      <c r="E85" s="14">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F85" s="10" t="str">
+      <c r="G83" s="11">
+        <f t="shared" si="8"/>
+        <v>3577.5668402777774</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="7">
+        <f t="shared" si="5"/>
+        <v>3416</v>
+      </c>
+      <c r="C84" s="7" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G85" s="14">
+      <c r="D84" s="8" t="str">
         <f t="shared" si="6"/>
+        <v>NA</v>
+      </c>
+      <c r="E84" s="11">
+        <v>101.37065972222229</v>
+      </c>
+      <c r="F84" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>NA</v>
+      </c>
+      <c r="G84" s="11">
+        <f t="shared" si="8"/>
+        <v>3314.6293402777778</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="7">
+        <f t="shared" si="5"/>
+        <v>3492</v>
+      </c>
+      <c r="C85" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>NA</v>
+      </c>
+      <c r="D85" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v>NA</v>
+      </c>
+      <c r="E85" s="11">
+        <v>282.49565972222217</v>
+      </c>
+      <c r="F85" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>NA</v>
+      </c>
+      <c r="G85" s="11">
+        <f t="shared" si="8"/>
         <v>3209.5043402777778</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B86" s="10">
-        <f t="shared" si="4"/>
+      <c r="B86" s="7">
+        <f t="shared" si="5"/>
         <v>3730</v>
       </c>
-      <c r="C86" s="12">
-        <f t="shared" si="4"/>
+      <c r="C86" s="9">
+        <f t="shared" si="5"/>
         <v>3351.5833333333335</v>
       </c>
-      <c r="D86" s="13">
-        <f t="shared" si="4"/>
+      <c r="D86" s="10">
+        <f t="shared" si="6"/>
         <v>378.41666666666652</v>
       </c>
-      <c r="E86" s="14">
+      <c r="E86" s="11">
         <v>366.9435763888888</v>
       </c>
-      <c r="F86" s="14">
+      <c r="F86" s="11">
+        <f t="shared" si="7"/>
+        <v>11.473090277777715</v>
+      </c>
+      <c r="G86" s="11">
+        <f t="shared" si="8"/>
+        <v>3363.0564236111113</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="7">
         <f t="shared" si="5"/>
-        <v>11.473090277777715</v>
-      </c>
-      <c r="G86" s="14">
+        <v>3409</v>
+      </c>
+      <c r="C87" s="9">
+        <f t="shared" si="5"/>
+        <v>3350</v>
+      </c>
+      <c r="D87" s="11">
         <f t="shared" si="6"/>
-        <v>3363.0564236111113</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B87" s="10">
-        <f t="shared" si="4"/>
-        <v>3409</v>
-      </c>
-      <c r="C87" s="12">
-        <f t="shared" si="4"/>
-        <v>3350</v>
-      </c>
-      <c r="D87" s="13">
-        <f t="shared" si="4"/>
         <v>59</v>
       </c>
-      <c r="E87" s="14">
+      <c r="E87" s="11">
         <v>326.52690972222217</v>
       </c>
-      <c r="F87" s="14">
+      <c r="F87" s="11">
+        <f t="shared" si="7"/>
+        <v>-267.52690972222217</v>
+      </c>
+      <c r="G87" s="11">
+        <f t="shared" si="8"/>
+        <v>3082.4730902777778</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" s="7">
         <f t="shared" si="5"/>
-        <v>-267.52690972222217</v>
-      </c>
-      <c r="G87" s="14">
+        <v>3572</v>
+      </c>
+      <c r="C88" s="9">
+        <f t="shared" si="5"/>
+        <v>3343.2083333333335</v>
+      </c>
+      <c r="D88" s="11">
         <f t="shared" si="6"/>
-        <v>3082.4730902777778</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A88" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B88" s="10">
-        <f t="shared" si="4"/>
-        <v>3572</v>
-      </c>
-      <c r="C88" s="12">
-        <f t="shared" si="4"/>
-        <v>3343.2083333333335</v>
-      </c>
-      <c r="D88" s="13">
-        <f t="shared" si="4"/>
         <v>228.79166666666652</v>
       </c>
-      <c r="E88" s="14">
+      <c r="E88" s="11">
         <v>323.65190972222217</v>
       </c>
-      <c r="F88" s="14">
+      <c r="F88" s="11">
+        <f t="shared" si="7"/>
+        <v>-94.860243055555657</v>
+      </c>
+      <c r="G88" s="11">
+        <f t="shared" si="8"/>
+        <v>3248.3480902777778</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B89" s="7">
         <f t="shared" si="5"/>
-        <v>-94.860243055555657</v>
-      </c>
-      <c r="G88" s="14">
+        <v>3629</v>
+      </c>
+      <c r="C89" s="9">
+        <f t="shared" si="5"/>
+        <v>3326.2083333333335</v>
+      </c>
+      <c r="D89" s="11">
         <f t="shared" si="6"/>
-        <v>3248.3480902777778</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B89" s="10">
-        <f t="shared" si="4"/>
-        <v>3629</v>
-      </c>
-      <c r="C89" s="12">
-        <f t="shared" si="4"/>
-        <v>3326.2083333333335</v>
-      </c>
-      <c r="D89" s="13">
-        <f t="shared" si="4"/>
         <v>302.79166666666652</v>
       </c>
-      <c r="E89" s="14">
+      <c r="E89" s="11">
         <v>367.17274305555554</v>
       </c>
-      <c r="F89" s="14">
+      <c r="F89" s="11">
+        <f t="shared" si="7"/>
+        <v>-64.381076388889028</v>
+      </c>
+      <c r="G89" s="11">
+        <f t="shared" si="8"/>
+        <v>3261.8272569444443</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" s="7">
         <f t="shared" si="5"/>
-        <v>-64.381076388889028</v>
-      </c>
-      <c r="G89" s="14">
+        <v>3408</v>
+      </c>
+      <c r="C90" s="9">
+        <f t="shared" si="5"/>
+        <v>3316.5416666666665</v>
+      </c>
+      <c r="D90" s="11">
         <f t="shared" si="6"/>
-        <v>3261.8272569444443</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B90" s="10">
-        <f t="shared" si="4"/>
-        <v>3408</v>
-      </c>
-      <c r="C90" s="12">
-        <f t="shared" si="4"/>
-        <v>3316.5416666666665</v>
-      </c>
-      <c r="D90" s="13">
-        <f t="shared" si="4"/>
         <v>91.458333333333485</v>
       </c>
-      <c r="E90" s="14">
+      <c r="E90" s="11">
         <v>35.506076388889028</v>
       </c>
-      <c r="F90" s="14">
+      <c r="F90" s="11">
+        <f t="shared" si="7"/>
+        <v>55.952256944444457</v>
+      </c>
+      <c r="G90" s="11">
+        <f t="shared" si="8"/>
+        <v>3372.4939236111109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" s="7">
         <f t="shared" si="5"/>
-        <v>55.952256944444457</v>
-      </c>
-      <c r="G90" s="14">
+        <v>3391</v>
+      </c>
+      <c r="C91" s="9">
+        <f t="shared" si="5"/>
+        <v>3318.5833333333335</v>
+      </c>
+      <c r="D91" s="11">
         <f t="shared" si="6"/>
-        <v>3372.4939236111109</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" s="10">
-        <f t="shared" si="4"/>
-        <v>3391</v>
-      </c>
-      <c r="C91" s="12">
-        <f t="shared" si="4"/>
-        <v>3318.5833333333335</v>
-      </c>
-      <c r="D91" s="13">
-        <f t="shared" si="4"/>
         <v>72.416666666666515</v>
       </c>
-      <c r="E91" s="14">
+      <c r="E91" s="11">
         <v>-62.754340277777828</v>
       </c>
-      <c r="F91" s="14">
+      <c r="F91" s="11">
+        <f t="shared" si="7"/>
+        <v>135.17100694444434</v>
+      </c>
+      <c r="G91" s="11">
+        <f t="shared" si="8"/>
+        <v>3453.7543402777778</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B92" s="7">
         <f t="shared" si="5"/>
-        <v>135.17100694444434</v>
-      </c>
-      <c r="G91" s="14">
+        <v>3010</v>
+      </c>
+      <c r="C92" s="9">
+        <f t="shared" si="5"/>
+        <v>3312.0833333333335</v>
+      </c>
+      <c r="D92" s="11">
         <f t="shared" si="6"/>
-        <v>3453.7543402777778</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B92" s="10">
-        <f t="shared" si="4"/>
-        <v>3010</v>
-      </c>
-      <c r="C92" s="12">
-        <f t="shared" si="4"/>
-        <v>3312.0833333333335</v>
-      </c>
-      <c r="D92" s="13">
-        <f t="shared" si="4"/>
         <v>-302.08333333333348</v>
       </c>
-      <c r="E92" s="14" cm="1">
+      <c r="E92" s="11" cm="1">
         <f t="array" ref="E92:E103">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F92" s="14">
+      <c r="F92" s="11">
+        <f t="shared" si="7"/>
+        <v>43.139756944444343</v>
+      </c>
+      <c r="G92" s="11">
+        <f t="shared" si="8"/>
+        <v>3355.2230902777778</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" s="7">
         <f t="shared" si="5"/>
-        <v>43.139756944444343</v>
-      </c>
-      <c r="G92" s="14">
+        <v>2734</v>
+      </c>
+      <c r="C93" s="9">
+        <f t="shared" si="5"/>
+        <v>3308.0416666666665</v>
+      </c>
+      <c r="D93" s="11">
         <f t="shared" si="6"/>
-        <v>3355.2230902777778</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A93" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B93" s="10">
-        <f t="shared" si="4"/>
-        <v>2734</v>
-      </c>
-      <c r="C93" s="12">
-        <f t="shared" si="4"/>
-        <v>3308.0416666666665</v>
-      </c>
-      <c r="D93" s="13">
-        <f t="shared" si="4"/>
         <v>-574.04166666666652</v>
       </c>
-      <c r="E93" s="14">
+      <c r="E93" s="11">
         <v>-690.77517361111109</v>
       </c>
-      <c r="F93" s="14">
+      <c r="F93" s="11">
+        <f t="shared" si="7"/>
+        <v>116.73350694444457</v>
+      </c>
+      <c r="G93" s="11">
+        <f t="shared" si="8"/>
+        <v>3424.7751736111113</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B94" s="7">
         <f t="shared" si="5"/>
-        <v>116.73350694444457</v>
-      </c>
-      <c r="G93" s="14">
+        <v>3015</v>
+      </c>
+      <c r="C94" s="9">
+        <f t="shared" si="5"/>
+        <v>3311.7083333333335</v>
+      </c>
+      <c r="D94" s="11">
         <f t="shared" si="6"/>
-        <v>3424.7751736111113</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A94" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B94" s="10">
-        <f t="shared" si="4"/>
-        <v>3015</v>
-      </c>
-      <c r="C94" s="12">
-        <f t="shared" si="4"/>
-        <v>3311.7083333333335</v>
-      </c>
-      <c r="D94" s="13">
-        <f t="shared" si="4"/>
         <v>-296.70833333333348</v>
       </c>
-      <c r="E94" s="14">
+      <c r="E94" s="11">
         <v>-365.34809027777783</v>
       </c>
-      <c r="F94" s="14">
+      <c r="F94" s="11">
+        <f t="shared" si="7"/>
+        <v>68.639756944444343</v>
+      </c>
+      <c r="G94" s="11">
+        <f t="shared" si="8"/>
+        <v>3380.3480902777778</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" s="7">
         <f t="shared" si="5"/>
-        <v>68.639756944444343</v>
-      </c>
-      <c r="G94" s="14">
+        <v>2979</v>
+      </c>
+      <c r="C95" s="9">
+        <f t="shared" si="5"/>
+        <v>3313.1666666666665</v>
+      </c>
+      <c r="D95" s="11">
         <f t="shared" si="6"/>
-        <v>3380.3480902777778</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A95" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B95" s="10">
-        <f t="shared" si="4"/>
-        <v>2979</v>
-      </c>
-      <c r="C95" s="12">
-        <f t="shared" si="4"/>
-        <v>3313.1666666666665</v>
-      </c>
-      <c r="D95" s="13">
-        <f t="shared" si="4"/>
         <v>-334.16666666666652</v>
       </c>
-      <c r="E95" s="14">
+      <c r="E95" s="11">
         <v>-339.5668402777776</v>
       </c>
-      <c r="F95" s="14">
+      <c r="F95" s="11">
+        <f t="shared" si="7"/>
+        <v>5.4001736111110858</v>
+      </c>
+      <c r="G95" s="11">
+        <f t="shared" si="8"/>
+        <v>3318.5668402777774</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B96" s="7">
         <f t="shared" si="5"/>
-        <v>5.4001736111110858</v>
-      </c>
-      <c r="G95" s="14">
+        <v>3443</v>
+      </c>
+      <c r="C96" s="9">
+        <f t="shared" si="5"/>
+        <v>3307.75</v>
+      </c>
+      <c r="D96" s="11">
         <f t="shared" si="6"/>
-        <v>3318.5668402777774</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A96" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B96" s="10">
-        <f t="shared" si="4"/>
-        <v>3443</v>
-      </c>
-      <c r="C96" s="12">
-        <f t="shared" si="4"/>
-        <v>3307.75</v>
-      </c>
-      <c r="D96" s="13">
-        <f t="shared" si="4"/>
         <v>135.25</v>
       </c>
-      <c r="E96" s="14">
+      <c r="E96" s="11">
         <v>101.37065972222229</v>
       </c>
-      <c r="F96" s="14">
-        <f t="shared" si="5"/>
+      <c r="F96" s="11">
+        <f t="shared" si="7"/>
         <v>33.879340277777715</v>
       </c>
-      <c r="G96" s="14">
+      <c r="G96" s="11">
+        <f t="shared" si="8"/>
+        <v>3341.6293402777778</v>
+      </c>
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A97" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B97" s="7">
+        <f t="shared" ref="B97:D112" si="9">B20</f>
+        <v>3514</v>
+      </c>
+      <c r="C97" s="9">
+        <f t="shared" si="9"/>
+        <v>3292.4166666666665</v>
+      </c>
+      <c r="D97" s="11">
         <f t="shared" si="6"/>
-        <v>3341.6293402777778</v>
-      </c>
-      <c r="H96" s="1"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A97" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B97" s="10">
-        <f t="shared" ref="B97:D112" si="7">B20</f>
-        <v>3514</v>
-      </c>
-      <c r="C97" s="12">
+        <v>221.58333333333348</v>
+      </c>
+      <c r="E97" s="11">
+        <v>282.49565972222217</v>
+      </c>
+      <c r="F97" s="11">
         <f t="shared" si="7"/>
-        <v>3292.4166666666665</v>
-      </c>
-      <c r="D97" s="13">
+        <v>-60.912326388888687</v>
+      </c>
+      <c r="G97" s="11">
+        <f t="shared" si="8"/>
+        <v>3231.5043402777778</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="7">
+        <f t="shared" si="9"/>
+        <v>3552</v>
+      </c>
+      <c r="C98" s="9">
+        <f t="shared" si="9"/>
+        <v>3281.0833333333335</v>
+      </c>
+      <c r="D98" s="11">
+        <f t="shared" si="6"/>
+        <v>270.91666666666652</v>
+      </c>
+      <c r="E98" s="11">
+        <v>366.9435763888888</v>
+      </c>
+      <c r="F98" s="11">
         <f t="shared" si="7"/>
-        <v>221.58333333333348</v>
-      </c>
-      <c r="E97" s="14">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F97" s="14">
-        <f t="shared" si="5"/>
-        <v>-60.912326388888687</v>
-      </c>
-      <c r="G97" s="14">
+        <v>-96.026909722222285</v>
+      </c>
+      <c r="G98" s="11">
+        <f t="shared" si="8"/>
+        <v>3185.0564236111113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B99" s="7">
+        <f t="shared" si="9"/>
+        <v>3490</v>
+      </c>
+      <c r="C99" s="9">
+        <f t="shared" si="9"/>
+        <v>3270.2083333333335</v>
+      </c>
+      <c r="D99" s="11">
         <f t="shared" si="6"/>
-        <v>3231.5043402777778</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A98" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="10">
+        <v>219.79166666666652</v>
+      </c>
+      <c r="E99" s="11">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F99" s="11">
         <f t="shared" si="7"/>
-        <v>3552</v>
-      </c>
-      <c r="C98" s="12">
+        <v>-106.73524305555566</v>
+      </c>
+      <c r="G99" s="11">
+        <f t="shared" si="8"/>
+        <v>3163.4730902777778</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100" s="7">
+        <f t="shared" si="9"/>
+        <v>3579</v>
+      </c>
+      <c r="C100" s="9">
+        <f t="shared" si="9"/>
+        <v>3259.4583333333335</v>
+      </c>
+      <c r="D100" s="11">
+        <f t="shared" si="6"/>
+        <v>319.54166666666652</v>
+      </c>
+      <c r="E100" s="11">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F100" s="11">
         <f t="shared" si="7"/>
-        <v>3281.0833333333335</v>
-      </c>
-      <c r="D98" s="13">
+        <v>-4.1102430555556566</v>
+      </c>
+      <c r="G100" s="11">
+        <f t="shared" si="8"/>
+        <v>3255.3480902777778</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A101" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" s="7">
+        <f t="shared" si="9"/>
+        <v>3657</v>
+      </c>
+      <c r="C101" s="9">
+        <f t="shared" si="9"/>
+        <v>3261.1666666666665</v>
+      </c>
+      <c r="D101" s="11">
+        <f t="shared" si="6"/>
+        <v>395.83333333333348</v>
+      </c>
+      <c r="E101" s="11">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F101" s="11">
         <f t="shared" si="7"/>
-        <v>270.91666666666652</v>
-      </c>
-      <c r="E98" s="14">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F98" s="14">
-        <f t="shared" si="5"/>
-        <v>-96.026909722222285</v>
-      </c>
-      <c r="G98" s="14">
+        <v>28.660590277777942</v>
+      </c>
+      <c r="G101" s="11">
+        <f t="shared" si="8"/>
+        <v>3289.8272569444443</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A102" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" s="7">
+        <f t="shared" si="9"/>
+        <v>3250</v>
+      </c>
+      <c r="C102" s="9">
+        <f t="shared" si="9"/>
+        <v>3264.25</v>
+      </c>
+      <c r="D102" s="11">
         <f t="shared" si="6"/>
-        <v>3185.0564236111113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A99" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B99" s="10">
+        <v>-14.25</v>
+      </c>
+      <c r="E102" s="11">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F102" s="11">
         <f t="shared" si="7"/>
-        <v>3490</v>
-      </c>
-      <c r="C99" s="12">
+        <v>-49.756076388889028</v>
+      </c>
+      <c r="G102" s="11">
+        <f t="shared" si="8"/>
+        <v>3214.4939236111109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A103" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" s="7">
+        <f t="shared" si="9"/>
+        <v>3181</v>
+      </c>
+      <c r="C103" s="9">
+        <f t="shared" si="9"/>
+        <v>3260.4583333333335</v>
+      </c>
+      <c r="D103" s="11">
+        <f t="shared" si="6"/>
+        <v>-79.458333333333485</v>
+      </c>
+      <c r="E103" s="11">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F103" s="11">
         <f t="shared" si="7"/>
-        <v>3270.2083333333335</v>
-      </c>
-      <c r="D99" s="13">
-        <f t="shared" si="7"/>
-        <v>219.79166666666652</v>
-      </c>
-      <c r="E99" s="14">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F99" s="14">
-        <f t="shared" si="5"/>
-        <v>-106.73524305555566</v>
-      </c>
-      <c r="G99" s="14">
+        <v>-16.703993055555657</v>
+      </c>
+      <c r="G103" s="11">
+        <f t="shared" si="8"/>
+        <v>3243.7543402777778</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A104" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B104" s="7">
+        <f t="shared" si="9"/>
+        <v>2948</v>
+      </c>
+      <c r="C104" s="9">
+        <f t="shared" si="9"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D104" s="11">
         <f t="shared" si="6"/>
-        <v>3163.4730902777778</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A100" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B100" s="10">
-        <f t="shared" si="7"/>
-        <v>3579</v>
-      </c>
-      <c r="C100" s="12">
-        <f t="shared" si="7"/>
-        <v>3259.4583333333335</v>
-      </c>
-      <c r="D100" s="13">
-        <f t="shared" si="7"/>
-        <v>319.54166666666652</v>
-      </c>
-      <c r="E100" s="14">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F100" s="14">
-        <f t="shared" si="5"/>
-        <v>-4.1102430555556566</v>
-      </c>
-      <c r="G100" s="14">
-        <f t="shared" si="6"/>
-        <v>3255.3480902777778</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A101" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B101" s="10">
-        <f t="shared" si="7"/>
-        <v>3657</v>
-      </c>
-      <c r="C101" s="12">
-        <f t="shared" si="7"/>
-        <v>3261.1666666666665</v>
-      </c>
-      <c r="D101" s="13">
-        <f t="shared" si="7"/>
-        <v>395.83333333333348</v>
-      </c>
-      <c r="E101" s="14">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F101" s="14">
-        <f t="shared" si="5"/>
-        <v>28.660590277777942</v>
-      </c>
-      <c r="G101" s="14">
-        <f t="shared" si="6"/>
-        <v>3289.8272569444443</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A102" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B102" s="10">
-        <f t="shared" si="7"/>
-        <v>3250</v>
-      </c>
-      <c r="C102" s="12">
-        <f t="shared" si="7"/>
-        <v>3264.25</v>
-      </c>
-      <c r="D102" s="13">
-        <f t="shared" si="7"/>
-        <v>-14.25</v>
-      </c>
-      <c r="E102" s="14">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F102" s="14">
-        <f t="shared" si="5"/>
-        <v>-49.756076388889028</v>
-      </c>
-      <c r="G102" s="14">
-        <f t="shared" si="6"/>
-        <v>3214.4939236111109</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A103" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B103" s="10">
-        <f t="shared" si="7"/>
-        <v>3181</v>
-      </c>
-      <c r="C103" s="12">
-        <f t="shared" si="7"/>
-        <v>3260.4583333333335</v>
-      </c>
-      <c r="D103" s="13">
-        <f t="shared" si="7"/>
-        <v>-79.458333333333485</v>
-      </c>
-      <c r="E103" s="14">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F103" s="14">
-        <f t="shared" si="5"/>
-        <v>-16.703993055555657</v>
-      </c>
-      <c r="G103" s="14">
-        <f t="shared" si="6"/>
-        <v>3243.7543402777778</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A104" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B104" s="10">
-        <f t="shared" si="7"/>
-        <v>2948</v>
-      </c>
-      <c r="C104" s="12">
-        <f t="shared" si="7"/>
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D104" s="13">
-        <f t="shared" si="7"/>
         <v>-308.70833333333348</v>
       </c>
-      <c r="E104" s="14" cm="1">
+      <c r="E104" s="11" cm="1">
         <f t="array" ref="E104:E115">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F104" s="14">
-        <f t="shared" si="5"/>
+      <c r="F104" s="11">
+        <f t="shared" si="7"/>
         <v>36.514756944444343</v>
       </c>
-      <c r="G104" s="14">
+      <c r="G104" s="11">
+        <f t="shared" si="8"/>
+        <v>3293.2230902777778</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A105" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" s="7">
+        <f t="shared" si="9"/>
+        <v>2535</v>
+      </c>
+      <c r="C105" s="9">
+        <f t="shared" si="9"/>
+        <v>3262.125</v>
+      </c>
+      <c r="D105" s="11">
         <f t="shared" si="6"/>
-        <v>3293.2230902777778</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A105" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B105" s="10">
+        <v>-727.125</v>
+      </c>
+      <c r="E105" s="11">
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="F105" s="11">
         <f t="shared" si="7"/>
-        <v>2535</v>
-      </c>
-      <c r="C105" s="12">
+        <v>-36.349826388888914</v>
+      </c>
+      <c r="G105" s="11">
+        <f t="shared" si="8"/>
+        <v>3225.7751736111113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A106" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B106" s="7">
+        <f t="shared" si="9"/>
+        <v>2956</v>
+      </c>
+      <c r="C106" s="9">
+        <f t="shared" si="9"/>
+        <v>3267.0833333333335</v>
+      </c>
+      <c r="D106" s="11">
+        <f t="shared" si="6"/>
+        <v>-311.08333333333348</v>
+      </c>
+      <c r="E106" s="11">
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="F106" s="11">
         <f t="shared" si="7"/>
-        <v>3262.125</v>
-      </c>
-      <c r="D105" s="13">
+        <v>54.264756944444343</v>
+      </c>
+      <c r="G106" s="11">
+        <f t="shared" si="8"/>
+        <v>3321.3480902777778</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A107" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107" s="7">
+        <f t="shared" si="9"/>
+        <v>3079</v>
+      </c>
+      <c r="C107" s="9">
+        <f t="shared" si="9"/>
+        <v>3259.2916666666665</v>
+      </c>
+      <c r="D107" s="11">
+        <f t="shared" si="6"/>
+        <v>-180.29166666666652</v>
+      </c>
+      <c r="E107" s="11">
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F107" s="11">
         <f t="shared" si="7"/>
-        <v>-727.125</v>
-      </c>
-      <c r="E105" s="14">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F105" s="14">
-        <f t="shared" si="5"/>
-        <v>-36.349826388888914</v>
-      </c>
-      <c r="G105" s="14">
+        <v>159.27517361111109</v>
+      </c>
+      <c r="G107" s="11">
+        <f t="shared" si="8"/>
+        <v>3418.5668402777774</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A108" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B108" s="7">
+        <f t="shared" si="9"/>
+        <v>3417</v>
+      </c>
+      <c r="C108" s="9">
+        <f t="shared" si="9"/>
+        <v>3254</v>
+      </c>
+      <c r="D108" s="11">
         <f t="shared" si="6"/>
-        <v>3225.7751736111113</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A106" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B106" s="10">
+        <v>163</v>
+      </c>
+      <c r="E108" s="11">
+        <v>101.37065972222229</v>
+      </c>
+      <c r="F108" s="11">
         <f t="shared" si="7"/>
-        <v>2956</v>
-      </c>
-      <c r="C106" s="12">
+        <v>61.629340277777715</v>
+      </c>
+      <c r="G108" s="11">
+        <f t="shared" si="8"/>
+        <v>3315.6293402777778</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A109" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B109" s="7">
+        <f t="shared" si="9"/>
+        <v>3449</v>
+      </c>
+      <c r="C109" s="9">
+        <f t="shared" si="9"/>
+        <v>3256.9583333333335</v>
+      </c>
+      <c r="D109" s="11">
+        <f t="shared" si="6"/>
+        <v>192.04166666666652</v>
+      </c>
+      <c r="E109" s="11">
+        <v>282.49565972222217</v>
+      </c>
+      <c r="F109" s="11">
         <f t="shared" si="7"/>
-        <v>3267.0833333333335</v>
-      </c>
-      <c r="D106" s="13">
-        <f t="shared" si="7"/>
-        <v>-311.08333333333348</v>
-      </c>
-      <c r="E106" s="14">
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="F106" s="14">
-        <f t="shared" si="5"/>
-        <v>54.264756944444343</v>
-      </c>
-      <c r="G106" s="14">
-        <f t="shared" si="6"/>
-        <v>3321.3480902777778</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A107" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B107" s="10">
-        <f t="shared" si="7"/>
-        <v>3079</v>
-      </c>
-      <c r="C107" s="12">
-        <f t="shared" si="7"/>
-        <v>3259.2916666666665</v>
-      </c>
-      <c r="D107" s="13">
-        <f t="shared" si="7"/>
-        <v>-180.29166666666652</v>
-      </c>
-      <c r="E107" s="14">
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F107" s="14">
-        <f t="shared" si="5"/>
-        <v>159.27517361111109</v>
-      </c>
-      <c r="G107" s="14">
-        <f t="shared" si="6"/>
-        <v>3418.5668402777774</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A108" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B108" s="10">
-        <f t="shared" si="7"/>
-        <v>3417</v>
-      </c>
-      <c r="C108" s="12">
-        <f t="shared" si="7"/>
-        <v>3254</v>
-      </c>
-      <c r="D108" s="13">
-        <f t="shared" si="7"/>
-        <v>163</v>
-      </c>
-      <c r="E108" s="14">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F108" s="14">
-        <f t="shared" si="5"/>
-        <v>61.629340277777715</v>
-      </c>
-      <c r="G108" s="14">
-        <f t="shared" si="6"/>
-        <v>3315.6293402777778</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A109" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B109" s="10">
-        <f t="shared" si="7"/>
-        <v>3449</v>
-      </c>
-      <c r="C109" s="12">
-        <f t="shared" si="7"/>
-        <v>3256.9583333333335</v>
-      </c>
-      <c r="D109" s="13">
-        <f t="shared" si="7"/>
-        <v>192.04166666666652</v>
-      </c>
-      <c r="E109" s="14">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F109" s="14">
-        <f t="shared" si="5"/>
         <v>-90.453993055555657</v>
       </c>
-      <c r="G109" s="14">
-        <f t="shared" si="6"/>
+      <c r="G109" s="11">
+        <f t="shared" si="8"/>
         <v>3166.5043402777778</v>
       </c>
       <c r="H109" s="1"/>
@@ -5751,30 +5736,30 @@
       <c r="M109" s="1"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A110" s="9" t="s">
+      <c r="A110" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="7">
+        <f t="shared" si="9"/>
+        <v>3527</v>
+      </c>
+      <c r="C110" s="9">
+        <f t="shared" si="9"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D110" s="11">
+        <f t="shared" si="6"/>
+        <v>270.29166666666652</v>
+      </c>
+      <c r="E110" s="11">
+        <v>366.9435763888888</v>
+      </c>
+      <c r="F110" s="11">
         <f t="shared" si="7"/>
-        <v>3527</v>
-      </c>
-      <c r="C110" s="12">
-        <f t="shared" si="7"/>
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D110" s="13">
-        <f t="shared" si="7"/>
-        <v>270.29166666666652</v>
-      </c>
-      <c r="E110" s="14">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F110" s="14">
-        <f t="shared" si="5"/>
         <v>-96.651909722222285</v>
       </c>
-      <c r="G110" s="14">
-        <f t="shared" si="6"/>
+      <c r="G110" s="11">
+        <f t="shared" si="8"/>
         <v>3160.0564236111113</v>
       </c>
       <c r="H110" s="1"/>
@@ -5785,30 +5770,30 @@
       <c r="M110" s="1"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A111" s="9" t="s">
+      <c r="A111" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="7">
+        <f t="shared" si="9"/>
+        <v>3645</v>
+      </c>
+      <c r="C111" s="9">
+        <f t="shared" si="9"/>
+        <v>3269</v>
+      </c>
+      <c r="D111" s="11">
+        <f t="shared" si="6"/>
+        <v>376</v>
+      </c>
+      <c r="E111" s="11">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F111" s="11">
         <f t="shared" si="7"/>
-        <v>3645</v>
-      </c>
-      <c r="C111" s="12">
-        <f t="shared" si="7"/>
-        <v>3269</v>
-      </c>
-      <c r="D111" s="13">
-        <f t="shared" si="7"/>
-        <v>376</v>
-      </c>
-      <c r="E111" s="14">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F111" s="14">
-        <f t="shared" si="5"/>
         <v>49.473090277777828</v>
       </c>
-      <c r="G111" s="14">
-        <f t="shared" si="6"/>
+      <c r="G111" s="11">
+        <f t="shared" si="8"/>
         <v>3318.4730902777778</v>
       </c>
       <c r="H111" s="1"/>
@@ -5819,30 +5804,30 @@
       <c r="M111" s="1"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A112" s="9" t="s">
+      <c r="A112" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="7">
+        <f t="shared" si="9"/>
+        <v>3543</v>
+      </c>
+      <c r="C112" s="9">
+        <f t="shared" si="9"/>
+        <v>3279.0833333333335</v>
+      </c>
+      <c r="D112" s="11">
+        <f t="shared" si="6"/>
+        <v>263.91666666666652</v>
+      </c>
+      <c r="E112" s="11">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F112" s="11">
         <f t="shared" si="7"/>
-        <v>3543</v>
-      </c>
-      <c r="C112" s="12">
-        <f t="shared" si="7"/>
-        <v>3279.0833333333335</v>
-      </c>
-      <c r="D112" s="13">
-        <f t="shared" si="7"/>
-        <v>263.91666666666652</v>
-      </c>
-      <c r="E112" s="14">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F112" s="14">
-        <f t="shared" si="5"/>
         <v>-59.735243055555657</v>
       </c>
-      <c r="G112" s="14">
-        <f t="shared" si="6"/>
+      <c r="G112" s="11">
+        <f t="shared" si="8"/>
         <v>3219.3480902777778</v>
       </c>
       <c r="H112" s="1"/>
@@ -5853,58 +5838,58 @@
       <c r="M112" s="1"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A113" s="9" t="s">
+      <c r="A113" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B113" s="10">
-        <f t="shared" ref="B113:D128" si="8">B36</f>
+      <c r="B113" s="7">
+        <f t="shared" ref="B113:D128" si="10">B36</f>
         <v>3506</v>
       </c>
-      <c r="C113" s="12">
+      <c r="C113" s="9">
+        <f t="shared" si="10"/>
+        <v>3252.8333333333335</v>
+      </c>
+      <c r="D113" s="11">
+        <f t="shared" si="6"/>
+        <v>253.16666666666652</v>
+      </c>
+      <c r="E113" s="11">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F113" s="11">
+        <f t="shared" si="7"/>
+        <v>-114.00607638888903</v>
+      </c>
+      <c r="G113" s="11">
         <f t="shared" si="8"/>
-        <v>3252.8333333333335</v>
-      </c>
-      <c r="D113" s="13">
+        <v>3138.8272569444443</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A114" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114" s="7">
+        <f t="shared" si="10"/>
+        <v>3274</v>
+      </c>
+      <c r="C114" s="9">
+        <f t="shared" si="10"/>
+        <v>3228.0416666666665</v>
+      </c>
+      <c r="D114" s="11">
+        <f t="shared" si="6"/>
+        <v>45.958333333333485</v>
+      </c>
+      <c r="E114" s="11">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F114" s="11">
+        <f t="shared" si="7"/>
+        <v>10.452256944444457</v>
+      </c>
+      <c r="G114" s="11">
         <f t="shared" si="8"/>
-        <v>253.16666666666652</v>
-      </c>
-      <c r="E113" s="14">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F113" s="14">
-        <f t="shared" si="5"/>
-        <v>-114.00607638888903</v>
-      </c>
-      <c r="G113" s="14">
-        <f t="shared" si="6"/>
-        <v>3138.8272569444443</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A114" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B114" s="10">
-        <f t="shared" si="8"/>
-        <v>3274</v>
-      </c>
-      <c r="C114" s="12">
-        <f t="shared" si="8"/>
-        <v>3228.0416666666665</v>
-      </c>
-      <c r="D114" s="13">
-        <f t="shared" si="8"/>
-        <v>45.958333333333485</v>
-      </c>
-      <c r="E114" s="14">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F114" s="14">
-        <f t="shared" si="5"/>
-        <v>10.452256944444457</v>
-      </c>
-      <c r="G114" s="14">
-        <f t="shared" si="6"/>
         <v>3238.4939236111109</v>
       </c>
       <c r="H114" s="1"/>
@@ -5915,30 +5900,30 @@
       <c r="M114" s="1"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A115" s="9" t="s">
+      <c r="A115" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="7">
+        <f t="shared" si="10"/>
+        <v>3228</v>
+      </c>
+      <c r="C115" s="9">
+        <f t="shared" si="10"/>
+        <v>3248.2083333333335</v>
+      </c>
+      <c r="D115" s="11">
+        <f t="shared" si="6"/>
+        <v>-20.208333333333485</v>
+      </c>
+      <c r="E115" s="11">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F115" s="11">
+        <f t="shared" si="7"/>
+        <v>42.546006944444343</v>
+      </c>
+      <c r="G115" s="11">
         <f t="shared" si="8"/>
-        <v>3228</v>
-      </c>
-      <c r="C115" s="12">
-        <f t="shared" si="8"/>
-        <v>3248.2083333333335</v>
-      </c>
-      <c r="D115" s="13">
-        <f t="shared" si="8"/>
-        <v>-20.208333333333485</v>
-      </c>
-      <c r="E115" s="14">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F115" s="14">
-        <f t="shared" si="5"/>
-        <v>42.546006944444343</v>
-      </c>
-      <c r="G115" s="14">
-        <f t="shared" si="6"/>
         <v>3290.7543402777778</v>
       </c>
       <c r="H115" s="1"/>
@@ -5950,676 +5935,676 @@
       <c r="N115" s="1"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A116" s="9" t="s">
+      <c r="A116" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B116" s="10">
-        <f t="shared" si="8"/>
+      <c r="B116" s="7">
+        <f t="shared" si="10"/>
         <v>2895</v>
       </c>
-      <c r="C116" s="12">
-        <f t="shared" si="8"/>
+      <c r="C116" s="9">
+        <f t="shared" si="10"/>
         <v>3294.2916666666665</v>
       </c>
-      <c r="D116" s="13">
-        <f t="shared" si="8"/>
+      <c r="D116" s="11">
+        <f t="shared" si="6"/>
         <v>-399.29166666666652</v>
       </c>
-      <c r="E116" s="14" cm="1">
+      <c r="E116" s="11" cm="1">
         <f t="array" ref="E116:E127">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F116" s="14">
-        <f t="shared" si="5"/>
+      <c r="F116" s="11">
+        <f t="shared" si="7"/>
         <v>-54.068576388888687</v>
       </c>
-      <c r="G116" s="14">
+      <c r="G116" s="11">
+        <f t="shared" si="8"/>
+        <v>3240.2230902777778</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A117" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B117" s="7">
+        <f t="shared" si="10"/>
+        <v>2883</v>
+      </c>
+      <c r="C117" s="9">
+        <f t="shared" si="10"/>
+        <v>3340.3333333333335</v>
+      </c>
+      <c r="D117" s="11">
         <f t="shared" si="6"/>
-        <v>3240.2230902777778</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A117" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B117" s="10">
+        <v>-457.33333333333348</v>
+      </c>
+      <c r="E117" s="11">
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="F117" s="11">
+        <f t="shared" si="7"/>
+        <v>233.4418402777776</v>
+      </c>
+      <c r="G117" s="11">
         <f t="shared" si="8"/>
-        <v>2883</v>
-      </c>
-      <c r="C117" s="12">
+        <v>3573.7751736111113</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A118" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B118" s="7">
+        <f t="shared" si="10"/>
+        <v>2850</v>
+      </c>
+      <c r="C118" s="9">
+        <f t="shared" si="10"/>
+        <v>3384.6666666666665</v>
+      </c>
+      <c r="D118" s="11">
+        <f t="shared" si="6"/>
+        <v>-534.66666666666652</v>
+      </c>
+      <c r="E118" s="11">
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="F118" s="11">
+        <f t="shared" si="7"/>
+        <v>-169.31857638888869</v>
+      </c>
+      <c r="G118" s="11">
         <f t="shared" si="8"/>
-        <v>3340.3333333333335</v>
-      </c>
-      <c r="D117" s="13">
+        <v>3215.3480902777778</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A119" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" s="7">
+        <f t="shared" si="10"/>
+        <v>2555</v>
+      </c>
+      <c r="C119" s="9">
+        <f t="shared" si="10"/>
+        <v>3433.5416666666665</v>
+      </c>
+      <c r="D119" s="11">
+        <f t="shared" si="6"/>
+        <v>-878.54166666666652</v>
+      </c>
+      <c r="E119" s="11">
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F119" s="11">
+        <f t="shared" si="7"/>
+        <v>-538.97482638888891</v>
+      </c>
+      <c r="G119" s="11">
         <f t="shared" si="8"/>
-        <v>-457.33333333333348</v>
-      </c>
-      <c r="E117" s="14">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F117" s="14">
-        <f t="shared" si="5"/>
-        <v>233.4418402777776</v>
-      </c>
-      <c r="G117" s="14">
+        <v>2894.5668402777774</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A120" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120" s="7">
+        <f t="shared" si="10"/>
+        <v>3346</v>
+      </c>
+      <c r="C120" s="9">
+        <f t="shared" si="10"/>
+        <v>3481.2916666666665</v>
+      </c>
+      <c r="D120" s="11">
         <f t="shared" si="6"/>
-        <v>3573.7751736111113</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A118" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B118" s="10">
+        <v>-135.29166666666652</v>
+      </c>
+      <c r="E120" s="11">
+        <v>101.37065972222229</v>
+      </c>
+      <c r="F120" s="11">
+        <f t="shared" si="7"/>
+        <v>-236.6623263888888</v>
+      </c>
+      <c r="G120" s="11">
         <f t="shared" si="8"/>
-        <v>2850</v>
-      </c>
-      <c r="C118" s="12">
+        <v>3244.6293402777778</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A121" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B121" s="7">
+        <f t="shared" si="10"/>
+        <v>4004</v>
+      </c>
+      <c r="C121" s="9">
+        <f t="shared" si="10"/>
+        <v>3514.8333333333335</v>
+      </c>
+      <c r="D121" s="11">
+        <f t="shared" si="6"/>
+        <v>489.16666666666652</v>
+      </c>
+      <c r="E121" s="11">
+        <v>282.49565972222217</v>
+      </c>
+      <c r="F121" s="11">
+        <f t="shared" si="7"/>
+        <v>206.67100694444434</v>
+      </c>
+      <c r="G121" s="11">
         <f t="shared" si="8"/>
-        <v>3384.6666666666665</v>
-      </c>
-      <c r="D118" s="13">
+        <v>3721.5043402777778</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A122" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B122" s="7">
+        <f t="shared" si="10"/>
+        <v>4078</v>
+      </c>
+      <c r="C122" s="9">
+        <f t="shared" si="10"/>
+        <v>3549.875</v>
+      </c>
+      <c r="D122" s="11">
+        <f t="shared" si="6"/>
+        <v>528.125</v>
+      </c>
+      <c r="E122" s="11">
+        <v>366.9435763888888</v>
+      </c>
+      <c r="F122" s="11">
+        <f t="shared" si="7"/>
+        <v>161.1814236111112</v>
+      </c>
+      <c r="G122" s="11">
         <f t="shared" si="8"/>
-        <v>-534.66666666666652</v>
-      </c>
-      <c r="E118" s="14">
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="F118" s="14">
-        <f t="shared" si="5"/>
-        <v>-169.31857638888869</v>
-      </c>
-      <c r="G118" s="14">
+        <v>3711.0564236111113</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A123" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B123" s="7">
+        <f t="shared" si="10"/>
+        <v>4199</v>
+      </c>
+      <c r="C123" s="9">
+        <f t="shared" si="10"/>
+        <v>3567.7083333333335</v>
+      </c>
+      <c r="D123" s="11">
         <f t="shared" si="6"/>
-        <v>3215.3480902777778</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A119" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B119" s="10">
+        <v>631.29166666666652</v>
+      </c>
+      <c r="E123" s="11">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F123" s="11">
+        <f t="shared" si="7"/>
+        <v>304.76475694444434</v>
+      </c>
+      <c r="G123" s="11">
         <f t="shared" si="8"/>
-        <v>2555</v>
-      </c>
-      <c r="C119" s="12">
+        <v>3872.4730902777778</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A124" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" s="7">
+        <f t="shared" si="10"/>
+        <v>4053</v>
+      </c>
+      <c r="C124" s="9">
+        <f t="shared" si="10"/>
+        <v>3590.6666666666665</v>
+      </c>
+      <c r="D124" s="11">
+        <f t="shared" si="6"/>
+        <v>462.33333333333348</v>
+      </c>
+      <c r="E124" s="11">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F124" s="11">
+        <f t="shared" si="7"/>
+        <v>138.68142361111131</v>
+      </c>
+      <c r="G124" s="11">
         <f t="shared" si="8"/>
-        <v>3433.5416666666665</v>
-      </c>
-      <c r="D119" s="13">
+        <v>3729.3480902777778</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A125" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B125" s="7">
+        <f t="shared" si="10"/>
+        <v>4169</v>
+      </c>
+      <c r="C125" s="9">
+        <f t="shared" si="10"/>
+        <v>3672.125</v>
+      </c>
+      <c r="D125" s="11">
+        <f t="shared" si="6"/>
+        <v>496.875</v>
+      </c>
+      <c r="E125" s="11">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F125" s="11">
+        <f t="shared" si="7"/>
+        <v>129.70225694444446</v>
+      </c>
+      <c r="G125" s="11">
         <f t="shared" si="8"/>
-        <v>-878.54166666666652</v>
-      </c>
-      <c r="E119" s="14">
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F119" s="14">
-        <f t="shared" si="5"/>
-        <v>-538.97482638888891</v>
-      </c>
-      <c r="G119" s="14">
+        <v>3801.8272569444443</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A126" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126" s="7">
+        <f t="shared" si="10"/>
+        <v>3757</v>
+      </c>
+      <c r="C126" s="9">
+        <f t="shared" si="10"/>
+        <v>3758.1666666666665</v>
+      </c>
+      <c r="D126" s="11">
         <f t="shared" si="6"/>
-        <v>2894.5668402777774</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A120" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B120" s="10">
+        <v>-1.1666666666665151</v>
+      </c>
+      <c r="E126" s="11">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F126" s="11">
+        <f t="shared" si="7"/>
+        <v>-36.672743055555543</v>
+      </c>
+      <c r="G126" s="11">
         <f t="shared" si="8"/>
-        <v>3346</v>
-      </c>
-      <c r="C120" s="12">
+        <v>3721.4939236111109</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A127" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B127" s="7">
+        <f t="shared" si="10"/>
+        <v>3550</v>
+      </c>
+      <c r="C127" s="9">
+        <f t="shared" si="10"/>
+        <v>3793.7916666666665</v>
+      </c>
+      <c r="D127" s="11">
+        <f t="shared" si="6"/>
+        <v>-243.79166666666652</v>
+      </c>
+      <c r="E127" s="11">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F127" s="11">
+        <f t="shared" si="7"/>
+        <v>-181.03732638888869</v>
+      </c>
+      <c r="G127" s="11">
         <f t="shared" si="8"/>
-        <v>3481.2916666666665</v>
-      </c>
-      <c r="D120" s="13">
-        <f t="shared" si="8"/>
-        <v>-135.29166666666652</v>
-      </c>
-      <c r="E120" s="14">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F120" s="14">
-        <f t="shared" si="5"/>
-        <v>-236.6623263888888</v>
-      </c>
-      <c r="G120" s="14">
+        <v>3612.7543402777778</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A128" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B128" s="7">
+        <f t="shared" si="10"/>
+        <v>3414</v>
+      </c>
+      <c r="C128" s="9">
+        <f t="shared" si="10"/>
+        <v>3804.8333333333335</v>
+      </c>
+      <c r="D128" s="11">
         <f t="shared" si="6"/>
-        <v>3244.6293402777778</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A121" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B121" s="10">
-        <f t="shared" si="8"/>
-        <v>4004</v>
-      </c>
-      <c r="C121" s="12">
-        <f t="shared" si="8"/>
-        <v>3514.8333333333335</v>
-      </c>
-      <c r="D121" s="13">
-        <f t="shared" si="8"/>
-        <v>489.16666666666652</v>
-      </c>
-      <c r="E121" s="14">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F121" s="14">
-        <f t="shared" si="5"/>
-        <v>206.67100694444434</v>
-      </c>
-      <c r="G121" s="14">
-        <f t="shared" si="6"/>
-        <v>3721.5043402777778</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A122" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B122" s="10">
-        <f t="shared" si="8"/>
-        <v>4078</v>
-      </c>
-      <c r="C122" s="12">
-        <f t="shared" si="8"/>
-        <v>3549.875</v>
-      </c>
-      <c r="D122" s="13">
-        <f t="shared" si="8"/>
-        <v>528.125</v>
-      </c>
-      <c r="E122" s="14">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F122" s="14">
-        <f t="shared" si="5"/>
-        <v>161.1814236111112</v>
-      </c>
-      <c r="G122" s="14">
-        <f t="shared" si="6"/>
-        <v>3711.0564236111113</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A123" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B123" s="10">
-        <f t="shared" si="8"/>
-        <v>4199</v>
-      </c>
-      <c r="C123" s="12">
-        <f t="shared" si="8"/>
-        <v>3567.7083333333335</v>
-      </c>
-      <c r="D123" s="13">
-        <f t="shared" si="8"/>
-        <v>631.29166666666652</v>
-      </c>
-      <c r="E123" s="14">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F123" s="14">
-        <f t="shared" si="5"/>
-        <v>304.76475694444434</v>
-      </c>
-      <c r="G123" s="14">
-        <f t="shared" si="6"/>
-        <v>3872.4730902777778</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A124" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B124" s="10">
-        <f t="shared" si="8"/>
-        <v>4053</v>
-      </c>
-      <c r="C124" s="12">
-        <f t="shared" si="8"/>
-        <v>3590.6666666666665</v>
-      </c>
-      <c r="D124" s="13">
-        <f t="shared" si="8"/>
-        <v>462.33333333333348</v>
-      </c>
-      <c r="E124" s="14">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F124" s="14">
-        <f t="shared" si="5"/>
-        <v>138.68142361111131</v>
-      </c>
-      <c r="G124" s="14">
-        <f t="shared" si="6"/>
-        <v>3729.3480902777778</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A125" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B125" s="10">
-        <f t="shared" si="8"/>
-        <v>4169</v>
-      </c>
-      <c r="C125" s="12">
-        <f t="shared" si="8"/>
-        <v>3672.125</v>
-      </c>
-      <c r="D125" s="13">
-        <f t="shared" si="8"/>
-        <v>496.875</v>
-      </c>
-      <c r="E125" s="14">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F125" s="14">
-        <f t="shared" si="5"/>
-        <v>129.70225694444446</v>
-      </c>
-      <c r="G125" s="14">
-        <f t="shared" si="6"/>
-        <v>3801.8272569444443</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A126" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B126" s="10">
-        <f t="shared" si="8"/>
-        <v>3757</v>
-      </c>
-      <c r="C126" s="12">
-        <f t="shared" si="8"/>
-        <v>3758.1666666666665</v>
-      </c>
-      <c r="D126" s="13">
-        <f t="shared" si="8"/>
-        <v>-1.1666666666665151</v>
-      </c>
-      <c r="E126" s="14">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F126" s="14">
-        <f t="shared" si="5"/>
-        <v>-36.672743055555543</v>
-      </c>
-      <c r="G126" s="14">
-        <f t="shared" si="6"/>
-        <v>3721.4939236111109</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A127" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B127" s="10">
-        <f t="shared" si="8"/>
-        <v>3550</v>
-      </c>
-      <c r="C127" s="12">
-        <f t="shared" si="8"/>
-        <v>3793.7916666666665</v>
-      </c>
-      <c r="D127" s="13">
-        <f t="shared" si="8"/>
-        <v>-243.79166666666652</v>
-      </c>
-      <c r="E127" s="14">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F127" s="14">
-        <f t="shared" si="5"/>
-        <v>-181.03732638888869</v>
-      </c>
-      <c r="G127" s="14">
-        <f t="shared" si="6"/>
-        <v>3612.7543402777778</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A128" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B128" s="10">
-        <f t="shared" si="8"/>
-        <v>3414</v>
-      </c>
-      <c r="C128" s="12">
-        <f t="shared" si="8"/>
-        <v>3804.8333333333335</v>
-      </c>
-      <c r="D128" s="13">
-        <f t="shared" si="8"/>
         <v>-390.83333333333348</v>
       </c>
-      <c r="E128" s="14" cm="1">
+      <c r="E128" s="11" cm="1">
         <f t="array" ref="E128:E139">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
-      <c r="F128" s="14">
-        <f t="shared" si="5"/>
+      <c r="F128" s="11">
+        <f t="shared" si="7"/>
         <v>-45.610243055555657</v>
       </c>
-      <c r="G128" s="14">
+      <c r="G128" s="11">
+        <f t="shared" si="8"/>
+        <v>3759.2230902777778</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B129" s="7">
+        <f t="shared" ref="B129:D139" si="11">B52</f>
+        <v>2792</v>
+      </c>
+      <c r="C129" s="9">
+        <f t="shared" si="11"/>
+        <v>3816.625</v>
+      </c>
+      <c r="D129" s="11">
         <f t="shared" si="6"/>
-        <v>3759.2230902777778</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B129" s="10">
-        <f t="shared" ref="B129:D139" si="9">B52</f>
-        <v>2792</v>
-      </c>
-      <c r="C129" s="12">
-        <f t="shared" si="9"/>
-        <v>3816.625</v>
-      </c>
-      <c r="D129" s="13">
-        <f t="shared" si="9"/>
         <v>-1024.625</v>
       </c>
-      <c r="E129" s="14">
+      <c r="E129" s="11">
         <v>-690.77517361111109</v>
       </c>
-      <c r="F129" s="14">
-        <f t="shared" si="5"/>
+      <c r="F129" s="11">
+        <f t="shared" si="7"/>
         <v>-333.84982638888891</v>
       </c>
-      <c r="G129" s="14">
+      <c r="G129" s="11">
+        <f t="shared" si="8"/>
+        <v>3482.7751736111113</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A130" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B130" s="7">
+        <f t="shared" si="11"/>
+        <v>3492</v>
+      </c>
+      <c r="C130" s="9">
+        <f t="shared" si="11"/>
+        <v>3830.9583333333335</v>
+      </c>
+      <c r="D130" s="11">
         <f t="shared" si="6"/>
-        <v>3482.7751736111113</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A130" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B130" s="10">
-        <f t="shared" si="9"/>
-        <v>3492</v>
-      </c>
-      <c r="C130" s="12">
-        <f t="shared" si="9"/>
-        <v>3830.9583333333335</v>
-      </c>
-      <c r="D130" s="13">
-        <f t="shared" si="9"/>
         <v>-338.95833333333348</v>
       </c>
-      <c r="E130" s="14">
+      <c r="E130" s="11">
         <v>-365.34809027777783</v>
       </c>
-      <c r="F130" s="14">
-        <f t="shared" si="5"/>
+      <c r="F130" s="11">
+        <f t="shared" si="7"/>
         <v>26.389756944444343</v>
       </c>
-      <c r="G130" s="14">
+      <c r="G130" s="11">
+        <f t="shared" si="8"/>
+        <v>3857.3480902777778</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A131" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B131" s="7">
+        <f t="shared" si="11"/>
+        <v>3868</v>
+      </c>
+      <c r="C131" s="9">
+        <f t="shared" si="11"/>
+        <v>3853.2916666666665</v>
+      </c>
+      <c r="D131" s="11">
         <f t="shared" si="6"/>
-        <v>3857.3480902777778</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A131" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B131" s="10">
-        <f t="shared" si="9"/>
-        <v>3868</v>
-      </c>
-      <c r="C131" s="12">
-        <f t="shared" si="9"/>
-        <v>3853.2916666666665</v>
-      </c>
-      <c r="D131" s="13">
-        <f t="shared" si="9"/>
         <v>14.708333333333485</v>
       </c>
-      <c r="E131" s="14">
+      <c r="E131" s="11">
         <v>-339.5668402777776</v>
       </c>
-      <c r="F131" s="14">
-        <f t="shared" si="5"/>
+      <c r="F131" s="11">
+        <f t="shared" si="7"/>
         <v>354.27517361111109</v>
       </c>
-      <c r="G131" s="14">
+      <c r="G131" s="11">
+        <f t="shared" si="8"/>
+        <v>4207.5668402777774</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B132" s="7">
+        <f t="shared" si="11"/>
+        <v>4098</v>
+      </c>
+      <c r="C132" s="9">
+        <f t="shared" si="11"/>
+        <v>3875.5</v>
+      </c>
+      <c r="D132" s="11">
         <f t="shared" si="6"/>
-        <v>4207.5668402777774</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B132" s="10">
-        <f t="shared" si="9"/>
-        <v>4098</v>
-      </c>
-      <c r="C132" s="12">
-        <f t="shared" si="9"/>
-        <v>3875.5</v>
-      </c>
-      <c r="D132" s="13">
-        <f t="shared" si="9"/>
         <v>222.5</v>
       </c>
-      <c r="E132" s="14">
+      <c r="E132" s="11">
         <v>101.37065972222229</v>
       </c>
-      <c r="F132" s="14">
-        <f t="shared" si="5"/>
+      <c r="F132" s="11">
+        <f t="shared" si="7"/>
         <v>121.12934027777771</v>
       </c>
-      <c r="G132" s="14">
+      <c r="G132" s="11">
+        <f t="shared" si="8"/>
+        <v>3996.6293402777778</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A133" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B133" s="7">
+        <f t="shared" si="11"/>
+        <v>4107</v>
+      </c>
+      <c r="C133" s="9">
+        <f t="shared" si="11"/>
+        <v>3899.8333333333335</v>
+      </c>
+      <c r="D133" s="11">
         <f t="shared" si="6"/>
-        <v>3996.6293402777778</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B133" s="10">
-        <f t="shared" si="9"/>
-        <v>4107</v>
-      </c>
-      <c r="C133" s="12">
-        <f t="shared" si="9"/>
-        <v>3899.8333333333335</v>
-      </c>
-      <c r="D133" s="13">
-        <f t="shared" si="9"/>
         <v>207.16666666666652</v>
       </c>
-      <c r="E133" s="14">
+      <c r="E133" s="11">
         <v>282.49565972222217</v>
       </c>
-      <c r="F133" s="14">
-        <f t="shared" si="5"/>
+      <c r="F133" s="11">
+        <f t="shared" si="7"/>
         <v>-75.328993055555657</v>
       </c>
-      <c r="G133" s="14">
+      <c r="G133" s="11">
+        <f t="shared" si="8"/>
+        <v>3824.5043402777778</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A134" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B134" s="7">
+        <f t="shared" si="11"/>
+        <v>4240</v>
+      </c>
+      <c r="C134" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>NA</v>
+      </c>
+      <c r="D134" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>3824.5043402777778</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A134" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B134" s="10">
-        <f t="shared" si="9"/>
-        <v>4240</v>
-      </c>
-      <c r="C134" s="10" t="str">
-        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D134" s="11" t="str">
-        <f t="shared" si="9"/>
+      <c r="E134" s="11">
+        <v>366.9435763888888</v>
+      </c>
+      <c r="F134" s="11" t="str">
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
-      <c r="E134" s="14">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F134" s="14" t="str">
-        <f t="shared" si="5"/>
+      <c r="G134" s="11">
+        <f t="shared" si="8"/>
+        <v>3873.0564236111113</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B135" s="7">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="C135" s="7" t="str">
+        <f t="shared" si="11"/>
         <v>NA</v>
       </c>
-      <c r="G134" s="14">
+      <c r="D135" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>3873.0564236111113</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B135" s="10">
-        <f t="shared" si="9"/>
-        <v>4320</v>
-      </c>
-      <c r="C135" s="10" t="str">
-        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D135" s="11" t="str">
-        <f t="shared" si="9"/>
+      <c r="E135" s="11">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F135" s="11" t="str">
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
-      <c r="E135" s="14">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F135" s="14" t="str">
-        <f t="shared" si="5"/>
+      <c r="G135" s="11">
+        <f t="shared" si="8"/>
+        <v>3993.4730902777778</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B136" s="7">
+        <f t="shared" si="11"/>
+        <v>4276</v>
+      </c>
+      <c r="C136" s="7" t="str">
+        <f t="shared" si="11"/>
         <v>NA</v>
       </c>
-      <c r="G135" s="14">
+      <c r="D136" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>3993.4730902777778</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A136" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B136" s="10">
-        <f t="shared" si="9"/>
-        <v>4276</v>
-      </c>
-      <c r="C136" s="10" t="str">
-        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D136" s="11" t="str">
-        <f t="shared" si="9"/>
+      <c r="E136" s="11">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F136" s="11" t="str">
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
-      <c r="E136" s="14">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F136" s="14" t="str">
-        <f t="shared" si="5"/>
+      <c r="G136" s="11">
+        <f t="shared" si="8"/>
+        <v>3952.3480902777778</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B137" s="7">
+        <f t="shared" si="11"/>
+        <v>4482</v>
+      </c>
+      <c r="C137" s="7" t="str">
+        <f t="shared" si="11"/>
         <v>NA</v>
       </c>
-      <c r="G136" s="14">
+      <c r="D137" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>3952.3480902777778</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B137" s="10">
-        <f t="shared" si="9"/>
-        <v>4482</v>
-      </c>
-      <c r="C137" s="10" t="str">
-        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D137" s="11" t="str">
-        <f t="shared" si="9"/>
+      <c r="E137" s="11">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F137" s="11" t="str">
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
-      <c r="E137" s="14">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F137" s="14" t="str">
-        <f t="shared" si="5"/>
+      <c r="G137" s="11">
+        <f t="shared" si="8"/>
+        <v>4114.8272569444443</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A138" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B138" s="7">
+        <f t="shared" si="11"/>
+        <v>3977</v>
+      </c>
+      <c r="C138" s="7" t="str">
+        <f t="shared" si="11"/>
         <v>NA</v>
       </c>
-      <c r="G137" s="14">
+      <c r="D138" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>4114.8272569444443</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A138" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B138" s="10">
-        <f t="shared" si="9"/>
-        <v>3977</v>
-      </c>
-      <c r="C138" s="10" t="str">
-        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D138" s="11" t="str">
-        <f t="shared" si="9"/>
+      <c r="E138" s="11">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F138" s="11" t="str">
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
-      <c r="E138" s="14">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F138" s="14" t="str">
-        <f t="shared" si="5"/>
+      <c r="G138" s="11">
+        <f t="shared" si="8"/>
+        <v>3941.4939236111109</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A139" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B139" s="13">
+        <f t="shared" si="11"/>
+        <v>3914</v>
+      </c>
+      <c r="C139" s="13" t="str">
+        <f t="shared" si="11"/>
         <v>NA</v>
       </c>
-      <c r="G138" s="14">
+      <c r="D139" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>3941.4939236111109</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A139" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B139" s="16">
-        <f t="shared" si="9"/>
-        <v>3914</v>
-      </c>
-      <c r="C139" s="16" t="str">
-        <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="D139" s="40" t="str">
-        <f t="shared" si="9"/>
+      <c r="E139" s="11">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F139" s="11" t="str">
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
-      <c r="E139" s="14">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F139" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>NA</v>
-      </c>
-      <c r="G139" s="14">
-        <f t="shared" si="6"/>
+      <c r="G139" s="11">
+        <f t="shared" si="8"/>
         <v>3976.7543402777778</v>
       </c>
     </row>
@@ -6637,23 +6622,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -6848,32 +6816,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6890,4 +6850,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/handouts/chapter_1_4_handout_key.xlsx
+++ b/docs/handouts/chapter_1_4_handout_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BF4CA8-18C5-43EE-9812-55BD45BEF5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE0197B-CDB7-490D-9150-0FD5962D45EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17745" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Key" sheetId="3" r:id="rId1"/>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="84">
   <si>
     <t>Month</t>
   </si>
@@ -605,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -701,6 +701,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2172,7 +2181,7 @@
                       <m:accPr>
                         <m:chr m:val="̅"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2345,7 +2354,7 @@
                     <m:accPr>
                       <m:chr m:val="̿"/>
                       <m:ctrlPr>
-                        <a:rPr lang="en-US" sz="1400" i="1">
+                        <a:rPr lang="en-US" sz="1400" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
                       </m:ctrlPr>
@@ -3616,6 +3625,7 @@
         <v>3351.5833333333335</v>
       </c>
       <c r="D9" s="10">
+        <f>B9-C9</f>
         <v>378.41666666666652</v>
       </c>
     </row>
@@ -3630,8 +3640,8 @@
         <f t="shared" ref="C10:C56" si="0">(0.5*B4+SUM(B5:B15)+0.5*B16)/12</f>
         <v>3350</v>
       </c>
-      <c r="D10" s="11">
-        <f>IFERROR(B10-C10, "NA")</f>
+      <c r="D10" s="10">
+        <f t="shared" ref="D10:D14" si="1">B10-C10</f>
         <v>59</v>
       </c>
     </row>
@@ -3646,8 +3656,8 @@
         <f t="shared" si="0"/>
         <v>3343.2083333333335</v>
       </c>
-      <c r="D11" s="11">
-        <f t="shared" ref="D11:D62" si="1">IFERROR(B11-C11, "NA")</f>
+      <c r="D11" s="10">
+        <f t="shared" si="1"/>
         <v>228.79166666666652</v>
       </c>
     </row>
@@ -3662,7 +3672,7 @@
         <f t="shared" si="0"/>
         <v>3326.2083333333335</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f t="shared" si="1"/>
         <v>302.79166666666652</v>
       </c>
@@ -3678,7 +3688,7 @@
         <f t="shared" si="0"/>
         <v>3316.5416666666665</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f t="shared" si="1"/>
         <v>91.458333333333485</v>
       </c>
@@ -3694,7 +3704,7 @@
         <f t="shared" si="0"/>
         <v>3318.5833333333335</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f t="shared" si="1"/>
         <v>72.416666666666515</v>
       </c>
@@ -3711,7 +3721,7 @@
         <v>3312.0833333333335</v>
       </c>
       <c r="D15" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D15:D56" si="2">B15-C15</f>
         <v>-302.08333333333348</v>
       </c>
     </row>
@@ -3727,7 +3737,7 @@
         <v>3308.0416666666665</v>
       </c>
       <c r="D16" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-574.04166666666652</v>
       </c>
     </row>
@@ -3743,7 +3753,7 @@
         <v>3311.7083333333335</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-296.70833333333348</v>
       </c>
     </row>
@@ -3759,7 +3769,7 @@
         <v>3313.1666666666665</v>
       </c>
       <c r="D18" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-334.16666666666652</v>
       </c>
     </row>
@@ -3775,7 +3785,7 @@
         <v>3307.75</v>
       </c>
       <c r="D19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>135.25</v>
       </c>
     </row>
@@ -3791,7 +3801,7 @@
         <v>3292.4166666666665</v>
       </c>
       <c r="D20" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>221.58333333333348</v>
       </c>
     </row>
@@ -3807,7 +3817,7 @@
         <v>3281.0833333333335</v>
       </c>
       <c r="D21" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>270.91666666666652</v>
       </c>
     </row>
@@ -3823,7 +3833,7 @@
         <v>3270.2083333333335</v>
       </c>
       <c r="D22" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>219.79166666666652</v>
       </c>
     </row>
@@ -3839,7 +3849,7 @@
         <v>3259.4583333333335</v>
       </c>
       <c r="D23" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>319.54166666666652</v>
       </c>
     </row>
@@ -3855,7 +3865,7 @@
         <v>3261.1666666666665</v>
       </c>
       <c r="D24" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>395.83333333333348</v>
       </c>
     </row>
@@ -3871,7 +3881,7 @@
         <v>3264.25</v>
       </c>
       <c r="D25" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-14.25</v>
       </c>
     </row>
@@ -3887,7 +3897,7 @@
         <v>3260.4583333333335</v>
       </c>
       <c r="D26" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-79.458333333333485</v>
       </c>
     </row>
@@ -3903,7 +3913,7 @@
         <v>3256.7083333333335</v>
       </c>
       <c r="D27" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-308.70833333333348</v>
       </c>
     </row>
@@ -3919,7 +3929,7 @@
         <v>3262.125</v>
       </c>
       <c r="D28" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-727.125</v>
       </c>
     </row>
@@ -3935,7 +3945,7 @@
         <v>3267.0833333333335</v>
       </c>
       <c r="D29" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-311.08333333333348</v>
       </c>
     </row>
@@ -3951,7 +3961,7 @@
         <v>3259.2916666666665</v>
       </c>
       <c r="D30" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-180.29166666666652</v>
       </c>
     </row>
@@ -3967,7 +3977,7 @@
         <v>3254</v>
       </c>
       <c r="D31" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>163</v>
       </c>
     </row>
@@ -3983,7 +3993,7 @@
         <v>3256.9583333333335</v>
       </c>
       <c r="D32" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>192.04166666666652</v>
       </c>
     </row>
@@ -3999,7 +4009,7 @@
         <v>3256.7083333333335</v>
       </c>
       <c r="D33" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>270.29166666666652</v>
       </c>
     </row>
@@ -4015,7 +4025,7 @@
         <v>3269</v>
       </c>
       <c r="D34" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>376</v>
       </c>
     </row>
@@ -4031,7 +4041,7 @@
         <v>3279.0833333333335</v>
       </c>
       <c r="D35" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>263.91666666666652</v>
       </c>
     </row>
@@ -4047,7 +4057,7 @@
         <v>3252.8333333333335</v>
       </c>
       <c r="D36" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>253.16666666666652</v>
       </c>
     </row>
@@ -4063,7 +4073,7 @@
         <v>3228.0416666666665</v>
       </c>
       <c r="D37" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>45.958333333333485</v>
       </c>
     </row>
@@ -4079,7 +4089,7 @@
         <v>3248.2083333333335</v>
       </c>
       <c r="D38" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-20.208333333333485</v>
       </c>
     </row>
@@ -4095,7 +4105,7 @@
         <v>3294.2916666666665</v>
       </c>
       <c r="D39" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-399.29166666666652</v>
       </c>
     </row>
@@ -4111,7 +4121,7 @@
         <v>3340.3333333333335</v>
       </c>
       <c r="D40" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-457.33333333333348</v>
       </c>
     </row>
@@ -4127,7 +4137,7 @@
         <v>3384.6666666666665</v>
       </c>
       <c r="D41" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-534.66666666666652</v>
       </c>
     </row>
@@ -4143,7 +4153,7 @@
         <v>3433.5416666666665</v>
       </c>
       <c r="D42" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-878.54166666666652</v>
       </c>
     </row>
@@ -4159,7 +4169,7 @@
         <v>3481.2916666666665</v>
       </c>
       <c r="D43" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-135.29166666666652</v>
       </c>
     </row>
@@ -4175,7 +4185,7 @@
         <v>3514.8333333333335</v>
       </c>
       <c r="D44" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>489.16666666666652</v>
       </c>
     </row>
@@ -4191,7 +4201,7 @@
         <v>3549.875</v>
       </c>
       <c r="D45" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>528.125</v>
       </c>
     </row>
@@ -4207,7 +4217,7 @@
         <v>3567.7083333333335</v>
       </c>
       <c r="D46" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>631.29166666666652</v>
       </c>
     </row>
@@ -4223,7 +4233,7 @@
         <v>3590.6666666666665</v>
       </c>
       <c r="D47" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>462.33333333333348</v>
       </c>
     </row>
@@ -4239,7 +4249,7 @@
         <v>3672.125</v>
       </c>
       <c r="D48" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>496.875</v>
       </c>
     </row>
@@ -4255,7 +4265,7 @@
         <v>3758.1666666666665</v>
       </c>
       <c r="D49" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.1666666666665151</v>
       </c>
     </row>
@@ -4271,7 +4281,7 @@
         <v>3793.7916666666665</v>
       </c>
       <c r="D50" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-243.79166666666652</v>
       </c>
     </row>
@@ -4287,7 +4297,7 @@
         <v>3804.8333333333335</v>
       </c>
       <c r="D51" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-390.83333333333348</v>
       </c>
     </row>
@@ -4303,7 +4313,7 @@
         <v>3816.625</v>
       </c>
       <c r="D52" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1024.625</v>
       </c>
     </row>
@@ -4319,7 +4329,7 @@
         <v>3830.9583333333335</v>
       </c>
       <c r="D53" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-338.95833333333348</v>
       </c>
     </row>
@@ -4335,7 +4345,7 @@
         <v>3853.2916666666665</v>
       </c>
       <c r="D54" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.708333333333485</v>
       </c>
     </row>
@@ -4351,7 +4361,7 @@
         <v>3875.5</v>
       </c>
       <c r="D55" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>222.5</v>
       </c>
     </row>
@@ -4367,7 +4377,7 @@
         <v>3899.8333333333335</v>
       </c>
       <c r="D56" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>207.16666666666652</v>
       </c>
     </row>
@@ -4381,9 +4391,8 @@
       <c r="C57" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D57" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
+      <c r="D57" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -4396,9 +4405,8 @@
       <c r="C58" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
+      <c r="D58" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -4411,9 +4419,8 @@
       <c r="C59" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D59" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
+      <c r="D59" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -4426,9 +4433,8 @@
       <c r="C60" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D60" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
+      <c r="D60" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -4441,9 +4447,8 @@
       <c r="C61" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D61" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
+      <c r="D61" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -4456,9 +4461,8 @@
       <c r="C62" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D62" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
+      <c r="D62" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -4765,39 +4769,39 @@
         <v>-370.35416666666674</v>
       </c>
       <c r="E73" s="11">
-        <f t="shared" ref="E73:M73" si="2">AVERAGE(E68:E72)</f>
+        <f t="shared" ref="E73:M73" si="3">AVERAGE(E68:E72)</f>
         <v>-344.57291666666652</v>
       </c>
       <c r="F73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>96.364583333333371</v>
       </c>
       <c r="G73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>277.48958333333326</v>
       </c>
       <c r="H73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>361.93749999999989</v>
       </c>
       <c r="I73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>321.52083333333326</v>
       </c>
       <c r="J73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>318.64583333333326</v>
       </c>
       <c r="K73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>362.16666666666663</v>
       </c>
       <c r="L73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30.500000000000114</v>
       </c>
       <c r="M73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-67.760416666666742</v>
       </c>
       <c r="N73" s="22">
@@ -4807,51 +4811,51 @@
     <row r="74" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="23"/>
       <c r="B74" s="24">
-        <f t="shared" ref="B74:M74" si="3">B73-$N73</f>
+        <f t="shared" ref="B74:M74" si="4">B73-$N73</f>
         <v>-345.22309027777783</v>
       </c>
       <c r="C74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-690.77517361111109</v>
       </c>
       <c r="D74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-365.34809027777783</v>
       </c>
       <c r="E74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-339.5668402777776</v>
       </c>
       <c r="F74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101.37065972222229</v>
       </c>
       <c r="G74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>282.49565972222217</v>
       </c>
       <c r="H74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>366.9435763888888</v>
       </c>
       <c r="I74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>326.52690972222217</v>
       </c>
       <c r="J74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>323.65190972222217</v>
       </c>
       <c r="K74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>367.17274305555554</v>
       </c>
       <c r="L74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>35.506076388889028</v>
       </c>
       <c r="M74" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-62.754340277777828</v>
       </c>
       <c r="N74" s="25"/>
@@ -4894,14 +4898,14 @@
         <v>3034</v>
       </c>
       <c r="C80" s="7" t="str">
-        <f t="shared" ref="C80:D80" si="4">C3</f>
+        <f t="shared" ref="C80" si="5">C3</f>
         <v>NA</v>
       </c>
-      <c r="D80" s="8" t="str">
+      <c r="D80" s="40" t="str">
         <f>IF(LEN(D3)&gt;0,D3,"")</f>
         <v>NA</v>
       </c>
-      <c r="E80" s="11" cm="1">
+      <c r="E80" s="41" cm="1">
         <f t="array" ref="E80:E91">TRANSPOSE(B$74:M$74)</f>
         <v>-345.22309027777783</v>
       </c>
@@ -4909,7 +4913,7 @@
         <f>IFERROR(B3-C3-E80, "NA")</f>
         <v>NA</v>
       </c>
-      <c r="G80" s="11">
+      <c r="G80" s="42">
         <f>B80-E80</f>
         <v>3379.2230902777778</v>
       </c>
@@ -4919,26 +4923,26 @@
         <v>5</v>
       </c>
       <c r="B81" s="7">
-        <f t="shared" ref="B81:D96" si="5">B4</f>
+        <f t="shared" ref="B81:C96" si="6">B4</f>
         <v>2748</v>
       </c>
       <c r="C81" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NA</v>
       </c>
       <c r="D81" s="8" t="str">
-        <f t="shared" ref="D81:D139" si="6">IF(LEN(D4)&gt;0,D4,"")</f>
+        <f t="shared" ref="D81:D139" si="7">IF(LEN(D4)&gt;0,D4,"")</f>
         <v>NA</v>
       </c>
       <c r="E81" s="11">
         <v>-690.77517361111109</v>
       </c>
       <c r="F81" s="7" t="str">
-        <f t="shared" ref="F81:F139" si="7">IFERROR(B4-C4-E81, "NA")</f>
+        <f t="shared" ref="F81:F139" si="8">IFERROR(B4-C4-E81, "NA")</f>
         <v>NA</v>
       </c>
       <c r="G81" s="11">
-        <f t="shared" ref="G81:G139" si="8">B81-E81</f>
+        <f t="shared" ref="G81:G139" si="9">B81-E81</f>
         <v>3438.7751736111113</v>
       </c>
     </row>
@@ -4947,26 +4951,26 @@
         <v>6</v>
       </c>
       <c r="B82" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3164</v>
       </c>
       <c r="C82" s="7" t="str">
-        <f t="shared" si="5"/>
-        <v>NA</v>
-      </c>
-      <c r="D82" s="8" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
+      <c r="D82" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>NA</v>
+      </c>
       <c r="E82" s="11">
         <v>-365.34809027777783</v>
       </c>
       <c r="F82" s="7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G82" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3529.3480902777778</v>
       </c>
     </row>
@@ -4975,26 +4979,26 @@
         <v>7</v>
       </c>
       <c r="B83" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3238</v>
       </c>
       <c r="C83" s="7" t="str">
-        <f t="shared" si="5"/>
-        <v>NA</v>
-      </c>
-      <c r="D83" s="8" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
+      <c r="D83" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>NA</v>
+      </c>
       <c r="E83" s="11">
         <v>-339.5668402777776</v>
       </c>
       <c r="F83" s="7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G83" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3577.5668402777774</v>
       </c>
     </row>
@@ -5003,26 +5007,26 @@
         <v>8</v>
       </c>
       <c r="B84" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3416</v>
       </c>
       <c r="C84" s="7" t="str">
-        <f t="shared" si="5"/>
-        <v>NA</v>
-      </c>
-      <c r="D84" s="8" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
+      <c r="D84" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>NA</v>
+      </c>
       <c r="E84" s="11">
         <v>101.37065972222229</v>
       </c>
       <c r="F84" s="7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G84" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3314.6293402777778</v>
       </c>
     </row>
@@ -5031,26 +5035,26 @@
         <v>9</v>
       </c>
       <c r="B85" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3492</v>
       </c>
       <c r="C85" s="7" t="str">
-        <f t="shared" si="5"/>
-        <v>NA</v>
-      </c>
-      <c r="D85" s="8" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
+      <c r="D85" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>NA</v>
+      </c>
       <c r="E85" s="11">
         <v>282.49565972222217</v>
       </c>
       <c r="F85" s="7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G85" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3209.5043402777778</v>
       </c>
     </row>
@@ -5059,26 +5063,26 @@
         <v>10</v>
       </c>
       <c r="B86" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3730</v>
       </c>
       <c r="C86" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3351.5833333333335</v>
       </c>
       <c r="D86" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>378.41666666666652</v>
       </c>
       <c r="E86" s="11">
         <v>366.9435763888888</v>
       </c>
-      <c r="F86" s="11">
-        <f t="shared" si="7"/>
+      <c r="F86" s="9">
+        <f t="shared" si="8"/>
         <v>11.473090277777715</v>
       </c>
       <c r="G86" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3363.0564236111113</v>
       </c>
     </row>
@@ -5087,26 +5091,26 @@
         <v>11</v>
       </c>
       <c r="B87" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3409</v>
       </c>
       <c r="C87" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3350</v>
       </c>
-      <c r="D87" s="11">
-        <f t="shared" si="6"/>
+      <c r="D87" s="10">
+        <f t="shared" si="7"/>
         <v>59</v>
       </c>
       <c r="E87" s="11">
         <v>326.52690972222217</v>
       </c>
       <c r="F87" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-267.52690972222217</v>
       </c>
       <c r="G87" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3082.4730902777778</v>
       </c>
     </row>
@@ -5115,26 +5119,26 @@
         <v>12</v>
       </c>
       <c r="B88" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3572</v>
       </c>
       <c r="C88" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3343.2083333333335</v>
       </c>
-      <c r="D88" s="11">
-        <f t="shared" si="6"/>
+      <c r="D88" s="10">
+        <f t="shared" si="7"/>
         <v>228.79166666666652</v>
       </c>
       <c r="E88" s="11">
         <v>323.65190972222217</v>
       </c>
       <c r="F88" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-94.860243055555657</v>
       </c>
       <c r="G88" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3248.3480902777778</v>
       </c>
     </row>
@@ -5143,26 +5147,26 @@
         <v>13</v>
       </c>
       <c r="B89" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3629</v>
       </c>
       <c r="C89" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3326.2083333333335</v>
       </c>
-      <c r="D89" s="11">
-        <f t="shared" si="6"/>
+      <c r="D89" s="10">
+        <f t="shared" si="7"/>
         <v>302.79166666666652</v>
       </c>
       <c r="E89" s="11">
         <v>367.17274305555554</v>
       </c>
       <c r="F89" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-64.381076388889028</v>
       </c>
       <c r="G89" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3261.8272569444443</v>
       </c>
     </row>
@@ -5171,26 +5175,26 @@
         <v>14</v>
       </c>
       <c r="B90" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3408</v>
       </c>
       <c r="C90" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3316.5416666666665</v>
       </c>
-      <c r="D90" s="11">
-        <f t="shared" si="6"/>
+      <c r="D90" s="10">
+        <f t="shared" si="7"/>
         <v>91.458333333333485</v>
       </c>
       <c r="E90" s="11">
         <v>35.506076388889028</v>
       </c>
       <c r="F90" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>55.952256944444457</v>
       </c>
       <c r="G90" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3372.4939236111109</v>
       </c>
     </row>
@@ -5199,26 +5203,26 @@
         <v>15</v>
       </c>
       <c r="B91" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3391</v>
       </c>
       <c r="C91" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3318.5833333333335</v>
       </c>
-      <c r="D91" s="11">
-        <f t="shared" si="6"/>
+      <c r="D91" s="10">
+        <f t="shared" si="7"/>
         <v>72.416666666666515</v>
       </c>
       <c r="E91" s="11">
         <v>-62.754340277777828</v>
       </c>
       <c r="F91" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>135.17100694444434</v>
       </c>
       <c r="G91" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3453.7543402777778</v>
       </c>
     </row>
@@ -5227,15 +5231,15 @@
         <v>16</v>
       </c>
       <c r="B92" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3010</v>
       </c>
       <c r="C92" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3312.0833333333335</v>
       </c>
       <c r="D92" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-302.08333333333348</v>
       </c>
       <c r="E92" s="11" cm="1">
@@ -5243,11 +5247,11 @@
         <v>-345.22309027777783</v>
       </c>
       <c r="F92" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>43.139756944444343</v>
       </c>
       <c r="G92" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3355.2230902777778</v>
       </c>
     </row>
@@ -5256,26 +5260,26 @@
         <v>17</v>
       </c>
       <c r="B93" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2734</v>
       </c>
       <c r="C93" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3308.0416666666665</v>
       </c>
       <c r="D93" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-574.04166666666652</v>
       </c>
       <c r="E93" s="11">
         <v>-690.77517361111109</v>
       </c>
       <c r="F93" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>116.73350694444457</v>
       </c>
       <c r="G93" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3424.7751736111113</v>
       </c>
     </row>
@@ -5284,26 +5288,26 @@
         <v>18</v>
       </c>
       <c r="B94" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3015</v>
       </c>
       <c r="C94" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3311.7083333333335</v>
       </c>
       <c r="D94" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-296.70833333333348</v>
       </c>
       <c r="E94" s="11">
         <v>-365.34809027777783</v>
       </c>
       <c r="F94" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>68.639756944444343</v>
       </c>
       <c r="G94" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3380.3480902777778</v>
       </c>
     </row>
@@ -5312,26 +5316,26 @@
         <v>19</v>
       </c>
       <c r="B95" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2979</v>
       </c>
       <c r="C95" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3313.1666666666665</v>
       </c>
       <c r="D95" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-334.16666666666652</v>
       </c>
       <c r="E95" s="11">
         <v>-339.5668402777776</v>
       </c>
       <c r="F95" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.4001736111110858</v>
       </c>
       <c r="G95" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3318.5668402777774</v>
       </c>
     </row>
@@ -5340,26 +5344,26 @@
         <v>20</v>
       </c>
       <c r="B96" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3443</v>
       </c>
       <c r="C96" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3307.75</v>
       </c>
       <c r="D96" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>135.25</v>
       </c>
       <c r="E96" s="11">
         <v>101.37065972222229</v>
       </c>
       <c r="F96" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>33.879340277777715</v>
       </c>
       <c r="G96" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3341.6293402777778</v>
       </c>
       <c r="H96" s="1"/>
@@ -5369,26 +5373,26 @@
         <v>21</v>
       </c>
       <c r="B97" s="7">
-        <f t="shared" ref="B97:D112" si="9">B20</f>
+        <f t="shared" ref="B97:C112" si="10">B20</f>
         <v>3514</v>
       </c>
       <c r="C97" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3292.4166666666665</v>
       </c>
       <c r="D97" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>221.58333333333348</v>
       </c>
       <c r="E97" s="11">
         <v>282.49565972222217</v>
       </c>
       <c r="F97" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-60.912326388888687</v>
       </c>
       <c r="G97" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3231.5043402777778</v>
       </c>
     </row>
@@ -5397,26 +5401,26 @@
         <v>22</v>
       </c>
       <c r="B98" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3552</v>
       </c>
       <c r="C98" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3281.0833333333335</v>
       </c>
       <c r="D98" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>270.91666666666652</v>
       </c>
       <c r="E98" s="11">
         <v>366.9435763888888</v>
       </c>
       <c r="F98" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-96.026909722222285</v>
       </c>
       <c r="G98" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3185.0564236111113</v>
       </c>
     </row>
@@ -5425,26 +5429,26 @@
         <v>23</v>
       </c>
       <c r="B99" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3490</v>
       </c>
       <c r="C99" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3270.2083333333335</v>
       </c>
       <c r="D99" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>219.79166666666652</v>
       </c>
       <c r="E99" s="11">
         <v>326.52690972222217</v>
       </c>
       <c r="F99" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-106.73524305555566</v>
       </c>
       <c r="G99" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3163.4730902777778</v>
       </c>
     </row>
@@ -5453,26 +5457,26 @@
         <v>24</v>
       </c>
       <c r="B100" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3579</v>
       </c>
       <c r="C100" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3259.4583333333335</v>
       </c>
       <c r="D100" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>319.54166666666652</v>
       </c>
       <c r="E100" s="11">
         <v>323.65190972222217</v>
       </c>
       <c r="F100" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-4.1102430555556566</v>
       </c>
       <c r="G100" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3255.3480902777778</v>
       </c>
     </row>
@@ -5481,26 +5485,26 @@
         <v>25</v>
       </c>
       <c r="B101" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3657</v>
       </c>
       <c r="C101" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3261.1666666666665</v>
       </c>
       <c r="D101" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>395.83333333333348</v>
       </c>
       <c r="E101" s="11">
         <v>367.17274305555554</v>
       </c>
       <c r="F101" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>28.660590277777942</v>
       </c>
       <c r="G101" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3289.8272569444443</v>
       </c>
     </row>
@@ -5509,26 +5513,26 @@
         <v>26</v>
       </c>
       <c r="B102" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3250</v>
       </c>
       <c r="C102" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3264.25</v>
       </c>
       <c r="D102" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-14.25</v>
       </c>
       <c r="E102" s="11">
         <v>35.506076388889028</v>
       </c>
       <c r="F102" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-49.756076388889028</v>
       </c>
       <c r="G102" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3214.4939236111109</v>
       </c>
     </row>
@@ -5537,26 +5541,26 @@
         <v>27</v>
       </c>
       <c r="B103" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3181</v>
       </c>
       <c r="C103" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3260.4583333333335</v>
       </c>
       <c r="D103" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-79.458333333333485</v>
       </c>
       <c r="E103" s="11">
         <v>-62.754340277777828</v>
       </c>
       <c r="F103" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-16.703993055555657</v>
       </c>
       <c r="G103" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3243.7543402777778</v>
       </c>
     </row>
@@ -5565,15 +5569,15 @@
         <v>28</v>
       </c>
       <c r="B104" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2948</v>
       </c>
       <c r="C104" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3256.7083333333335</v>
       </c>
       <c r="D104" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-308.70833333333348</v>
       </c>
       <c r="E104" s="11" cm="1">
@@ -5581,11 +5585,11 @@
         <v>-345.22309027777783</v>
       </c>
       <c r="F104" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>36.514756944444343</v>
       </c>
       <c r="G104" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3293.2230902777778</v>
       </c>
     </row>
@@ -5594,26 +5598,26 @@
         <v>29</v>
       </c>
       <c r="B105" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2535</v>
       </c>
       <c r="C105" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3262.125</v>
       </c>
       <c r="D105" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-727.125</v>
       </c>
       <c r="E105" s="11">
         <v>-690.77517361111109</v>
       </c>
       <c r="F105" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-36.349826388888914</v>
       </c>
       <c r="G105" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3225.7751736111113</v>
       </c>
     </row>
@@ -5622,26 +5626,26 @@
         <v>30</v>
       </c>
       <c r="B106" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2956</v>
       </c>
       <c r="C106" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3267.0833333333335</v>
       </c>
       <c r="D106" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-311.08333333333348</v>
       </c>
       <c r="E106" s="11">
         <v>-365.34809027777783</v>
       </c>
       <c r="F106" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>54.264756944444343</v>
       </c>
       <c r="G106" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3321.3480902777778</v>
       </c>
     </row>
@@ -5650,26 +5654,26 @@
         <v>31</v>
       </c>
       <c r="B107" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3079</v>
       </c>
       <c r="C107" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3259.2916666666665</v>
       </c>
       <c r="D107" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-180.29166666666652</v>
       </c>
       <c r="E107" s="11">
         <v>-339.5668402777776</v>
       </c>
       <c r="F107" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>159.27517361111109</v>
       </c>
       <c r="G107" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3418.5668402777774</v>
       </c>
     </row>
@@ -5678,26 +5682,26 @@
         <v>32</v>
       </c>
       <c r="B108" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3417</v>
       </c>
       <c r="C108" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3254</v>
       </c>
       <c r="D108" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>163</v>
       </c>
       <c r="E108" s="11">
         <v>101.37065972222229</v>
       </c>
       <c r="F108" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>61.629340277777715</v>
       </c>
       <c r="G108" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3315.6293402777778</v>
       </c>
     </row>
@@ -5706,26 +5710,26 @@
         <v>33</v>
       </c>
       <c r="B109" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3449</v>
       </c>
       <c r="C109" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3256.9583333333335</v>
       </c>
       <c r="D109" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>192.04166666666652</v>
       </c>
       <c r="E109" s="11">
         <v>282.49565972222217</v>
       </c>
       <c r="F109" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-90.453993055555657</v>
       </c>
       <c r="G109" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3166.5043402777778</v>
       </c>
       <c r="H109" s="1"/>
@@ -5740,26 +5744,26 @@
         <v>34</v>
       </c>
       <c r="B110" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3527</v>
       </c>
       <c r="C110" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3256.7083333333335</v>
       </c>
       <c r="D110" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>270.29166666666652</v>
       </c>
       <c r="E110" s="11">
         <v>366.9435763888888</v>
       </c>
       <c r="F110" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-96.651909722222285</v>
       </c>
       <c r="G110" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3160.0564236111113</v>
       </c>
       <c r="H110" s="1"/>
@@ -5774,26 +5778,26 @@
         <v>35</v>
       </c>
       <c r="B111" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3645</v>
       </c>
       <c r="C111" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3269</v>
       </c>
       <c r="D111" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>376</v>
       </c>
       <c r="E111" s="11">
         <v>326.52690972222217</v>
       </c>
       <c r="F111" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>49.473090277777828</v>
       </c>
       <c r="G111" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3318.4730902777778</v>
       </c>
       <c r="H111" s="1"/>
@@ -5808,26 +5812,26 @@
         <v>36</v>
       </c>
       <c r="B112" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3543</v>
       </c>
       <c r="C112" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3279.0833333333335</v>
       </c>
       <c r="D112" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>263.91666666666652</v>
       </c>
       <c r="E112" s="11">
         <v>323.65190972222217</v>
       </c>
       <c r="F112" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-59.735243055555657</v>
       </c>
       <c r="G112" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3219.3480902777778</v>
       </c>
       <c r="H112" s="1"/>
@@ -5842,26 +5846,26 @@
         <v>37</v>
       </c>
       <c r="B113" s="7">
-        <f t="shared" ref="B113:D128" si="10">B36</f>
+        <f t="shared" ref="B113:C128" si="11">B36</f>
         <v>3506</v>
       </c>
       <c r="C113" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3252.8333333333335</v>
       </c>
       <c r="D113" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>253.16666666666652</v>
       </c>
       <c r="E113" s="11">
         <v>367.17274305555554</v>
       </c>
       <c r="F113" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-114.00607638888903</v>
       </c>
       <c r="G113" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3138.8272569444443</v>
       </c>
     </row>
@@ -5870,26 +5874,26 @@
         <v>38</v>
       </c>
       <c r="B114" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3274</v>
       </c>
       <c r="C114" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3228.0416666666665</v>
       </c>
       <c r="D114" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>45.958333333333485</v>
       </c>
       <c r="E114" s="11">
         <v>35.506076388889028</v>
       </c>
       <c r="F114" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10.452256944444457</v>
       </c>
       <c r="G114" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3238.4939236111109</v>
       </c>
       <c r="H114" s="1"/>
@@ -5904,26 +5908,26 @@
         <v>39</v>
       </c>
       <c r="B115" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3228</v>
       </c>
       <c r="C115" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3248.2083333333335</v>
       </c>
       <c r="D115" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-20.208333333333485</v>
       </c>
       <c r="E115" s="11">
         <v>-62.754340277777828</v>
       </c>
       <c r="F115" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>42.546006944444343</v>
       </c>
       <c r="G115" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3290.7543402777778</v>
       </c>
       <c r="H115" s="1"/>
@@ -5939,15 +5943,15 @@
         <v>40</v>
       </c>
       <c r="B116" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2895</v>
       </c>
       <c r="C116" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3294.2916666666665</v>
       </c>
       <c r="D116" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-399.29166666666652</v>
       </c>
       <c r="E116" s="11" cm="1">
@@ -5955,11 +5959,11 @@
         <v>-345.22309027777783</v>
       </c>
       <c r="F116" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-54.068576388888687</v>
       </c>
       <c r="G116" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3240.2230902777778</v>
       </c>
     </row>
@@ -5968,26 +5972,26 @@
         <v>41</v>
       </c>
       <c r="B117" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2883</v>
       </c>
       <c r="C117" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3340.3333333333335</v>
       </c>
       <c r="D117" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-457.33333333333348</v>
       </c>
       <c r="E117" s="11">
         <v>-690.77517361111109</v>
       </c>
       <c r="F117" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>233.4418402777776</v>
       </c>
       <c r="G117" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3573.7751736111113</v>
       </c>
     </row>
@@ -5996,26 +6000,26 @@
         <v>42</v>
       </c>
       <c r="B118" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2850</v>
       </c>
       <c r="C118" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3384.6666666666665</v>
       </c>
       <c r="D118" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-534.66666666666652</v>
       </c>
       <c r="E118" s="11">
         <v>-365.34809027777783</v>
       </c>
       <c r="F118" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-169.31857638888869</v>
       </c>
       <c r="G118" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3215.3480902777778</v>
       </c>
     </row>
@@ -6024,26 +6028,26 @@
         <v>43</v>
       </c>
       <c r="B119" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2555</v>
       </c>
       <c r="C119" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3433.5416666666665</v>
       </c>
       <c r="D119" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-878.54166666666652</v>
       </c>
       <c r="E119" s="11">
         <v>-339.5668402777776</v>
       </c>
       <c r="F119" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-538.97482638888891</v>
       </c>
       <c r="G119" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2894.5668402777774</v>
       </c>
     </row>
@@ -6052,26 +6056,26 @@
         <v>44</v>
       </c>
       <c r="B120" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3346</v>
       </c>
       <c r="C120" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3481.2916666666665</v>
       </c>
       <c r="D120" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-135.29166666666652</v>
       </c>
       <c r="E120" s="11">
         <v>101.37065972222229</v>
       </c>
       <c r="F120" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-236.6623263888888</v>
       </c>
       <c r="G120" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3244.6293402777778</v>
       </c>
     </row>
@@ -6080,26 +6084,26 @@
         <v>45</v>
       </c>
       <c r="B121" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4004</v>
       </c>
       <c r="C121" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3514.8333333333335</v>
       </c>
       <c r="D121" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>489.16666666666652</v>
       </c>
       <c r="E121" s="11">
         <v>282.49565972222217</v>
       </c>
       <c r="F121" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>206.67100694444434</v>
       </c>
       <c r="G121" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3721.5043402777778</v>
       </c>
     </row>
@@ -6108,26 +6112,26 @@
         <v>46</v>
       </c>
       <c r="B122" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4078</v>
       </c>
       <c r="C122" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3549.875</v>
       </c>
       <c r="D122" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>528.125</v>
       </c>
       <c r="E122" s="11">
         <v>366.9435763888888</v>
       </c>
       <c r="F122" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>161.1814236111112</v>
       </c>
       <c r="G122" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3711.0564236111113</v>
       </c>
     </row>
@@ -6136,26 +6140,26 @@
         <v>47</v>
       </c>
       <c r="B123" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4199</v>
       </c>
       <c r="C123" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3567.7083333333335</v>
       </c>
       <c r="D123" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>631.29166666666652</v>
       </c>
       <c r="E123" s="11">
         <v>326.52690972222217</v>
       </c>
       <c r="F123" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>304.76475694444434</v>
       </c>
       <c r="G123" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3872.4730902777778</v>
       </c>
     </row>
@@ -6164,26 +6168,26 @@
         <v>48</v>
       </c>
       <c r="B124" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4053</v>
       </c>
       <c r="C124" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3590.6666666666665</v>
       </c>
       <c r="D124" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>462.33333333333348</v>
       </c>
       <c r="E124" s="11">
         <v>323.65190972222217</v>
       </c>
       <c r="F124" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>138.68142361111131</v>
       </c>
       <c r="G124" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3729.3480902777778</v>
       </c>
     </row>
@@ -6192,26 +6196,26 @@
         <v>49</v>
       </c>
       <c r="B125" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4169</v>
       </c>
       <c r="C125" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3672.125</v>
       </c>
       <c r="D125" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>496.875</v>
       </c>
       <c r="E125" s="11">
         <v>367.17274305555554</v>
       </c>
       <c r="F125" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>129.70225694444446</v>
       </c>
       <c r="G125" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3801.8272569444443</v>
       </c>
     </row>
@@ -6220,26 +6224,26 @@
         <v>50</v>
       </c>
       <c r="B126" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3757</v>
       </c>
       <c r="C126" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3758.1666666666665</v>
       </c>
       <c r="D126" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.1666666666665151</v>
       </c>
       <c r="E126" s="11">
         <v>35.506076388889028</v>
       </c>
       <c r="F126" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-36.672743055555543</v>
       </c>
       <c r="G126" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3721.4939236111109</v>
       </c>
     </row>
@@ -6248,26 +6252,26 @@
         <v>51</v>
       </c>
       <c r="B127" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3550</v>
       </c>
       <c r="C127" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3793.7916666666665</v>
       </c>
       <c r="D127" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-243.79166666666652</v>
       </c>
       <c r="E127" s="11">
         <v>-62.754340277777828</v>
       </c>
       <c r="F127" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-181.03732638888869</v>
       </c>
       <c r="G127" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3612.7543402777778</v>
       </c>
     </row>
@@ -6276,15 +6280,15 @@
         <v>52</v>
       </c>
       <c r="B128" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3414</v>
       </c>
       <c r="C128" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3804.8333333333335</v>
       </c>
       <c r="D128" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-390.83333333333348</v>
       </c>
       <c r="E128" s="11" cm="1">
@@ -6292,11 +6296,11 @@
         <v>-345.22309027777783</v>
       </c>
       <c r="F128" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-45.610243055555657</v>
       </c>
       <c r="G128" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3759.2230902777778</v>
       </c>
     </row>
@@ -6305,26 +6309,26 @@
         <v>53</v>
       </c>
       <c r="B129" s="7">
-        <f t="shared" ref="B129:D139" si="11">B52</f>
+        <f t="shared" ref="B129:C139" si="12">B52</f>
         <v>2792</v>
       </c>
       <c r="C129" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3816.625</v>
       </c>
       <c r="D129" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1024.625</v>
       </c>
       <c r="E129" s="11">
         <v>-690.77517361111109</v>
       </c>
       <c r="F129" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-333.84982638888891</v>
       </c>
       <c r="G129" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3482.7751736111113</v>
       </c>
     </row>
@@ -6333,26 +6337,26 @@
         <v>54</v>
       </c>
       <c r="B130" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3492</v>
       </c>
       <c r="C130" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3830.9583333333335</v>
       </c>
       <c r="D130" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-338.95833333333348</v>
       </c>
       <c r="E130" s="11">
         <v>-365.34809027777783</v>
       </c>
       <c r="F130" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>26.389756944444343</v>
       </c>
       <c r="G130" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3857.3480902777778</v>
       </c>
     </row>
@@ -6361,26 +6365,26 @@
         <v>55</v>
       </c>
       <c r="B131" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3868</v>
       </c>
       <c r="C131" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3853.2916666666665</v>
       </c>
       <c r="D131" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.708333333333485</v>
       </c>
       <c r="E131" s="11">
         <v>-339.5668402777776</v>
       </c>
       <c r="F131" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>354.27517361111109</v>
       </c>
       <c r="G131" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4207.5668402777774</v>
       </c>
     </row>
@@ -6389,26 +6393,26 @@
         <v>56</v>
       </c>
       <c r="B132" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4098</v>
       </c>
       <c r="C132" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3875.5</v>
       </c>
       <c r="D132" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>222.5</v>
       </c>
       <c r="E132" s="11">
         <v>101.37065972222229</v>
       </c>
       <c r="F132" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>121.12934027777771</v>
       </c>
       <c r="G132" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3996.6293402777778</v>
       </c>
     </row>
@@ -6417,26 +6421,26 @@
         <v>57</v>
       </c>
       <c r="B133" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4107</v>
       </c>
       <c r="C133" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3899.8333333333335</v>
       </c>
       <c r="D133" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>207.16666666666652</v>
       </c>
       <c r="E133" s="11">
         <v>282.49565972222217</v>
       </c>
       <c r="F133" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-75.328993055555657</v>
       </c>
       <c r="G133" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3824.5043402777778</v>
       </c>
     </row>
@@ -6445,26 +6449,26 @@
         <v>58</v>
       </c>
       <c r="B134" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4240</v>
       </c>
       <c r="C134" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>NA</v>
       </c>
       <c r="D134" s="11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="E134" s="11">
         <v>366.9435763888888</v>
       </c>
       <c r="F134" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G134" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3873.0564236111113</v>
       </c>
     </row>
@@ -6473,26 +6477,26 @@
         <v>59</v>
       </c>
       <c r="B135" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4320</v>
       </c>
       <c r="C135" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>NA</v>
       </c>
       <c r="D135" s="11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="E135" s="11">
         <v>326.52690972222217</v>
       </c>
       <c r="F135" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G135" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3993.4730902777778</v>
       </c>
     </row>
@@ -6501,26 +6505,26 @@
         <v>60</v>
       </c>
       <c r="B136" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4276</v>
       </c>
       <c r="C136" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>NA</v>
       </c>
       <c r="D136" s="11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="E136" s="11">
         <v>323.65190972222217</v>
       </c>
       <c r="F136" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G136" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3952.3480902777778</v>
       </c>
     </row>
@@ -6529,26 +6533,26 @@
         <v>61</v>
       </c>
       <c r="B137" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4482</v>
       </c>
       <c r="C137" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>NA</v>
       </c>
       <c r="D137" s="11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="E137" s="11">
         <v>367.17274305555554</v>
       </c>
       <c r="F137" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G137" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4114.8272569444443</v>
       </c>
     </row>
@@ -6557,26 +6561,26 @@
         <v>62</v>
       </c>
       <c r="B138" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3977</v>
       </c>
       <c r="C138" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>NA</v>
       </c>
       <c r="D138" s="11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="E138" s="11">
         <v>35.506076388889028</v>
       </c>
       <c r="F138" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G138" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3941.4939236111109</v>
       </c>
     </row>
@@ -6585,26 +6589,26 @@
         <v>63</v>
       </c>
       <c r="B139" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3914</v>
       </c>
       <c r="C139" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>NA</v>
       </c>
       <c r="D139" s="11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="E139" s="11">
         <v>-62.754340277777828</v>
       </c>
       <c r="F139" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="G139" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3976.7543402777778</v>
       </c>
     </row>
@@ -6616,8 +6620,9 @@
     <mergeCell ref="A78:G78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/docs/handouts/chapter_1_4_handout_key.xlsx
+++ b/docs/handouts/chapter_1_4_handout_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE0197B-CDB7-490D-9150-0FD5962D45EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1162387E-9CCA-4653-B29E-13156250FDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="19200" windowHeight="11170" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Key" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,20 @@
     <author>Tyson Brost</author>
   </authors>
   <commentList>
-    <comment ref="N71" authorId="0" shapeId="0" xr:uid="{7AB34930-2485-49E2-A678-E9A1E1596D84}">
+    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{CF60AC78-5442-4236-AECE-C0C7ACA4D6BF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Unadjusted monthly additive components</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N73" authorId="0" shapeId="0" xr:uid="{7AB34930-2485-49E2-A678-E9A1E1596D84}">
       <text>
         <r>
           <rPr>
@@ -54,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{CF60AC78-5442-4236-AECE-C0C7ACA4D6BF}">
+    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{24587962-40B9-471A-B152-48A295F4681E}">
       <text>
         <r>
           <rPr>
@@ -64,19 +77,6 @@
             <family val="2"/>
           </rPr>
           <t>Unadjusted monthly additive components</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A75" authorId="0" shapeId="0" xr:uid="{A19E4124-49FE-4496-96B5-9863E9772391}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color indexed="81"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Seasonally adjusted mean for each month</t>
         </r>
       </text>
     </comment>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="85">
   <si>
     <t>Month</t>
   </si>
@@ -119,250 +119,255 @@
     <t>Random</t>
   </si>
   <si>
-    <t xml:space="preserve">Seasonally Adjusted
+    <t>2017 Jan</t>
+  </si>
+  <si>
+    <t>2017 Feb</t>
+  </si>
+  <si>
+    <t>2017 Mar</t>
+  </si>
+  <si>
+    <t>2017 Apr</t>
+  </si>
+  <si>
+    <t>2017 May</t>
+  </si>
+  <si>
+    <t>2017 Jun</t>
+  </si>
+  <si>
+    <t>2017 Jul</t>
+  </si>
+  <si>
+    <t>2017 Aug</t>
+  </si>
+  <si>
+    <t>2017 Sep</t>
+  </si>
+  <si>
+    <t>2017 Oct</t>
+  </si>
+  <si>
+    <t>2017 Nov</t>
+  </si>
+  <si>
+    <t>2017 Dec</t>
+  </si>
+  <si>
+    <t>2018 Jan</t>
+  </si>
+  <si>
+    <t>2018 Feb</t>
+  </si>
+  <si>
+    <t>2018 Mar</t>
+  </si>
+  <si>
+    <t>2018 Apr</t>
+  </si>
+  <si>
+    <t>2018 May</t>
+  </si>
+  <si>
+    <t>2018 Jun</t>
+  </si>
+  <si>
+    <t>2018 Jul</t>
+  </si>
+  <si>
+    <t>2018 Aug</t>
+  </si>
+  <si>
+    <t>2018 Sep</t>
+  </si>
+  <si>
+    <t>2018 Oct</t>
+  </si>
+  <si>
+    <t>2018 Nov</t>
+  </si>
+  <si>
+    <t>2018 Dec</t>
+  </si>
+  <si>
+    <t>2019 Jan</t>
+  </si>
+  <si>
+    <t>2019 Feb</t>
+  </si>
+  <si>
+    <t>2019 Mar</t>
+  </si>
+  <si>
+    <t>2019 Apr</t>
+  </si>
+  <si>
+    <t>2019 May</t>
+  </si>
+  <si>
+    <t>2019 Jun</t>
+  </si>
+  <si>
+    <t>2019 Jul</t>
+  </si>
+  <si>
+    <t>2019 Aug</t>
+  </si>
+  <si>
+    <t>2019 Sep</t>
+  </si>
+  <si>
+    <t>2019 Oct</t>
+  </si>
+  <si>
+    <t>2019 Nov</t>
+  </si>
+  <si>
+    <t>2019 Dec</t>
+  </si>
+  <si>
+    <t>2020 Jan</t>
+  </si>
+  <si>
+    <t>2020 Feb</t>
+  </si>
+  <si>
+    <t>2020 Mar</t>
+  </si>
+  <si>
+    <t>2020 Apr</t>
+  </si>
+  <si>
+    <t>2020 May</t>
+  </si>
+  <si>
+    <t>2020 Jun</t>
+  </si>
+  <si>
+    <t>2020 Jul</t>
+  </si>
+  <si>
+    <t>2020 Aug</t>
+  </si>
+  <si>
+    <t>2020 Sep</t>
+  </si>
+  <si>
+    <t>2020 Oct</t>
+  </si>
+  <si>
+    <t>2020 Nov</t>
+  </si>
+  <si>
+    <t>2020 Dec</t>
+  </si>
+  <si>
+    <t>2021 Jan</t>
+  </si>
+  <si>
+    <t>2021 Feb</t>
+  </si>
+  <si>
+    <t>2021 Mar</t>
+  </si>
+  <si>
+    <t>2021 Apr</t>
+  </si>
+  <si>
+    <t>2021 May</t>
+  </si>
+  <si>
+    <t>2021 Jun</t>
+  </si>
+  <si>
+    <t>2021 Jul</t>
+  </si>
+  <si>
+    <t>2021 Aug</t>
+  </si>
+  <si>
+    <t>2021 Sep</t>
+  </si>
+  <si>
+    <t>2021 Oct</t>
+  </si>
+  <si>
+    <t>2021 Nov</t>
+  </si>
+  <si>
+    <t>2021 Dec</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Mean,</t>
+  </si>
+  <si>
+    <t>(Hint:  Should be close to -5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall mean, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonally 
+Adjusted
 </t>
   </si>
   <si>
-    <t>2017 Jan</t>
-  </si>
-  <si>
-    <t>2017 Feb</t>
-  </si>
-  <si>
-    <t>2017 Mar</t>
-  </si>
-  <si>
-    <t>2017 Apr</t>
-  </si>
-  <si>
-    <t>2017 May</t>
-  </si>
-  <si>
-    <t>2017 Jun</t>
-  </si>
-  <si>
-    <t>2017 Jul</t>
-  </si>
-  <si>
-    <t>2017 Aug</t>
-  </si>
-  <si>
-    <t>2017 Sep</t>
-  </si>
-  <si>
-    <t>2017 Oct</t>
-  </si>
-  <si>
-    <t>2017 Nov</t>
-  </si>
-  <si>
-    <t>2017 Dec</t>
-  </si>
-  <si>
-    <t>2018 Jan</t>
-  </si>
-  <si>
-    <t>2018 Feb</t>
-  </si>
-  <si>
-    <t>2018 Mar</t>
-  </si>
-  <si>
-    <t>2018 Apr</t>
-  </si>
-  <si>
-    <t>2018 May</t>
-  </si>
-  <si>
-    <t>2018 Jun</t>
-  </si>
-  <si>
-    <t>2018 Jul</t>
-  </si>
-  <si>
-    <t>2018 Aug</t>
-  </si>
-  <si>
-    <t>2018 Sep</t>
-  </si>
-  <si>
-    <t>2018 Oct</t>
-  </si>
-  <si>
-    <t>2018 Nov</t>
-  </si>
-  <si>
-    <t>2018 Dec</t>
-  </si>
-  <si>
-    <t>2019 Jan</t>
-  </si>
-  <si>
-    <t>2019 Feb</t>
-  </si>
-  <si>
-    <t>2019 Mar</t>
-  </si>
-  <si>
-    <t>2019 Apr</t>
-  </si>
-  <si>
-    <t>2019 May</t>
-  </si>
-  <si>
-    <t>2019 Jun</t>
-  </si>
-  <si>
-    <t>2019 Jul</t>
-  </si>
-  <si>
-    <t>2019 Aug</t>
-  </si>
-  <si>
-    <t>2019 Sep</t>
-  </si>
-  <si>
-    <t>2019 Oct</t>
-  </si>
-  <si>
-    <t>2019 Nov</t>
-  </si>
-  <si>
-    <t>2019 Dec</t>
-  </si>
-  <si>
-    <t>2020 Jan</t>
-  </si>
-  <si>
-    <t>2020 Feb</t>
-  </si>
-  <si>
-    <t>2020 Mar</t>
-  </si>
-  <si>
-    <t>2020 Apr</t>
-  </si>
-  <si>
-    <t>2020 May</t>
-  </si>
-  <si>
-    <t>2020 Jun</t>
-  </si>
-  <si>
-    <t>2020 Jul</t>
-  </si>
-  <si>
-    <t>2020 Aug</t>
-  </si>
-  <si>
-    <t>2020 Sep</t>
-  </si>
-  <si>
-    <t>2020 Oct</t>
-  </si>
-  <si>
-    <t>2020 Nov</t>
-  </si>
-  <si>
-    <t>2020 Dec</t>
-  </si>
-  <si>
-    <t>2021 Jan</t>
-  </si>
-  <si>
-    <t>2021 Feb</t>
-  </si>
-  <si>
-    <t>2021 Mar</t>
-  </si>
-  <si>
-    <t>2021 Apr</t>
-  </si>
-  <si>
-    <t>2021 May</t>
-  </si>
-  <si>
-    <t>2021 Jun</t>
-  </si>
-  <si>
-    <t>2021 Jul</t>
-  </si>
-  <si>
-    <t>2021 Aug</t>
-  </si>
-  <si>
-    <t>2021 Sep</t>
-  </si>
-  <si>
-    <t>2021 Oct</t>
-  </si>
-  <si>
-    <t>2021 Nov</t>
-  </si>
-  <si>
-    <t>2021 Dec</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>Jul</t>
-  </si>
-  <si>
-    <t>Aug</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
-    <t>Oct</t>
-  </si>
-  <si>
-    <t>Nov</t>
-  </si>
-  <si>
-    <t>Dec</t>
-  </si>
-  <si>
-    <t>Overall
-Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Table 1: Computation of the 
-Centered Moving Average,      , and the Estimated Monthly Additive Effect,</t>
-  </si>
-  <si>
-    <t>Table 2: Computation of</t>
-  </si>
-  <si>
-    <t>Mean,</t>
-  </si>
-  <si>
-    <t>Table 3: Computation of        the Random Component and the Seasonally Adjusted Time Series</t>
+    <t xml:space="preserve">Year </t>
+  </si>
+  <si>
+    <t>Table 2:  Computation of</t>
+  </si>
+  <si>
+    <t>Table 3:  Computation of the Estimate of the Random 
+Component and the Seasonally Adjusted Time Series</t>
+  </si>
+  <si>
+    <t>Table 1:  Computation of the 
+Centered Moving Average,          , and 
+the Estimated Monthly Additive Effect,</t>
   </si>
 </sst>
 </file>
@@ -409,18 +414,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -435,7 +434,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -515,50 +514,12 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -605,73 +566,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -687,29 +640,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -733,9 +677,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>295434</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>205613</xdr:rowOff>
+      <xdr:colOff>327184</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>364363</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -753,7 +697,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1130459" y="15680563"/>
+              <a:off x="1165384" y="17026763"/>
               <a:ext cx="196079" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -832,7 +776,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1130459" y="15680563"/>
+              <a:off x="1165384" y="17026763"/>
               <a:ext cx="196079" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -879,8 +823,8 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>295434</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>137033</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>283083</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187167" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -898,7 +842,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1968659" y="15618333"/>
+              <a:off x="1971834" y="16945483"/>
               <a:ext cx="187167" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -970,7 +914,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1968659" y="15618333"/>
+              <a:off x="1971834" y="16945483"/>
               <a:ext cx="187167" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1016,9 +960,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>341154</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>137033</xdr:rowOff>
+      <xdr:colOff>303054</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>270383</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -1036,7 +980,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2865279" y="15618333"/>
+              <a:off x="2830354" y="16932783"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1108,7 +1052,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2865279" y="15618333"/>
+              <a:off x="2830354" y="16932783"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1154,9 +1098,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>320040</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>269240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -1174,7 +1118,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3622040" y="15585440"/>
+              <a:off x="3590290" y="16931640"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1246,7 +1190,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3622040" y="15585440"/>
+              <a:off x="3590290" y="16931640"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1292,9 +1236,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>569754</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>205613</xdr:rowOff>
+      <xdr:colOff>315754</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>459613</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -1312,7 +1256,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5437029" y="15680563"/>
+              <a:off x="5186204" y="17122013"/>
               <a:ext cx="196079" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1391,7 +1335,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5437029" y="15680563"/>
+              <a:off x="5186204" y="17122013"/>
               <a:ext cx="196079" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1438,7 +1382,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
@@ -1641,7 +1585,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>83693</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="187167" cy="221214"/>
+    <xdr:ext cx="220509" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
@@ -1657,8 +1601,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1990249" y="667893"/>
-              <a:ext cx="187167" cy="221214"/>
+              <a:off x="1987074" y="1023493"/>
+              <a:ext cx="220509" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1689,24 +1633,61 @@
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
+                    <m:sSub>
+                      <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
                           </a:rPr>
                         </m:ctrlPr>
-                      </m:accPr>
+                      </m:sSubPr>
                       <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̂"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑚</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
                         <m:r>
                           <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>𝑚</m:t>
+                          <m:t>𝑡</m:t>
                         </m:r>
-                      </m:e>
-                    </m:acc>
+                      </m:sub>
+                    </m:sSub>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
@@ -1729,8 +1710,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1990249" y="667893"/>
-              <a:ext cx="187167" cy="221214"/>
+              <a:off x="1987074" y="1023493"/>
+              <a:ext cx="220509" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1759,10 +1740,34 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑚 ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑚 ̂</a:t>
+                <a:t>𝑡</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
@@ -1779,7 +1784,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>83693</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="120161" cy="221214"/>
+    <xdr:ext cx="163057" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
@@ -1795,8 +1800,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2811939" y="667893"/>
-              <a:ext cx="120161" cy="221214"/>
+              <a:off x="2815114" y="1023493"/>
+              <a:ext cx="163057" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1827,24 +1832,61 @@
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
+                    <m:sSub>
+                      <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
                           </a:rPr>
                         </m:ctrlPr>
-                      </m:accPr>
+                      </m:sSubPr>
                       <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̂"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑠</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
                         <m:r>
                           <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>𝑠</m:t>
+                          <m:t>𝑡</m:t>
                         </m:r>
-                      </m:e>
-                    </m:acc>
+                      </m:sub>
+                    </m:sSub>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
@@ -1867,8 +1909,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2811939" y="667893"/>
-              <a:ext cx="120161" cy="221214"/>
+              <a:off x="2815114" y="1023493"/>
+              <a:ext cx="163057" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1897,10 +1939,34 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑠 ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑠 ̂</a:t>
+                <a:t>𝑡</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
@@ -1914,7 +1980,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
@@ -1968,166 +2034,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>387985</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>153670</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="TextBox 11">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C958AE0A-781D-4922-88BE-6EDE1C063529}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="391160" y="13850620"/>
-              <a:ext cx="320040" cy="221214"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:acc>
-                          <m:accPr>
-                            <m:chr m:val="̅"/>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:accPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑠</m:t>
-                            </m:r>
-                          </m:e>
-                        </m:acc>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1400"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="TextBox 11">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C958AE0A-781D-4922-88BE-6EDE1C063529}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="391160" y="13850620"/>
-              <a:ext cx="320040" cy="221214"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑠 ̅_𝑡</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1400"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="231923"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -2145,7 +2054,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="381000" y="14151610"/>
+              <a:off x="501650" y="15161260"/>
               <a:ext cx="180819" cy="231923"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2248,7 +2157,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="381000" y="14151610"/>
+              <a:off x="501650" y="15161260"/>
               <a:ext cx="180819" cy="231923"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2278,16 +2187,10 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-US" sz="1400" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑠 ̂_𝑡 ) ̅</a:t>
+                <a:t>(𝑠 ̂_𝑡 ) ̅</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
@@ -2300,9 +2203,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>152399</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>755649</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="379575" cy="250903"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -2320,7 +2223,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10001249" y="13916025"/>
+              <a:off x="11093449" y="14712950"/>
               <a:ext cx="379575" cy="250903"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2348,63 +2251,63 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
-                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:acc>
-                    <m:accPr>
-                      <m:chr m:val="̿"/>
-                      <m:ctrlPr>
-                        <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        </a:rPr>
-                      </m:ctrlPr>
-                    </m:accPr>
-                    <m:e>
-                      <m:sSub>
-                        <m:sSubPr>
-                          <m:ctrlPr>
-                            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                            </a:rPr>
-                          </m:ctrlPr>
-                        </m:sSubPr>
-                        <m:e>
-                          <m:acc>
-                            <m:accPr>
-                              <m:chr m:val="̂"/>
-                              <m:ctrlPr>
-                                <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                </a:rPr>
-                              </m:ctrlPr>
-                            </m:accPr>
-                            <m:e>
-                              <m:r>
-                                <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                </a:rPr>
-                                <m:t>𝑠</m:t>
-                              </m:r>
-                            </m:e>
-                          </m:acc>
-                        </m:e>
-                        <m:sub>
-                          <m:r>
-                            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                            </a:rPr>
-                            <m:t>𝑡</m:t>
-                          </m:r>
-                        </m:sub>
-                      </m:sSub>
-                    </m:e>
-                  </m:acc>
-                </m:oMath>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̿"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:acc>
+                              <m:accPr>
+                                <m:chr m:val="̂"/>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:accPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑠</m:t>
+                                </m:r>
+                              </m:e>
+                            </m:acc>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                  </m:oMath>
+                </m:oMathPara>
               </a14:m>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400"/>
-                <a:t>=</a:t>
-              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2423,162 +2326,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10001249" y="13916025"/>
+              <a:off x="11093449" y="14712950"/>
               <a:ext cx="379575" cy="250903"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑠 ̂_𝑡 ) ̿</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400"/>
-                <a:t>=</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>202565</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>77470</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="TextBox 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA6F6110-F50F-4612-9089-D374F44DE0FF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1875790" y="15003145"/>
-              <a:ext cx="320040" cy="221214"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑧</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1400"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="TextBox 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA6F6110-F50F-4612-9089-D374F44DE0FF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1875790" y="15003145"/>
-              <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2610,7 +2359,7 @@
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑧_𝑡</a:t>
+                <a:t>(𝑠 ̂_𝑡 ) ̿</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
@@ -2624,7 +2373,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>243840</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2751,9 +2500,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>104934</xdr:colOff>
+      <xdr:colOff>549434</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>197993</xdr:rowOff>
+      <xdr:rowOff>356743</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187167" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -2771,7 +2520,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1778159" y="201168"/>
+              <a:off x="2225834" y="356743"/>
               <a:ext cx="187167" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2843,7 +2592,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1778159" y="201168"/>
+              <a:off x="2225834" y="356743"/>
               <a:ext cx="187167" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2888,10 +2637,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>714534</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>308134</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>388493</xdr:rowOff>
+      <xdr:rowOff>553593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -2909,7 +2658,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2387759" y="391668"/>
+              <a:off x="2835434" y="553593"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2981,7 +2730,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2387759" y="391668"/>
+              <a:off x="2835434" y="553593"/>
               <a:ext cx="120161" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3026,10 +2775,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -3047,7 +2796,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5781675" y="12468225"/>
+              <a:off x="6007100" y="12820650"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3138,7 +2887,351 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5781675" y="12468225"/>
+              <a:off x="6007100" y="12820650"/>
+              <a:ext cx="320040" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑠 ̅_𝑡</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="137024" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="TextBox 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0497318-A545-4B2A-93AC-76AD690B7B31}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="139700" y="14050010"/>
+              <a:ext cx="137024" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̂"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑠</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="TextBox 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0497318-A545-4B2A-93AC-76AD690B7B31}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="139700" y="14050010"/>
+              <a:ext cx="137024" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑠 ̂_𝑡</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>375285</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>248920</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="320040" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="TextBox 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EDF0A85-6172-484C-8171-68CAD5E758BB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="375285" y="15266670"/>
+              <a:ext cx="320040" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑠</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="TextBox 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EDF0A85-6172-484C-8171-68CAD5E758BB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="375285" y="15266670"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3501,2236 +3594,2289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F625CA8D-140F-4656-AD4A-A92BAB597FB2}">
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" customWidth="1"/>
-    <col min="14" max="14" width="9.6328125" customWidth="1"/>
+    <col min="7" max="13" width="11.1796875" customWidth="1"/>
+    <col min="14" max="14" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="32"/>
+    <row r="1" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5">
+        <v>3034</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7">
-        <v>3034</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="5">
+        <v>2748</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="7">
-        <v>2748</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="5">
+        <v>3164</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="7">
-        <v>3164</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="5">
+        <v>3238</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7">
-        <v>3238</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="5">
+        <v>3416</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7">
-        <v>3416</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="5">
+        <v>3492</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7">
-        <v>3492</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>3730</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="4">
         <f>(0.5*B3+SUM(B4:B14)+0.5*B15)/12</f>
         <v>3351.5833333333335</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="4">
         <f>B9-C9</f>
         <v>378.41666666666652</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="7">
+      <c r="A10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5">
         <v>3409</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="4">
         <f t="shared" ref="C10:C56" si="0">(0.5*B4+SUM(B5:B15)+0.5*B16)/12</f>
         <v>3350</v>
       </c>
-      <c r="D10" s="10">
-        <f t="shared" ref="D10:D14" si="1">B10-C10</f>
+      <c r="D10" s="30">
+        <f t="shared" ref="D10:D56" si="1">B10-C10</f>
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="7">
+      <c r="A11" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="5">
         <v>3572</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="4">
         <f t="shared" si="0"/>
         <v>3343.2083333333335</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="30">
         <f t="shared" si="1"/>
         <v>228.79166666666652</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="7">
+      <c r="A12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="5">
         <v>3629</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="4">
         <f t="shared" si="0"/>
         <v>3326.2083333333335</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="30">
         <f t="shared" si="1"/>
         <v>302.79166666666652</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="7">
+      <c r="A13" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5">
         <v>3408</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="4">
         <f t="shared" si="0"/>
         <v>3316.5416666666665</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="30">
         <f t="shared" si="1"/>
         <v>91.458333333333485</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="7">
+      <c r="A14" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="5">
         <v>3391</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="4">
         <f t="shared" si="0"/>
         <v>3318.5833333333335</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="30">
         <f t="shared" si="1"/>
         <v>72.416666666666515</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="A15" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5">
         <v>3010</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="4">
         <f t="shared" si="0"/>
         <v>3312.0833333333335</v>
       </c>
-      <c r="D15" s="11">
-        <f t="shared" ref="D15:D56" si="2">B15-C15</f>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
         <v>-302.08333333333348</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="7">
+      <c r="A16" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="5">
         <v>2734</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="4">
         <f t="shared" si="0"/>
         <v>3308.0416666666665</v>
       </c>
-      <c r="D16" s="11">
-        <f t="shared" si="2"/>
+      <c r="D16" s="2">
+        <f t="shared" si="1"/>
         <v>-574.04166666666652</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="7">
+      <c r="A17" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="5">
         <v>3015</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="4">
         <f t="shared" si="0"/>
         <v>3311.7083333333335</v>
       </c>
-      <c r="D17" s="11">
-        <f t="shared" si="2"/>
+      <c r="D17" s="2">
+        <f t="shared" si="1"/>
         <v>-296.70833333333348</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="7">
+      <c r="A18" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="5">
         <v>2979</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="4">
         <f t="shared" si="0"/>
         <v>3313.1666666666665</v>
       </c>
-      <c r="D18" s="11">
-        <f t="shared" si="2"/>
+      <c r="D18" s="2">
+        <f t="shared" si="1"/>
         <v>-334.16666666666652</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="7">
+      <c r="A19" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="5">
         <v>3443</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="4">
         <f t="shared" si="0"/>
         <v>3307.75</v>
       </c>
-      <c r="D19" s="11">
-        <f t="shared" si="2"/>
+      <c r="D19" s="2">
+        <f t="shared" si="1"/>
         <v>135.25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="7">
+      <c r="A20" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="5">
         <v>3514</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="4">
         <f t="shared" si="0"/>
         <v>3292.4166666666665</v>
       </c>
-      <c r="D20" s="11">
-        <f t="shared" si="2"/>
+      <c r="D20" s="2">
+        <f t="shared" si="1"/>
         <v>221.58333333333348</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="7">
+      <c r="A21" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="5">
         <v>3552</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="4">
         <f t="shared" si="0"/>
         <v>3281.0833333333335</v>
       </c>
-      <c r="D21" s="11">
-        <f t="shared" si="2"/>
+      <c r="D21" s="2">
+        <f t="shared" si="1"/>
         <v>270.91666666666652</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="7">
+      <c r="A22" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="5">
         <v>3490</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="4">
         <f t="shared" si="0"/>
         <v>3270.2083333333335</v>
       </c>
-      <c r="D22" s="11">
-        <f t="shared" si="2"/>
+      <c r="D22" s="2">
+        <f t="shared" si="1"/>
         <v>219.79166666666652</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="7">
+      <c r="A23" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="5">
         <v>3579</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="4">
         <f t="shared" si="0"/>
         <v>3259.4583333333335</v>
       </c>
-      <c r="D23" s="11">
-        <f t="shared" si="2"/>
+      <c r="D23" s="2">
+        <f t="shared" si="1"/>
         <v>319.54166666666652</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="7">
+      <c r="A24" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="5">
         <v>3657</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="4">
         <f t="shared" si="0"/>
         <v>3261.1666666666665</v>
       </c>
-      <c r="D24" s="11">
-        <f t="shared" si="2"/>
+      <c r="D24" s="2">
+        <f t="shared" si="1"/>
         <v>395.83333333333348</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="7">
+      <c r="A25" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="5">
         <v>3250</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="4">
         <f t="shared" si="0"/>
         <v>3264.25</v>
       </c>
-      <c r="D25" s="11">
-        <f t="shared" si="2"/>
+      <c r="D25" s="2">
+        <f t="shared" si="1"/>
         <v>-14.25</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="7">
+      <c r="A26" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="5">
         <v>3181</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="4">
         <f t="shared" si="0"/>
         <v>3260.4583333333335</v>
       </c>
-      <c r="D26" s="11">
-        <f t="shared" si="2"/>
+      <c r="D26" s="2">
+        <f t="shared" si="1"/>
         <v>-79.458333333333485</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="7">
+      <c r="A27" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="5">
         <v>2948</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="4">
         <f t="shared" si="0"/>
         <v>3256.7083333333335</v>
       </c>
-      <c r="D27" s="11">
-        <f t="shared" si="2"/>
+      <c r="D27" s="4">
+        <f t="shared" si="1"/>
         <v>-308.70833333333348</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="7">
+      <c r="A28" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="5">
         <v>2535</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="4">
         <f t="shared" si="0"/>
         <v>3262.125</v>
       </c>
-      <c r="D28" s="11">
-        <f t="shared" si="2"/>
+      <c r="D28" s="2">
+        <f t="shared" si="1"/>
         <v>-727.125</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="7">
+      <c r="A29" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="5">
         <v>2956</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="4">
         <f t="shared" si="0"/>
         <v>3267.0833333333335</v>
       </c>
-      <c r="D29" s="11">
-        <f t="shared" si="2"/>
+      <c r="D29" s="2">
+        <f t="shared" si="1"/>
         <v>-311.08333333333348</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="7">
+      <c r="A30" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="5">
         <v>3079</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="4">
         <f t="shared" si="0"/>
         <v>3259.2916666666665</v>
       </c>
-      <c r="D30" s="11">
-        <f t="shared" si="2"/>
+      <c r="D30" s="2">
+        <f t="shared" si="1"/>
         <v>-180.29166666666652</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="7">
+      <c r="A31" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="5">
         <v>3417</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="4">
         <f t="shared" si="0"/>
         <v>3254</v>
       </c>
-      <c r="D31" s="11">
-        <f t="shared" si="2"/>
+      <c r="D31" s="2">
+        <f t="shared" si="1"/>
         <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="7">
+      <c r="A32" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="5">
         <v>3449</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="4">
         <f t="shared" si="0"/>
         <v>3256.9583333333335</v>
       </c>
-      <c r="D32" s="11">
-        <f t="shared" si="2"/>
+      <c r="D32" s="2">
+        <f t="shared" si="1"/>
         <v>192.04166666666652</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="7">
+      <c r="A33" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="5">
         <v>3527</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="4">
         <f t="shared" si="0"/>
         <v>3256.7083333333335</v>
       </c>
-      <c r="D33" s="11">
-        <f t="shared" si="2"/>
+      <c r="D33" s="2">
+        <f t="shared" si="1"/>
         <v>270.29166666666652</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="7">
+      <c r="A34" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="5">
         <v>3645</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="4">
         <f t="shared" si="0"/>
         <v>3269</v>
       </c>
-      <c r="D34" s="11">
-        <f t="shared" si="2"/>
+      <c r="D34" s="2">
+        <f t="shared" si="1"/>
         <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="7">
+      <c r="A35" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="5">
         <v>3543</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="4">
         <f t="shared" si="0"/>
         <v>3279.0833333333335</v>
       </c>
-      <c r="D35" s="11">
-        <f t="shared" si="2"/>
+      <c r="D35" s="2">
+        <f t="shared" si="1"/>
         <v>263.91666666666652</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="7">
+      <c r="A36" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="5">
         <v>3506</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="4">
         <f t="shared" si="0"/>
         <v>3252.8333333333335</v>
       </c>
-      <c r="D36" s="11">
-        <f t="shared" si="2"/>
+      <c r="D36" s="2">
+        <f t="shared" si="1"/>
         <v>253.16666666666652</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="A37" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5">
         <v>3274</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="4">
         <f t="shared" si="0"/>
         <v>3228.0416666666665</v>
       </c>
-      <c r="D37" s="11">
-        <f t="shared" si="2"/>
+      <c r="D37" s="2">
+        <f t="shared" si="1"/>
         <v>45.958333333333485</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="7">
+      <c r="A38" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5">
         <v>3228</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="4">
         <f t="shared" si="0"/>
         <v>3248.2083333333335</v>
       </c>
-      <c r="D38" s="11">
-        <f t="shared" si="2"/>
+      <c r="D38" s="2">
+        <f t="shared" si="1"/>
         <v>-20.208333333333485</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="7">
+      <c r="A39" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5">
         <v>2895</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="4">
         <f t="shared" si="0"/>
         <v>3294.2916666666665</v>
       </c>
-      <c r="D39" s="11">
-        <f t="shared" si="2"/>
+      <c r="D39" s="4">
+        <f t="shared" si="1"/>
         <v>-399.29166666666652</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="7">
+      <c r="A40" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5">
         <v>2883</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="4">
         <f t="shared" si="0"/>
         <v>3340.3333333333335</v>
       </c>
-      <c r="D40" s="11">
-        <f t="shared" si="2"/>
+      <c r="D40" s="2">
+        <f t="shared" si="1"/>
         <v>-457.33333333333348</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="7">
+      <c r="A41" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5">
         <v>2850</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="4">
         <f t="shared" si="0"/>
         <v>3384.6666666666665</v>
       </c>
-      <c r="D41" s="11">
-        <f t="shared" si="2"/>
+      <c r="D41" s="2">
+        <f t="shared" si="1"/>
         <v>-534.66666666666652</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="7">
+      <c r="A42" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5">
         <v>2555</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="4">
         <f t="shared" si="0"/>
         <v>3433.5416666666665</v>
       </c>
-      <c r="D42" s="11">
-        <f t="shared" si="2"/>
+      <c r="D42" s="2">
+        <f t="shared" si="1"/>
         <v>-878.54166666666652</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="7">
+      <c r="A43" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="5">
         <v>3346</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="4">
         <f t="shared" si="0"/>
         <v>3481.2916666666665</v>
       </c>
-      <c r="D43" s="11">
-        <f t="shared" si="2"/>
+      <c r="D43" s="2">
+        <f t="shared" si="1"/>
         <v>-135.29166666666652</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="7">
+      <c r="A44" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="5">
         <v>4004</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="4">
         <f t="shared" si="0"/>
         <v>3514.8333333333335</v>
       </c>
-      <c r="D44" s="11">
-        <f t="shared" si="2"/>
+      <c r="D44" s="2">
+        <f t="shared" si="1"/>
         <v>489.16666666666652</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="7">
+      <c r="A45" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="5">
         <v>4078</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="4">
         <f t="shared" si="0"/>
         <v>3549.875</v>
       </c>
-      <c r="D45" s="11">
-        <f t="shared" si="2"/>
+      <c r="D45" s="2">
+        <f t="shared" si="1"/>
         <v>528.125</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="7">
+      <c r="A46" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="5">
         <v>4199</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="4">
         <f t="shared" si="0"/>
         <v>3567.7083333333335</v>
       </c>
-      <c r="D46" s="11">
-        <f t="shared" si="2"/>
+      <c r="D46" s="2">
+        <f t="shared" si="1"/>
         <v>631.29166666666652</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" s="7">
+      <c r="A47" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="5">
         <v>4053</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="4">
         <f t="shared" si="0"/>
         <v>3590.6666666666665</v>
       </c>
-      <c r="D47" s="11">
-        <f t="shared" si="2"/>
+      <c r="D47" s="2">
+        <f t="shared" si="1"/>
         <v>462.33333333333348</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="7">
+      <c r="A48" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="5">
         <v>4169</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="4">
         <f t="shared" si="0"/>
         <v>3672.125</v>
       </c>
-      <c r="D48" s="11">
-        <f t="shared" si="2"/>
+      <c r="D48" s="2">
+        <f t="shared" si="1"/>
         <v>496.875</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="7">
+      <c r="A49" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="5">
         <v>3757</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="4">
         <f t="shared" si="0"/>
         <v>3758.1666666666665</v>
       </c>
-      <c r="D49" s="11">
-        <f t="shared" si="2"/>
+      <c r="D49" s="2">
+        <f t="shared" si="1"/>
         <v>-1.1666666666665151</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="7">
+      <c r="A50" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="5">
         <v>3550</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="4">
         <f t="shared" si="0"/>
         <v>3793.7916666666665</v>
       </c>
-      <c r="D50" s="11">
-        <f t="shared" si="2"/>
+      <c r="D50" s="2">
+        <f t="shared" si="1"/>
         <v>-243.79166666666652</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="7">
+      <c r="A51" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="5">
         <v>3414</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="4">
         <f t="shared" si="0"/>
         <v>3804.8333333333335</v>
       </c>
-      <c r="D51" s="11">
-        <f t="shared" si="2"/>
+      <c r="D51" s="4">
+        <f t="shared" si="1"/>
         <v>-390.83333333333348</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" s="7">
+      <c r="A52" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="5">
         <v>2792</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="4">
         <f t="shared" si="0"/>
         <v>3816.625</v>
       </c>
-      <c r="D52" s="11">
-        <f t="shared" si="2"/>
+      <c r="D52" s="2">
+        <f t="shared" si="1"/>
         <v>-1024.625</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="7">
+      <c r="A53" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="5">
         <v>3492</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="4">
         <f t="shared" si="0"/>
         <v>3830.9583333333335</v>
       </c>
-      <c r="D53" s="11">
-        <f t="shared" si="2"/>
+      <c r="D53" s="2">
+        <f t="shared" si="1"/>
         <v>-338.95833333333348</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="7">
+      <c r="A54" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="5">
         <v>3868</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="4">
         <f t="shared" si="0"/>
         <v>3853.2916666666665</v>
       </c>
-      <c r="D54" s="11">
-        <f t="shared" si="2"/>
+      <c r="D54" s="2">
+        <f t="shared" si="1"/>
         <v>14.708333333333485</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" s="7">
+      <c r="A55" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="5">
         <v>4098</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="4">
         <f t="shared" si="0"/>
         <v>3875.5</v>
       </c>
-      <c r="D55" s="11">
-        <f t="shared" si="2"/>
+      <c r="D55" s="2">
+        <f t="shared" si="1"/>
         <v>222.5</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56" s="7">
+      <c r="A56" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="5">
         <v>4107</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="4">
         <f t="shared" si="0"/>
         <v>3899.8333333333335</v>
       </c>
-      <c r="D56" s="11">
-        <f t="shared" si="2"/>
+      <c r="D56" s="4">
+        <f t="shared" si="1"/>
         <v>207.16666666666652</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="5">
+        <v>4240</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B57" s="7">
-        <v>4240</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="6" t="s">
+      <c r="B58" s="5">
+        <v>4320</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="7">
-        <v>4320</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="6" t="s">
+      <c r="B59" s="5">
+        <v>4276</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="7">
-        <v>4276</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="6" t="s">
+      <c r="B60" s="5">
+        <v>4482</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B60" s="7">
-        <v>4482</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="6" t="s">
+      <c r="B61" s="5">
+        <v>3977</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="7">
-        <v>3977</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" s="13">
+      <c r="B62" s="5">
         <v>3914</v>
       </c>
-      <c r="C62" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>79</v>
+      <c r="C62" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+      <c r="K65" s="26"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="1:15" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="M66" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N66" s="13"/>
+    </row>
+    <row r="67" spans="1:15" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="10">
+        <v>2017</v>
+      </c>
+      <c r="B67" s="7" t="str" cm="1">
+        <f t="array" ref="B67:M67">TRANSPOSE(D3:D14)</f>
+        <v>NA</v>
+      </c>
+      <c r="C67" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D67" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="E67" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="F67" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="G67" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H67" s="8">
+        <v>378.41666666666652</v>
+      </c>
+      <c r="I67" s="31">
+        <v>59</v>
+      </c>
+      <c r="J67" s="31">
+        <v>228.79166666666652</v>
+      </c>
+      <c r="K67" s="31">
+        <v>302.79166666666652</v>
+      </c>
+      <c r="L67" s="31">
+        <v>91.458333333333485</v>
+      </c>
+      <c r="M67" s="31">
+        <v>72.416666666666515</v>
+      </c>
+      <c r="N67" s="14"/>
+    </row>
+    <row r="68" spans="1:15" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="10">
+        <v>2018</v>
+      </c>
+      <c r="B68" s="8" cm="1">
+        <f t="array" ref="B68:M68">TRANSPOSE(D15:D26)</f>
+        <v>-302.08333333333348</v>
+      </c>
+      <c r="C68" s="9">
+        <v>-574.04166666666652</v>
+      </c>
+      <c r="D68" s="9">
+        <v>-296.70833333333348</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-334.16666666666652</v>
+      </c>
+      <c r="F68" s="9">
+        <v>135.25</v>
+      </c>
+      <c r="G68" s="9">
+        <v>221.58333333333348</v>
+      </c>
+      <c r="H68" s="9">
+        <v>270.91666666666652</v>
+      </c>
+      <c r="I68" s="9">
+        <v>219.79166666666652</v>
+      </c>
+      <c r="J68" s="9">
+        <v>319.54166666666652</v>
+      </c>
+      <c r="K68" s="9">
+        <v>395.83333333333348</v>
+      </c>
+      <c r="L68" s="9">
+        <v>-14.25</v>
+      </c>
+      <c r="M68" s="9">
+        <v>-79.458333333333485</v>
+      </c>
+      <c r="N68" s="14"/>
+    </row>
+    <row r="69" spans="1:15" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="10">
+        <v>2019</v>
+      </c>
+      <c r="B69" s="8" cm="1">
+        <f t="array" ref="B69:M69">TRANSPOSE(D27:D38)</f>
+        <v>-308.70833333333348</v>
+      </c>
+      <c r="C69" s="9">
+        <v>-727.125</v>
+      </c>
+      <c r="D69" s="9">
+        <v>-311.08333333333348</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-180.29166666666652</v>
+      </c>
+      <c r="F69" s="9">
+        <v>163</v>
+      </c>
+      <c r="G69" s="9">
+        <v>192.04166666666652</v>
+      </c>
+      <c r="H69" s="9">
+        <v>270.29166666666652</v>
+      </c>
+      <c r="I69" s="9">
+        <v>376</v>
+      </c>
+      <c r="J69" s="9">
+        <v>263.91666666666652</v>
+      </c>
+      <c r="K69" s="9">
+        <v>253.16666666666652</v>
+      </c>
+      <c r="L69" s="9">
+        <v>45.958333333333485</v>
+      </c>
+      <c r="M69" s="9">
+        <v>-20.208333333333485</v>
+      </c>
+      <c r="N69" s="14"/>
+    </row>
+    <row r="70" spans="1:15" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B70" s="8" cm="1">
+        <f t="array" ref="B70:M70">TRANSPOSE(D39:D50)</f>
+        <v>-399.29166666666652</v>
+      </c>
+      <c r="C70" s="9">
+        <v>-457.33333333333348</v>
+      </c>
+      <c r="D70" s="9">
+        <v>-534.66666666666652</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-878.54166666666652</v>
+      </c>
+      <c r="F70" s="9">
+        <v>-135.29166666666652</v>
+      </c>
+      <c r="G70" s="9">
+        <v>489.16666666666652</v>
+      </c>
+      <c r="H70" s="9">
+        <v>528.125</v>
+      </c>
+      <c r="I70" s="9">
+        <v>631.29166666666652</v>
+      </c>
+      <c r="J70" s="9">
+        <v>462.33333333333348</v>
+      </c>
+      <c r="K70" s="9">
+        <v>496.875</v>
+      </c>
+      <c r="L70" s="9">
+        <v>-1.1666666666665151</v>
+      </c>
+      <c r="M70" s="9">
+        <v>-243.79166666666652</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B71" s="8" cm="1">
+        <f t="array" ref="B71:M71">TRANSPOSE(D51:D62)</f>
+        <v>-390.83333333333348</v>
+      </c>
+      <c r="C71" s="9">
+        <v>-1024.625</v>
+      </c>
+      <c r="D71" s="9">
+        <v>-338.95833333333348</v>
+      </c>
+      <c r="E71" s="9">
+        <v>14.708333333333485</v>
+      </c>
+      <c r="F71" s="9">
+        <v>222.5</v>
+      </c>
+      <c r="G71" s="8">
+        <v>207.16666666666652</v>
+      </c>
+      <c r="H71" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="I71" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="J71" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="K71" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L71" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="M71" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="N71" s="14"/>
+    </row>
+    <row r="72" spans="1:15" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="12"/>
+      <c r="N72" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="8">
+        <f t="shared" ref="B73:M73" si="2">AVERAGE(B67:B71)</f>
+        <v>-350.22916666666674</v>
+      </c>
+      <c r="C73" s="9">
+        <f t="shared" si="2"/>
+        <v>-695.78125</v>
+      </c>
+      <c r="D73" s="9">
+        <f t="shared" si="2"/>
+        <v>-370.35416666666674</v>
+      </c>
+      <c r="E73" s="9">
+        <f t="shared" si="2"/>
+        <v>-344.57291666666652</v>
+      </c>
+      <c r="F73" s="9">
+        <f t="shared" si="2"/>
+        <v>96.364583333333371</v>
+      </c>
+      <c r="G73" s="9">
+        <f t="shared" si="2"/>
+        <v>277.48958333333326</v>
+      </c>
+      <c r="H73" s="9">
+        <f t="shared" si="2"/>
+        <v>361.93749999999989</v>
+      </c>
+      <c r="I73" s="9">
+        <f t="shared" si="2"/>
+        <v>321.52083333333326</v>
+      </c>
+      <c r="J73" s="9">
+        <f t="shared" si="2"/>
+        <v>318.64583333333326</v>
+      </c>
+      <c r="K73" s="9">
+        <f t="shared" si="2"/>
+        <v>362.16666666666663</v>
+      </c>
+      <c r="L73" s="9">
+        <f t="shared" si="2"/>
+        <v>30.500000000000114</v>
+      </c>
+      <c r="M73" s="9">
+        <f t="shared" si="2"/>
+        <v>-67.760416666666742</v>
+      </c>
+      <c r="N73" s="9">
+        <f>AVERAGE(B73:M73)</f>
+        <v>-5.0060763888889142</v>
+      </c>
+      <c r="O73" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B65" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="B66" s="34"/>
-      <c r="C66" s="34"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="34"/>
-      <c r="I66" s="34"/>
-      <c r="J66" s="34"/>
-      <c r="K66" s="34"/>
-      <c r="L66" s="34"/>
-      <c r="M66" s="34"/>
-      <c r="N66" s="14"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F67" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H67" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="I67" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="J67" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="K67" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="L67" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="M67" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="N67" s="18"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="19">
-        <v>2017</v>
-      </c>
-      <c r="B68" s="7" t="str" cm="1">
-        <f t="array" ref="B68:M68">TRANSPOSE(D3:D14)</f>
+    <row r="74" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="16"/>
+      <c r="B74" s="8">
+        <f t="shared" ref="B74:M74" si="3">B73-$N$73</f>
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="C74" s="9">
+        <f t="shared" si="3"/>
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="D74" s="9">
+        <f t="shared" si="3"/>
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="E74" s="9">
+        <f t="shared" si="3"/>
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F74" s="9">
+        <f t="shared" si="3"/>
+        <v>101.37065972222229</v>
+      </c>
+      <c r="G74" s="9">
+        <f t="shared" si="3"/>
+        <v>282.49565972222217</v>
+      </c>
+      <c r="H74" s="9">
+        <f t="shared" si="3"/>
+        <v>366.9435763888888</v>
+      </c>
+      <c r="I74" s="9">
+        <f t="shared" si="3"/>
+        <v>326.52690972222217</v>
+      </c>
+      <c r="J74" s="9">
+        <f t="shared" si="3"/>
+        <v>323.65190972222217</v>
+      </c>
+      <c r="K74" s="9">
+        <f t="shared" si="3"/>
+        <v>367.17274305555554</v>
+      </c>
+      <c r="L74" s="9">
+        <f t="shared" si="3"/>
+        <v>35.506076388889028</v>
+      </c>
+      <c r="M74" s="9">
+        <f t="shared" si="3"/>
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="N74" s="17"/>
+      <c r="O74" s="6"/>
+    </row>
+    <row r="77" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="28"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="29"/>
+    </row>
+    <row r="78" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A79" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="5">
+        <f t="shared" ref="B79:C95" si="4">B3</f>
+        <v>3034</v>
+      </c>
+      <c r="C79" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="C68" s="7" t="str">
+      <c r="D79" s="5" t="str">
+        <f t="shared" ref="D79:D110" si="5">IF(LEN(D3)&gt;0,D3,"")</f>
         <v>NA</v>
       </c>
-      <c r="D68" s="7" t="str">
+      <c r="E79" s="4" cm="1">
+        <f t="array" ref="E79:E90">TRANSPOSE(B$74:M$74)</f>
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="F79" s="5" t="str">
+        <f t="shared" ref="F79:F110" si="6">IFERROR(B3-C3-E79, "NA")</f>
         <v>NA</v>
       </c>
-      <c r="E68" s="7" t="str">
+      <c r="G79" s="4">
+        <f>B79-E79</f>
+        <v>3379.2230902777778</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A80" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="5">
+        <f t="shared" si="4"/>
+        <v>2748</v>
+      </c>
+      <c r="C80" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="F68" s="7" t="str">
+      <c r="D80" s="5" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G68" s="7" t="str">
-        <v>NA</v>
-      </c>
-      <c r="H68" s="11">
-        <v>378.41666666666652</v>
-      </c>
-      <c r="I68" s="11">
-        <v>59</v>
-      </c>
-      <c r="J68" s="11">
-        <v>228.79166666666652</v>
-      </c>
-      <c r="K68" s="11">
-        <v>302.79166666666652</v>
-      </c>
-      <c r="L68" s="11">
-        <v>91.458333333333485</v>
-      </c>
-      <c r="M68" s="11">
-        <v>72.416666666666515</v>
-      </c>
-      <c r="N68" s="20"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="19">
-        <v>2018</v>
-      </c>
-      <c r="B69" s="11" cm="1">
-        <f t="array" ref="B69:M69">TRANSPOSE(D15:D26)</f>
-        <v>-302.08333333333348</v>
-      </c>
-      <c r="C69" s="11">
-        <v>-574.04166666666652</v>
-      </c>
-      <c r="D69" s="9">
-        <v>-296.70833333333348</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-334.16666666666652</v>
-      </c>
-      <c r="F69" s="9">
-        <v>135.25</v>
-      </c>
-      <c r="G69" s="9">
-        <v>221.58333333333348</v>
-      </c>
-      <c r="H69" s="9">
-        <v>270.91666666666652</v>
-      </c>
-      <c r="I69" s="9">
-        <v>219.79166666666652</v>
-      </c>
-      <c r="J69" s="9">
-        <v>319.54166666666652</v>
-      </c>
-      <c r="K69" s="9">
-        <v>395.83333333333348</v>
-      </c>
-      <c r="L69" s="9">
-        <v>-14.25</v>
-      </c>
-      <c r="M69" s="10">
-        <v>-79.458333333333485</v>
-      </c>
-      <c r="N69" s="20"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="19">
-        <v>2019</v>
-      </c>
-      <c r="B70" s="9" cm="1">
-        <f t="array" ref="B70:M70">TRANSPOSE(D27:D38)</f>
-        <v>-308.70833333333348</v>
-      </c>
-      <c r="C70" s="9">
-        <v>-727.125</v>
-      </c>
-      <c r="D70" s="9">
-        <v>-311.08333333333348</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-180.29166666666652</v>
-      </c>
-      <c r="F70" s="9">
-        <v>163</v>
-      </c>
-      <c r="G70" s="9">
-        <v>192.04166666666652</v>
-      </c>
-      <c r="H70" s="9">
-        <v>270.29166666666652</v>
-      </c>
-      <c r="I70" s="9">
-        <v>376</v>
-      </c>
-      <c r="J70" s="9">
-        <v>263.91666666666652</v>
-      </c>
-      <c r="K70" s="9">
-        <v>253.16666666666652</v>
-      </c>
-      <c r="L70" s="9">
-        <v>45.958333333333485</v>
-      </c>
-      <c r="M70" s="10">
-        <v>-20.208333333333485</v>
-      </c>
-      <c r="N70" s="20"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="19">
-        <v>2020</v>
-      </c>
-      <c r="B71" s="9" cm="1">
-        <f t="array" ref="B71:M71">TRANSPOSE(D39:D50)</f>
-        <v>-399.29166666666652</v>
-      </c>
-      <c r="C71" s="9">
-        <v>-457.33333333333348</v>
-      </c>
-      <c r="D71" s="9">
-        <v>-534.66666666666652</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-878.54166666666652</v>
-      </c>
-      <c r="F71" s="9">
-        <v>-135.29166666666652</v>
-      </c>
-      <c r="G71" s="9">
-        <v>489.16666666666652</v>
-      </c>
-      <c r="H71" s="9">
-        <v>528.125</v>
-      </c>
-      <c r="I71" s="9">
-        <v>631.29166666666652</v>
-      </c>
-      <c r="J71" s="9">
-        <v>462.33333333333348</v>
-      </c>
-      <c r="K71" s="9">
-        <v>496.875</v>
-      </c>
-      <c r="L71" s="9">
-        <v>-1.1666666666665151</v>
-      </c>
-      <c r="M71" s="10">
-        <v>-243.79166666666652</v>
-      </c>
-      <c r="N71" s="35" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="19">
-        <v>2021</v>
-      </c>
-      <c r="B72" s="9" cm="1">
-        <f t="array" ref="B72:M72">TRANSPOSE(D51:D62)</f>
-        <v>-390.83333333333348</v>
-      </c>
-      <c r="C72" s="9">
-        <v>-1024.625</v>
-      </c>
-      <c r="D72" s="9">
-        <v>-338.95833333333348</v>
-      </c>
-      <c r="E72" s="9">
-        <v>14.708333333333485</v>
-      </c>
-      <c r="F72" s="9">
-        <v>222.5</v>
-      </c>
-      <c r="G72" s="9">
-        <v>207.16666666666652</v>
-      </c>
-      <c r="H72" s="7" t="str">
-        <v>NA</v>
-      </c>
-      <c r="I72" s="7" t="str">
-        <v>NA</v>
-      </c>
-      <c r="J72" s="7" t="str">
-        <v>NA</v>
-      </c>
-      <c r="K72" s="7" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L72" s="7" t="str">
-        <v>NA</v>
-      </c>
-      <c r="M72" s="8" t="str">
-        <v>NA</v>
-      </c>
-      <c r="N72" s="36"/>
-    </row>
-    <row r="73" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B73" s="9">
-        <f>AVERAGE(B68:B72)</f>
-        <v>-350.22916666666674</v>
-      </c>
-      <c r="C73" s="9">
-        <f>AVERAGE(C68:C72)</f>
-        <v>-695.78125</v>
-      </c>
-      <c r="D73" s="9">
-        <f>AVERAGE(D68:D72)</f>
-        <v>-370.35416666666674</v>
-      </c>
-      <c r="E73" s="11">
-        <f t="shared" ref="E73:M73" si="3">AVERAGE(E68:E72)</f>
-        <v>-344.57291666666652</v>
-      </c>
-      <c r="F73" s="11">
-        <f t="shared" si="3"/>
-        <v>96.364583333333371</v>
-      </c>
-      <c r="G73" s="11">
-        <f t="shared" si="3"/>
-        <v>277.48958333333326</v>
-      </c>
-      <c r="H73" s="11">
-        <f t="shared" si="3"/>
-        <v>361.93749999999989</v>
-      </c>
-      <c r="I73" s="11">
-        <f t="shared" si="3"/>
-        <v>321.52083333333326</v>
-      </c>
-      <c r="J73" s="11">
-        <f t="shared" si="3"/>
-        <v>318.64583333333326</v>
-      </c>
-      <c r="K73" s="11">
-        <f t="shared" si="3"/>
-        <v>362.16666666666663</v>
-      </c>
-      <c r="L73" s="11">
-        <f t="shared" si="3"/>
-        <v>30.500000000000114</v>
-      </c>
-      <c r="M73" s="11">
-        <f t="shared" si="3"/>
-        <v>-67.760416666666742</v>
-      </c>
-      <c r="N73" s="22">
-        <v>-5.0060763888889142</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="23"/>
-      <c r="B74" s="24">
-        <f t="shared" ref="B74:M74" si="4">B73-$N73</f>
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="C74" s="11">
-        <f t="shared" si="4"/>
+      <c r="E80" s="4">
         <v>-690.77517361111109</v>
       </c>
-      <c r="D74" s="11">
-        <f t="shared" si="4"/>
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="E74" s="11">
-        <f t="shared" si="4"/>
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F74" s="11">
-        <f t="shared" si="4"/>
-        <v>101.37065972222229</v>
-      </c>
-      <c r="G74" s="11">
-        <f t="shared" si="4"/>
-        <v>282.49565972222217</v>
-      </c>
-      <c r="H74" s="11">
-        <f t="shared" si="4"/>
-        <v>366.9435763888888</v>
-      </c>
-      <c r="I74" s="11">
-        <f t="shared" si="4"/>
-        <v>326.52690972222217</v>
-      </c>
-      <c r="J74" s="11">
-        <f t="shared" si="4"/>
-        <v>323.65190972222217</v>
-      </c>
-      <c r="K74" s="11">
-        <f t="shared" si="4"/>
-        <v>367.17274305555554</v>
-      </c>
-      <c r="L74" s="11">
-        <f t="shared" si="4"/>
-        <v>35.506076388889028</v>
-      </c>
-      <c r="M74" s="11">
-        <f t="shared" si="4"/>
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="N74" s="25"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:14" ht="43.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="B78" s="38"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="39"/>
-    </row>
-    <row r="79" spans="1:14" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C79" s="28"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="G79" s="29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" s="7">
-        <f>B3</f>
-        <v>3034</v>
-      </c>
-      <c r="C80" s="7" t="str">
-        <f t="shared" ref="C80" si="5">C3</f>
-        <v>NA</v>
-      </c>
-      <c r="D80" s="40" t="str">
-        <f>IF(LEN(D3)&gt;0,D3,"")</f>
-        <v>NA</v>
-      </c>
-      <c r="E80" s="41" cm="1">
-        <f t="array" ref="E80:E91">TRANSPOSE(B$74:M$74)</f>
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="F80" s="7" t="str">
-        <f>IFERROR(B3-C3-E80, "NA")</f>
-        <v>NA</v>
-      </c>
-      <c r="G80" s="42">
-        <f>B80-E80</f>
-        <v>3379.2230902777778</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B81" s="7">
-        <f t="shared" ref="B81:C96" si="6">B4</f>
-        <v>2748</v>
-      </c>
-      <c r="C81" s="7" t="str">
+      <c r="F80" s="5" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
-      <c r="D81" s="8" t="str">
-        <f t="shared" ref="D81:D139" si="7">IF(LEN(D4)&gt;0,D4,"")</f>
+      <c r="G80" s="4">
+        <f t="shared" ref="G80:G138" si="7">B80-E80</f>
+        <v>3438.7751736111113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" s="5">
+        <f t="shared" si="4"/>
+        <v>3164</v>
+      </c>
+      <c r="C81" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E81" s="11">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F81" s="7" t="str">
-        <f t="shared" ref="F81:F139" si="8">IFERROR(B4-C4-E81, "NA")</f>
+      <c r="D81" s="5" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G81" s="11">
-        <f t="shared" ref="G81:G139" si="9">B81-E81</f>
-        <v>3438.7751736111113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82" s="7">
-        <f t="shared" si="6"/>
-        <v>3164</v>
-      </c>
-      <c r="C82" s="7" t="str">
+      <c r="E81" s="2">
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="F81" s="5" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
-      <c r="D82" s="8" t="str">
+      <c r="G81" s="2">
         <f t="shared" si="7"/>
+        <v>3529.3480902777778</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="5">
+        <f t="shared" si="4"/>
+        <v>3238</v>
+      </c>
+      <c r="C82" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E82" s="11">
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="F82" s="7" t="str">
-        <f t="shared" si="8"/>
+      <c r="D82" s="5" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G82" s="11">
-        <f t="shared" si="9"/>
-        <v>3529.3480902777778</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" s="7">
-        <f t="shared" si="6"/>
-        <v>3238</v>
-      </c>
-      <c r="C83" s="7" t="str">
+      <c r="E82" s="2">
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F82" s="5" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
-      <c r="D83" s="8" t="str">
+      <c r="G82" s="2">
         <f t="shared" si="7"/>
+        <v>3577.5668402777774</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="5">
+        <f t="shared" si="4"/>
+        <v>3416</v>
+      </c>
+      <c r="C83" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E83" s="11">
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F83" s="7" t="str">
-        <f t="shared" si="8"/>
+      <c r="D83" s="5" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G83" s="11">
-        <f t="shared" si="9"/>
-        <v>3577.5668402777774</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B84" s="7">
-        <f t="shared" si="6"/>
-        <v>3416</v>
-      </c>
-      <c r="C84" s="7" t="str">
+      <c r="E83" s="2">
+        <v>101.37065972222229</v>
+      </c>
+      <c r="F83" s="5" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
-      <c r="D84" s="8" t="str">
+      <c r="G83" s="2">
         <f t="shared" si="7"/>
+        <v>3314.6293402777778</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="5">
+        <f t="shared" si="4"/>
+        <v>3492</v>
+      </c>
+      <c r="C84" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="E84" s="11">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F84" s="7" t="str">
-        <f t="shared" si="8"/>
+      <c r="D84" s="5" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="G84" s="11">
-        <f t="shared" si="9"/>
-        <v>3314.6293402777778</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" s="7">
-        <f t="shared" si="6"/>
-        <v>3492</v>
-      </c>
-      <c r="C85" s="7" t="str">
+      <c r="E84" s="2">
+        <v>282.49565972222217</v>
+      </c>
+      <c r="F84" s="5" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
-      <c r="D85" s="8" t="str">
+      <c r="G84" s="2">
         <f t="shared" si="7"/>
-        <v>NA</v>
-      </c>
-      <c r="E85" s="11">
+        <v>3209.5043402777778</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="5">
+        <f t="shared" si="4"/>
+        <v>3730</v>
+      </c>
+      <c r="C85" s="4">
+        <f t="shared" si="4"/>
+        <v>3351.5833333333335</v>
+      </c>
+      <c r="D85" s="4">
+        <f t="shared" si="5"/>
+        <v>378.41666666666652</v>
+      </c>
+      <c r="E85" s="2">
+        <v>366.9435763888888</v>
+      </c>
+      <c r="F85" s="4">
+        <f t="shared" si="6"/>
+        <v>11.473090277777715</v>
+      </c>
+      <c r="G85" s="2">
+        <f t="shared" si="7"/>
+        <v>3363.0564236111113</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" s="5">
+        <f t="shared" si="4"/>
+        <v>3409</v>
+      </c>
+      <c r="C86" s="4">
+        <f t="shared" si="4"/>
+        <v>3350</v>
+      </c>
+      <c r="D86" s="30">
+        <f t="shared" si="5"/>
+        <v>59</v>
+      </c>
+      <c r="E86" s="2">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F86" s="4">
+        <f t="shared" si="6"/>
+        <v>-267.52690972222217</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="7"/>
+        <v>3082.4730902777778</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="5">
+        <f t="shared" si="4"/>
+        <v>3572</v>
+      </c>
+      <c r="C87" s="4">
+        <f t="shared" si="4"/>
+        <v>3343.2083333333335</v>
+      </c>
+      <c r="D87" s="30">
+        <f t="shared" si="5"/>
+        <v>228.79166666666652</v>
+      </c>
+      <c r="E87" s="2">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F87" s="2">
+        <f t="shared" si="6"/>
+        <v>-94.860243055555657</v>
+      </c>
+      <c r="G87" s="2">
+        <f t="shared" si="7"/>
+        <v>3248.3480902777778</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" s="5">
+        <f t="shared" si="4"/>
+        <v>3629</v>
+      </c>
+      <c r="C88" s="4">
+        <f t="shared" si="4"/>
+        <v>3326.2083333333335</v>
+      </c>
+      <c r="D88" s="30">
+        <f t="shared" si="5"/>
+        <v>302.79166666666652</v>
+      </c>
+      <c r="E88" s="2">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F88" s="2">
+        <f t="shared" si="6"/>
+        <v>-64.381076388889028</v>
+      </c>
+      <c r="G88" s="2">
+        <f t="shared" si="7"/>
+        <v>3261.8272569444443</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B89" s="5">
+        <f t="shared" si="4"/>
+        <v>3408</v>
+      </c>
+      <c r="C89" s="4">
+        <f t="shared" si="4"/>
+        <v>3316.5416666666665</v>
+      </c>
+      <c r="D89" s="30">
+        <f t="shared" si="5"/>
+        <v>91.458333333333485</v>
+      </c>
+      <c r="E89" s="2">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F89" s="2">
+        <f t="shared" si="6"/>
+        <v>55.952256944444457</v>
+      </c>
+      <c r="G89" s="2">
+        <f t="shared" si="7"/>
+        <v>3372.4939236111109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" s="5">
+        <f t="shared" si="4"/>
+        <v>3391</v>
+      </c>
+      <c r="C90" s="4">
+        <f t="shared" si="4"/>
+        <v>3318.5833333333335</v>
+      </c>
+      <c r="D90" s="30">
+        <f t="shared" si="5"/>
+        <v>72.416666666666515</v>
+      </c>
+      <c r="E90" s="2">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F90" s="2">
+        <f t="shared" si="6"/>
+        <v>135.17100694444434</v>
+      </c>
+      <c r="G90" s="2">
+        <f t="shared" si="7"/>
+        <v>3453.7543402777778</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" s="5">
+        <f t="shared" si="4"/>
+        <v>3010</v>
+      </c>
+      <c r="C91" s="4">
+        <f t="shared" si="4"/>
+        <v>3312.0833333333335</v>
+      </c>
+      <c r="D91" s="4">
+        <f t="shared" si="5"/>
+        <v>-302.08333333333348</v>
+      </c>
+      <c r="E91" s="2" cm="1">
+        <f t="array" ref="E91:E102">TRANSPOSE(B$74:M$74)</f>
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="F91" s="2">
+        <f t="shared" si="6"/>
+        <v>43.139756944444343</v>
+      </c>
+      <c r="G91" s="2">
+        <f t="shared" si="7"/>
+        <v>3355.2230902777778</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B92" s="5">
+        <f t="shared" si="4"/>
+        <v>2734</v>
+      </c>
+      <c r="C92" s="4">
+        <f t="shared" si="4"/>
+        <v>3308.0416666666665</v>
+      </c>
+      <c r="D92" s="2">
+        <f t="shared" si="5"/>
+        <v>-574.04166666666652</v>
+      </c>
+      <c r="E92" s="2">
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="F92" s="2">
+        <f t="shared" si="6"/>
+        <v>116.73350694444457</v>
+      </c>
+      <c r="G92" s="2">
+        <f t="shared" si="7"/>
+        <v>3424.7751736111113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" s="5">
+        <f t="shared" si="4"/>
+        <v>3015</v>
+      </c>
+      <c r="C93" s="4">
+        <f t="shared" si="4"/>
+        <v>3311.7083333333335</v>
+      </c>
+      <c r="D93" s="2">
+        <f t="shared" si="5"/>
+        <v>-296.70833333333348</v>
+      </c>
+      <c r="E93" s="2">
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="F93" s="2">
+        <f t="shared" si="6"/>
+        <v>68.639756944444343</v>
+      </c>
+      <c r="G93" s="2">
+        <f t="shared" si="7"/>
+        <v>3380.3480902777778</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B94" s="5">
+        <f t="shared" si="4"/>
+        <v>2979</v>
+      </c>
+      <c r="C94" s="4">
+        <f t="shared" si="4"/>
+        <v>3313.1666666666665</v>
+      </c>
+      <c r="D94" s="2">
+        <f t="shared" si="5"/>
+        <v>-334.16666666666652</v>
+      </c>
+      <c r="E94" s="2">
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F94" s="2">
+        <f t="shared" si="6"/>
+        <v>5.4001736111110858</v>
+      </c>
+      <c r="G94" s="2">
+        <f t="shared" si="7"/>
+        <v>3318.5668402777774</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" s="5">
+        <f t="shared" si="4"/>
+        <v>3443</v>
+      </c>
+      <c r="C95" s="4">
+        <f t="shared" si="4"/>
+        <v>3307.75</v>
+      </c>
+      <c r="D95" s="2">
+        <f t="shared" si="5"/>
+        <v>135.25</v>
+      </c>
+      <c r="E95" s="2">
+        <v>101.37065972222229</v>
+      </c>
+      <c r="F95" s="2">
+        <f t="shared" si="6"/>
+        <v>33.879340277777715</v>
+      </c>
+      <c r="G95" s="2">
+        <f t="shared" si="7"/>
+        <v>3341.6293402777778</v>
+      </c>
+      <c r="H95" s="1"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B96" s="5">
+        <f t="shared" ref="B96:C111" si="8">B20</f>
+        <v>3514</v>
+      </c>
+      <c r="C96" s="4">
+        <f t="shared" si="8"/>
+        <v>3292.4166666666665</v>
+      </c>
+      <c r="D96" s="2">
+        <f t="shared" si="5"/>
+        <v>221.58333333333348</v>
+      </c>
+      <c r="E96" s="2">
         <v>282.49565972222217</v>
       </c>
-      <c r="F85" s="7" t="str">
+      <c r="F96" s="2">
+        <f t="shared" si="6"/>
+        <v>-60.912326388888687</v>
+      </c>
+      <c r="G96" s="2">
+        <f t="shared" si="7"/>
+        <v>3231.5043402777778</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A97" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B97" s="5">
         <f t="shared" si="8"/>
-        <v>NA</v>
-      </c>
-      <c r="G85" s="11">
-        <f t="shared" si="9"/>
-        <v>3209.5043402777778</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B86" s="7">
+        <v>3552</v>
+      </c>
+      <c r="C97" s="4">
+        <f t="shared" si="8"/>
+        <v>3281.0833333333335</v>
+      </c>
+      <c r="D97" s="2">
+        <f t="shared" si="5"/>
+        <v>270.91666666666652</v>
+      </c>
+      <c r="E97" s="2">
+        <v>366.9435763888888</v>
+      </c>
+      <c r="F97" s="2">
         <f t="shared" si="6"/>
-        <v>3730</v>
-      </c>
-      <c r="C86" s="9">
+        <v>-96.026909722222285</v>
+      </c>
+      <c r="G97" s="2">
+        <f t="shared" si="7"/>
+        <v>3185.0564236111113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A98" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="5">
+        <f t="shared" si="8"/>
+        <v>3490</v>
+      </c>
+      <c r="C98" s="4">
+        <f t="shared" si="8"/>
+        <v>3270.2083333333335</v>
+      </c>
+      <c r="D98" s="2">
+        <f t="shared" si="5"/>
+        <v>219.79166666666652</v>
+      </c>
+      <c r="E98" s="2">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F98" s="2">
         <f t="shared" si="6"/>
-        <v>3351.5833333333335</v>
-      </c>
-      <c r="D86" s="10">
+        <v>-106.73524305555566</v>
+      </c>
+      <c r="G98" s="2">
         <f t="shared" si="7"/>
-        <v>378.41666666666652</v>
-      </c>
-      <c r="E86" s="11">
+        <v>3163.4730902777778</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A99" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B99" s="5">
+        <f t="shared" si="8"/>
+        <v>3579</v>
+      </c>
+      <c r="C99" s="4">
+        <f t="shared" si="8"/>
+        <v>3259.4583333333335</v>
+      </c>
+      <c r="D99" s="2">
+        <f t="shared" si="5"/>
+        <v>319.54166666666652</v>
+      </c>
+      <c r="E99" s="2">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F99" s="2">
+        <f t="shared" si="6"/>
+        <v>-4.1102430555556566</v>
+      </c>
+      <c r="G99" s="2">
+        <f t="shared" si="7"/>
+        <v>3255.3480902777778</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A100" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100" s="5">
+        <f t="shared" si="8"/>
+        <v>3657</v>
+      </c>
+      <c r="C100" s="4">
+        <f t="shared" si="8"/>
+        <v>3261.1666666666665</v>
+      </c>
+      <c r="D100" s="2">
+        <f t="shared" si="5"/>
+        <v>395.83333333333348</v>
+      </c>
+      <c r="E100" s="2">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F100" s="2">
+        <f t="shared" si="6"/>
+        <v>28.660590277777942</v>
+      </c>
+      <c r="G100" s="2">
+        <f t="shared" si="7"/>
+        <v>3289.8272569444443</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A101" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" s="5">
+        <f t="shared" si="8"/>
+        <v>3250</v>
+      </c>
+      <c r="C101" s="4">
+        <f t="shared" si="8"/>
+        <v>3264.25</v>
+      </c>
+      <c r="D101" s="2">
+        <f t="shared" si="5"/>
+        <v>-14.25</v>
+      </c>
+      <c r="E101" s="2">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F101" s="2">
+        <f t="shared" si="6"/>
+        <v>-49.756076388889028</v>
+      </c>
+      <c r="G101" s="2">
+        <f t="shared" si="7"/>
+        <v>3214.4939236111109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A102" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" s="5">
+        <f t="shared" si="8"/>
+        <v>3181</v>
+      </c>
+      <c r="C102" s="4">
+        <f t="shared" si="8"/>
+        <v>3260.4583333333335</v>
+      </c>
+      <c r="D102" s="2">
+        <f t="shared" si="5"/>
+        <v>-79.458333333333485</v>
+      </c>
+      <c r="E102" s="2">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F102" s="2">
+        <f t="shared" si="6"/>
+        <v>-16.703993055555657</v>
+      </c>
+      <c r="G102" s="2">
+        <f t="shared" si="7"/>
+        <v>3243.7543402777778</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A103" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" s="5">
+        <f t="shared" si="8"/>
+        <v>2948</v>
+      </c>
+      <c r="C103" s="4">
+        <f t="shared" si="8"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D103" s="4">
+        <f t="shared" si="5"/>
+        <v>-308.70833333333348</v>
+      </c>
+      <c r="E103" s="2" cm="1">
+        <f t="array" ref="E103:E114">TRANSPOSE(B$74:M$74)</f>
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="F103" s="2">
+        <f t="shared" si="6"/>
+        <v>36.514756944444343</v>
+      </c>
+      <c r="G103" s="2">
+        <f t="shared" si="7"/>
+        <v>3293.2230902777778</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A104" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B104" s="5">
+        <f t="shared" si="8"/>
+        <v>2535</v>
+      </c>
+      <c r="C104" s="4">
+        <f t="shared" si="8"/>
+        <v>3262.125</v>
+      </c>
+      <c r="D104" s="2">
+        <f t="shared" si="5"/>
+        <v>-727.125</v>
+      </c>
+      <c r="E104" s="2">
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="F104" s="2">
+        <f t="shared" si="6"/>
+        <v>-36.349826388888914</v>
+      </c>
+      <c r="G104" s="2">
+        <f t="shared" si="7"/>
+        <v>3225.7751736111113</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A105" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" s="5">
+        <f t="shared" si="8"/>
+        <v>2956</v>
+      </c>
+      <c r="C105" s="4">
+        <f t="shared" si="8"/>
+        <v>3267.0833333333335</v>
+      </c>
+      <c r="D105" s="2">
+        <f t="shared" si="5"/>
+        <v>-311.08333333333348</v>
+      </c>
+      <c r="E105" s="2">
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="F105" s="2">
+        <f t="shared" si="6"/>
+        <v>54.264756944444343</v>
+      </c>
+      <c r="G105" s="2">
+        <f t="shared" si="7"/>
+        <v>3321.3480902777778</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A106" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B106" s="5">
+        <f t="shared" si="8"/>
+        <v>3079</v>
+      </c>
+      <c r="C106" s="4">
+        <f t="shared" si="8"/>
+        <v>3259.2916666666665</v>
+      </c>
+      <c r="D106" s="2">
+        <f t="shared" si="5"/>
+        <v>-180.29166666666652</v>
+      </c>
+      <c r="E106" s="2">
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F106" s="2">
+        <f t="shared" si="6"/>
+        <v>159.27517361111109</v>
+      </c>
+      <c r="G106" s="2">
+        <f t="shared" si="7"/>
+        <v>3418.5668402777774</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A107" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107" s="5">
+        <f t="shared" si="8"/>
+        <v>3417</v>
+      </c>
+      <c r="C107" s="4">
+        <f t="shared" si="8"/>
+        <v>3254</v>
+      </c>
+      <c r="D107" s="2">
+        <f t="shared" si="5"/>
+        <v>163</v>
+      </c>
+      <c r="E107" s="2">
+        <v>101.37065972222229</v>
+      </c>
+      <c r="F107" s="2">
+        <f t="shared" si="6"/>
+        <v>61.629340277777715</v>
+      </c>
+      <c r="G107" s="2">
+        <f t="shared" si="7"/>
+        <v>3315.6293402777778</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A108" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B108" s="5">
+        <f t="shared" si="8"/>
+        <v>3449</v>
+      </c>
+      <c r="C108" s="4">
+        <f t="shared" si="8"/>
+        <v>3256.9583333333335</v>
+      </c>
+      <c r="D108" s="2">
+        <f t="shared" si="5"/>
+        <v>192.04166666666652</v>
+      </c>
+      <c r="E108" s="2">
+        <v>282.49565972222217</v>
+      </c>
+      <c r="F108" s="2">
+        <f t="shared" si="6"/>
+        <v>-90.453993055555657</v>
+      </c>
+      <c r="G108" s="2">
+        <f t="shared" si="7"/>
+        <v>3166.5043402777778</v>
+      </c>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A109" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B109" s="5">
+        <f t="shared" si="8"/>
+        <v>3527</v>
+      </c>
+      <c r="C109" s="4">
+        <f t="shared" si="8"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D109" s="2">
+        <f t="shared" si="5"/>
+        <v>270.29166666666652</v>
+      </c>
+      <c r="E109" s="2">
         <v>366.9435763888888</v>
       </c>
-      <c r="F86" s="9">
-        <f t="shared" si="8"/>
-        <v>11.473090277777715</v>
-      </c>
-      <c r="G86" s="11">
-        <f t="shared" si="9"/>
-        <v>3363.0564236111113</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B87" s="7">
+      <c r="F109" s="2">
         <f t="shared" si="6"/>
-        <v>3409</v>
-      </c>
-      <c r="C87" s="9">
-        <f t="shared" si="6"/>
-        <v>3350</v>
-      </c>
-      <c r="D87" s="10">
+        <v>-96.651909722222285</v>
+      </c>
+      <c r="G109" s="2">
         <f t="shared" si="7"/>
-        <v>59</v>
-      </c>
-      <c r="E87" s="11">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F87" s="11">
-        <f t="shared" si="8"/>
-        <v>-267.52690972222217</v>
-      </c>
-      <c r="G87" s="11">
-        <f t="shared" si="9"/>
-        <v>3082.4730902777778</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A88" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B88" s="7">
-        <f t="shared" si="6"/>
-        <v>3572</v>
-      </c>
-      <c r="C88" s="9">
-        <f t="shared" si="6"/>
-        <v>3343.2083333333335</v>
-      </c>
-      <c r="D88" s="10">
-        <f t="shared" si="7"/>
-        <v>228.79166666666652</v>
-      </c>
-      <c r="E88" s="11">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F88" s="11">
-        <f t="shared" si="8"/>
-        <v>-94.860243055555657</v>
-      </c>
-      <c r="G88" s="11">
-        <f t="shared" si="9"/>
-        <v>3248.3480902777778</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B89" s="7">
-        <f t="shared" si="6"/>
-        <v>3629</v>
-      </c>
-      <c r="C89" s="9">
-        <f t="shared" si="6"/>
-        <v>3326.2083333333335</v>
-      </c>
-      <c r="D89" s="10">
-        <f t="shared" si="7"/>
-        <v>302.79166666666652</v>
-      </c>
-      <c r="E89" s="11">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F89" s="11">
-        <f t="shared" si="8"/>
-        <v>-64.381076388889028</v>
-      </c>
-      <c r="G89" s="11">
-        <f t="shared" si="9"/>
-        <v>3261.8272569444443</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B90" s="7">
-        <f t="shared" si="6"/>
-        <v>3408</v>
-      </c>
-      <c r="C90" s="9">
-        <f t="shared" si="6"/>
-        <v>3316.5416666666665</v>
-      </c>
-      <c r="D90" s="10">
-        <f t="shared" si="7"/>
-        <v>91.458333333333485</v>
-      </c>
-      <c r="E90" s="11">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F90" s="11">
-        <f t="shared" si="8"/>
-        <v>55.952256944444457</v>
-      </c>
-      <c r="G90" s="11">
-        <f t="shared" si="9"/>
-        <v>3372.4939236111109</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" s="7">
-        <f t="shared" si="6"/>
-        <v>3391</v>
-      </c>
-      <c r="C91" s="9">
-        <f t="shared" si="6"/>
-        <v>3318.5833333333335</v>
-      </c>
-      <c r="D91" s="10">
-        <f t="shared" si="7"/>
-        <v>72.416666666666515</v>
-      </c>
-      <c r="E91" s="11">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F91" s="11">
-        <f t="shared" si="8"/>
-        <v>135.17100694444434</v>
-      </c>
-      <c r="G91" s="11">
-        <f t="shared" si="9"/>
-        <v>3453.7543402777778</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B92" s="7">
-        <f t="shared" si="6"/>
-        <v>3010</v>
-      </c>
-      <c r="C92" s="9">
-        <f t="shared" si="6"/>
-        <v>3312.0833333333335</v>
-      </c>
-      <c r="D92" s="11">
-        <f t="shared" si="7"/>
-        <v>-302.08333333333348</v>
-      </c>
-      <c r="E92" s="11" cm="1">
-        <f t="array" ref="E92:E103">TRANSPOSE(B$74:M$74)</f>
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="F92" s="11">
-        <f t="shared" si="8"/>
-        <v>43.139756944444343</v>
-      </c>
-      <c r="G92" s="11">
-        <f t="shared" si="9"/>
-        <v>3355.2230902777778</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A93" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B93" s="7">
-        <f t="shared" si="6"/>
-        <v>2734</v>
-      </c>
-      <c r="C93" s="9">
-        <f t="shared" si="6"/>
-        <v>3308.0416666666665</v>
-      </c>
-      <c r="D93" s="11">
-        <f t="shared" si="7"/>
-        <v>-574.04166666666652</v>
-      </c>
-      <c r="E93" s="11">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F93" s="11">
-        <f t="shared" si="8"/>
-        <v>116.73350694444457</v>
-      </c>
-      <c r="G93" s="11">
-        <f t="shared" si="9"/>
-        <v>3424.7751736111113</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A94" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B94" s="7">
-        <f t="shared" si="6"/>
-        <v>3015</v>
-      </c>
-      <c r="C94" s="9">
-        <f t="shared" si="6"/>
-        <v>3311.7083333333335</v>
-      </c>
-      <c r="D94" s="11">
-        <f t="shared" si="7"/>
-        <v>-296.70833333333348</v>
-      </c>
-      <c r="E94" s="11">
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="F94" s="11">
-        <f t="shared" si="8"/>
-        <v>68.639756944444343</v>
-      </c>
-      <c r="G94" s="11">
-        <f t="shared" si="9"/>
-        <v>3380.3480902777778</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A95" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B95" s="7">
-        <f t="shared" si="6"/>
-        <v>2979</v>
-      </c>
-      <c r="C95" s="9">
-        <f t="shared" si="6"/>
-        <v>3313.1666666666665</v>
-      </c>
-      <c r="D95" s="11">
-        <f t="shared" si="7"/>
-        <v>-334.16666666666652</v>
-      </c>
-      <c r="E95" s="11">
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F95" s="11">
-        <f t="shared" si="8"/>
-        <v>5.4001736111110858</v>
-      </c>
-      <c r="G95" s="11">
-        <f t="shared" si="9"/>
-        <v>3318.5668402777774</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A96" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B96" s="7">
-        <f t="shared" si="6"/>
-        <v>3443</v>
-      </c>
-      <c r="C96" s="9">
-        <f t="shared" si="6"/>
-        <v>3307.75</v>
-      </c>
-      <c r="D96" s="11">
-        <f t="shared" si="7"/>
-        <v>135.25</v>
-      </c>
-      <c r="E96" s="11">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F96" s="11">
-        <f t="shared" si="8"/>
-        <v>33.879340277777715</v>
-      </c>
-      <c r="G96" s="11">
-        <f t="shared" si="9"/>
-        <v>3341.6293402777778</v>
-      </c>
-      <c r="H96" s="1"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A97" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B97" s="7">
-        <f t="shared" ref="B97:C112" si="10">B20</f>
-        <v>3514</v>
-      </c>
-      <c r="C97" s="9">
-        <f t="shared" si="10"/>
-        <v>3292.4166666666665</v>
-      </c>
-      <c r="D97" s="11">
-        <f t="shared" si="7"/>
-        <v>221.58333333333348</v>
-      </c>
-      <c r="E97" s="11">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F97" s="11">
-        <f t="shared" si="8"/>
-        <v>-60.912326388888687</v>
-      </c>
-      <c r="G97" s="11">
-        <f t="shared" si="9"/>
-        <v>3231.5043402777778</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A98" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="7">
-        <f t="shared" si="10"/>
-        <v>3552</v>
-      </c>
-      <c r="C98" s="9">
-        <f t="shared" si="10"/>
-        <v>3281.0833333333335</v>
-      </c>
-      <c r="D98" s="11">
-        <f t="shared" si="7"/>
-        <v>270.91666666666652</v>
-      </c>
-      <c r="E98" s="11">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F98" s="11">
-        <f t="shared" si="8"/>
-        <v>-96.026909722222285</v>
-      </c>
-      <c r="G98" s="11">
-        <f t="shared" si="9"/>
-        <v>3185.0564236111113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B99" s="7">
-        <f t="shared" si="10"/>
-        <v>3490</v>
-      </c>
-      <c r="C99" s="9">
-        <f t="shared" si="10"/>
-        <v>3270.2083333333335</v>
-      </c>
-      <c r="D99" s="11">
-        <f t="shared" si="7"/>
-        <v>219.79166666666652</v>
-      </c>
-      <c r="E99" s="11">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F99" s="11">
-        <f t="shared" si="8"/>
-        <v>-106.73524305555566</v>
-      </c>
-      <c r="G99" s="11">
-        <f t="shared" si="9"/>
-        <v>3163.4730902777778</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A100" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B100" s="7">
-        <f t="shared" si="10"/>
-        <v>3579</v>
-      </c>
-      <c r="C100" s="9">
-        <f t="shared" si="10"/>
-        <v>3259.4583333333335</v>
-      </c>
-      <c r="D100" s="11">
-        <f t="shared" si="7"/>
-        <v>319.54166666666652</v>
-      </c>
-      <c r="E100" s="11">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F100" s="11">
-        <f t="shared" si="8"/>
-        <v>-4.1102430555556566</v>
-      </c>
-      <c r="G100" s="11">
-        <f t="shared" si="9"/>
-        <v>3255.3480902777778</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B101" s="7">
-        <f t="shared" si="10"/>
-        <v>3657</v>
-      </c>
-      <c r="C101" s="9">
-        <f t="shared" si="10"/>
-        <v>3261.1666666666665</v>
-      </c>
-      <c r="D101" s="11">
-        <f t="shared" si="7"/>
-        <v>395.83333333333348</v>
-      </c>
-      <c r="E101" s="11">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F101" s="11">
-        <f t="shared" si="8"/>
-        <v>28.660590277777942</v>
-      </c>
-      <c r="G101" s="11">
-        <f t="shared" si="9"/>
-        <v>3289.8272569444443</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B102" s="7">
-        <f t="shared" si="10"/>
-        <v>3250</v>
-      </c>
-      <c r="C102" s="9">
-        <f t="shared" si="10"/>
-        <v>3264.25</v>
-      </c>
-      <c r="D102" s="11">
-        <f t="shared" si="7"/>
-        <v>-14.25</v>
-      </c>
-      <c r="E102" s="11">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F102" s="11">
-        <f t="shared" si="8"/>
-        <v>-49.756076388889028</v>
-      </c>
-      <c r="G102" s="11">
-        <f t="shared" si="9"/>
-        <v>3214.4939236111109</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A103" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B103" s="7">
-        <f t="shared" si="10"/>
-        <v>3181</v>
-      </c>
-      <c r="C103" s="9">
-        <f t="shared" si="10"/>
-        <v>3260.4583333333335</v>
-      </c>
-      <c r="D103" s="11">
-        <f t="shared" si="7"/>
-        <v>-79.458333333333485</v>
-      </c>
-      <c r="E103" s="11">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F103" s="11">
-        <f t="shared" si="8"/>
-        <v>-16.703993055555657</v>
-      </c>
-      <c r="G103" s="11">
-        <f t="shared" si="9"/>
-        <v>3243.7543402777778</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A104" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B104" s="7">
-        <f t="shared" si="10"/>
-        <v>2948</v>
-      </c>
-      <c r="C104" s="9">
-        <f t="shared" si="10"/>
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D104" s="11">
-        <f t="shared" si="7"/>
-        <v>-308.70833333333348</v>
-      </c>
-      <c r="E104" s="11" cm="1">
-        <f t="array" ref="E104:E115">TRANSPOSE(B$74:M$74)</f>
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="F104" s="11">
-        <f t="shared" si="8"/>
-        <v>36.514756944444343</v>
-      </c>
-      <c r="G104" s="11">
-        <f t="shared" si="9"/>
-        <v>3293.2230902777778</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A105" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B105" s="7">
-        <f t="shared" si="10"/>
-        <v>2535</v>
-      </c>
-      <c r="C105" s="9">
-        <f t="shared" si="10"/>
-        <v>3262.125</v>
-      </c>
-      <c r="D105" s="11">
-        <f t="shared" si="7"/>
-        <v>-727.125</v>
-      </c>
-      <c r="E105" s="11">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F105" s="11">
-        <f t="shared" si="8"/>
-        <v>-36.349826388888914</v>
-      </c>
-      <c r="G105" s="11">
-        <f t="shared" si="9"/>
-        <v>3225.7751736111113</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A106" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B106" s="7">
-        <f t="shared" si="10"/>
-        <v>2956</v>
-      </c>
-      <c r="C106" s="9">
-        <f t="shared" si="10"/>
-        <v>3267.0833333333335</v>
-      </c>
-      <c r="D106" s="11">
-        <f t="shared" si="7"/>
-        <v>-311.08333333333348</v>
-      </c>
-      <c r="E106" s="11">
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="F106" s="11">
-        <f t="shared" si="8"/>
-        <v>54.264756944444343</v>
-      </c>
-      <c r="G106" s="11">
-        <f t="shared" si="9"/>
-        <v>3321.3480902777778</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A107" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B107" s="7">
-        <f t="shared" si="10"/>
-        <v>3079</v>
-      </c>
-      <c r="C107" s="9">
-        <f t="shared" si="10"/>
-        <v>3259.2916666666665</v>
-      </c>
-      <c r="D107" s="11">
-        <f t="shared" si="7"/>
-        <v>-180.29166666666652</v>
-      </c>
-      <c r="E107" s="11">
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F107" s="11">
-        <f t="shared" si="8"/>
-        <v>159.27517361111109</v>
-      </c>
-      <c r="G107" s="11">
-        <f t="shared" si="9"/>
-        <v>3418.5668402777774</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A108" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B108" s="7">
-        <f t="shared" si="10"/>
-        <v>3417</v>
-      </c>
-      <c r="C108" s="9">
-        <f t="shared" si="10"/>
-        <v>3254</v>
-      </c>
-      <c r="D108" s="11">
-        <f t="shared" si="7"/>
-        <v>163</v>
-      </c>
-      <c r="E108" s="11">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F108" s="11">
-        <f t="shared" si="8"/>
-        <v>61.629340277777715</v>
-      </c>
-      <c r="G108" s="11">
-        <f t="shared" si="9"/>
-        <v>3315.6293402777778</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A109" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B109" s="7">
-        <f t="shared" si="10"/>
-        <v>3449</v>
-      </c>
-      <c r="C109" s="9">
-        <f t="shared" si="10"/>
-        <v>3256.9583333333335</v>
-      </c>
-      <c r="D109" s="11">
-        <f t="shared" si="7"/>
-        <v>192.04166666666652</v>
-      </c>
-      <c r="E109" s="11">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F109" s="11">
-        <f t="shared" si="8"/>
-        <v>-90.453993055555657</v>
-      </c>
-      <c r="G109" s="11">
-        <f t="shared" si="9"/>
-        <v>3166.5043402777778</v>
+        <v>3160.0564236111113</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
@@ -5740,31 +5886,31 @@
       <c r="M109" s="1"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B110" s="7">
-        <f t="shared" si="10"/>
-        <v>3527</v>
-      </c>
-      <c r="C110" s="9">
-        <f t="shared" si="10"/>
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D110" s="11">
+      <c r="B110" s="5">
+        <f t="shared" si="8"/>
+        <v>3645</v>
+      </c>
+      <c r="C110" s="4">
+        <f t="shared" si="8"/>
+        <v>3269</v>
+      </c>
+      <c r="D110" s="2">
+        <f t="shared" si="5"/>
+        <v>376</v>
+      </c>
+      <c r="E110" s="2">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F110" s="2">
+        <f t="shared" si="6"/>
+        <v>49.473090277777828</v>
+      </c>
+      <c r="G110" s="2">
         <f t="shared" si="7"/>
-        <v>270.29166666666652</v>
-      </c>
-      <c r="E110" s="11">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F110" s="11">
-        <f t="shared" si="8"/>
-        <v>-96.651909722222285</v>
-      </c>
-      <c r="G110" s="11">
-        <f t="shared" si="9"/>
-        <v>3160.0564236111113</v>
+        <v>3318.4730902777778</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
@@ -5774,31 +5920,31 @@
       <c r="M110" s="1"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B111" s="7">
-        <f t="shared" si="10"/>
-        <v>3645</v>
-      </c>
-      <c r="C111" s="9">
-        <f t="shared" si="10"/>
-        <v>3269</v>
-      </c>
-      <c r="D111" s="11">
+      <c r="B111" s="5">
+        <f t="shared" si="8"/>
+        <v>3543</v>
+      </c>
+      <c r="C111" s="4">
+        <f t="shared" si="8"/>
+        <v>3279.0833333333335</v>
+      </c>
+      <c r="D111" s="2">
+        <f t="shared" ref="D111:D138" si="9">IF(LEN(D35)&gt;0,D35,"")</f>
+        <v>263.91666666666652</v>
+      </c>
+      <c r="E111" s="2">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F111" s="2">
+        <f t="shared" ref="F111:F138" si="10">IFERROR(B35-C35-E111, "NA")</f>
+        <v>-59.735243055555657</v>
+      </c>
+      <c r="G111" s="2">
         <f t="shared" si="7"/>
-        <v>376</v>
-      </c>
-      <c r="E111" s="11">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F111" s="11">
-        <f t="shared" si="8"/>
-        <v>49.473090277777828</v>
-      </c>
-      <c r="G111" s="11">
-        <f t="shared" si="9"/>
-        <v>3318.4730902777778</v>
+        <v>3219.3480902777778</v>
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
@@ -5808,93 +5954,93 @@
       <c r="M111" s="1"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B112" s="7">
-        <f t="shared" si="10"/>
-        <v>3543</v>
-      </c>
-      <c r="C112" s="9">
-        <f t="shared" si="10"/>
-        <v>3279.0833333333335</v>
-      </c>
-      <c r="D112" s="11">
-        <f t="shared" si="7"/>
-        <v>263.91666666666652</v>
-      </c>
-      <c r="E112" s="11">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F112" s="11">
-        <f t="shared" si="8"/>
-        <v>-59.735243055555657</v>
-      </c>
-      <c r="G112" s="11">
-        <f t="shared" si="9"/>
-        <v>3219.3480902777778</v>
-      </c>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1"/>
-      <c r="K112" s="1"/>
-      <c r="L112" s="1"/>
-      <c r="M112" s="1"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A113" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B113" s="7">
-        <f t="shared" ref="B113:C128" si="11">B36</f>
+      <c r="B112" s="5">
+        <f t="shared" ref="B112:C127" si="11">B36</f>
         <v>3506</v>
       </c>
-      <c r="C113" s="9">
+      <c r="C112" s="4">
         <f t="shared" si="11"/>
         <v>3252.8333333333335</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D112" s="2">
+        <f t="shared" si="9"/>
+        <v>253.16666666666652</v>
+      </c>
+      <c r="E112" s="2">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F112" s="2">
+        <f t="shared" si="10"/>
+        <v>-114.00607638888903</v>
+      </c>
+      <c r="G112" s="2">
         <f t="shared" si="7"/>
-        <v>253.16666666666652</v>
-      </c>
-      <c r="E113" s="11">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F113" s="11">
-        <f t="shared" si="8"/>
-        <v>-114.00607638888903</v>
-      </c>
-      <c r="G113" s="11">
-        <f t="shared" si="9"/>
         <v>3138.8272569444443</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A114" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B114" s="7">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A113" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B113" s="5">
         <f t="shared" si="11"/>
         <v>3274</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C113" s="4">
         <f t="shared" si="11"/>
         <v>3228.0416666666665</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D113" s="2">
+        <f t="shared" si="9"/>
+        <v>45.958333333333485</v>
+      </c>
+      <c r="E113" s="2">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F113" s="2">
+        <f t="shared" si="10"/>
+        <v>10.452256944444457</v>
+      </c>
+      <c r="G113" s="2">
         <f t="shared" si="7"/>
-        <v>45.958333333333485</v>
-      </c>
-      <c r="E114" s="11">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F114" s="11">
-        <f t="shared" si="8"/>
-        <v>10.452256944444457</v>
-      </c>
-      <c r="G114" s="11">
+        <v>3238.4939236111109</v>
+      </c>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A114" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114" s="5">
+        <f t="shared" si="11"/>
+        <v>3228</v>
+      </c>
+      <c r="C114" s="4">
+        <f t="shared" si="11"/>
+        <v>3248.2083333333335</v>
+      </c>
+      <c r="D114" s="2">
         <f t="shared" si="9"/>
-        <v>3238.4939236111109</v>
+        <v>-20.208333333333485</v>
+      </c>
+      <c r="E114" s="2">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F114" s="2">
+        <f t="shared" si="10"/>
+        <v>42.546006944444343</v>
+      </c>
+      <c r="G114" s="2">
+        <f t="shared" si="7"/>
+        <v>3290.7543402777778</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
@@ -5902,722 +6048,687 @@
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
+      <c r="N114" s="1"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B115" s="7">
-        <f t="shared" si="11"/>
-        <v>3228</v>
-      </c>
-      <c r="C115" s="9">
-        <f t="shared" si="11"/>
-        <v>3248.2083333333335</v>
-      </c>
-      <c r="D115" s="11">
-        <f t="shared" si="7"/>
-        <v>-20.208333333333485</v>
-      </c>
-      <c r="E115" s="11">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F115" s="11">
-        <f t="shared" si="8"/>
-        <v>42.546006944444343</v>
-      </c>
-      <c r="G115" s="11">
-        <f t="shared" si="9"/>
-        <v>3290.7543402777778</v>
-      </c>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-      <c r="K115" s="1"/>
-      <c r="L115" s="1"/>
-      <c r="M115" s="1"/>
-      <c r="N115" s="1"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A116" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B116" s="7">
+      <c r="B115" s="5">
         <f t="shared" si="11"/>
         <v>2895</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C115" s="4">
         <f t="shared" si="11"/>
         <v>3294.2916666666665</v>
       </c>
-      <c r="D116" s="11">
+      <c r="D115" s="4">
+        <f t="shared" si="9"/>
+        <v>-399.29166666666652</v>
+      </c>
+      <c r="E115" s="2" cm="1">
+        <f t="array" ref="E115:E126">TRANSPOSE(B$74:M$74)</f>
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="F115" s="2">
+        <f t="shared" si="10"/>
+        <v>-54.068576388888687</v>
+      </c>
+      <c r="G115" s="2">
         <f t="shared" si="7"/>
-        <v>-399.29166666666652</v>
-      </c>
-      <c r="E116" s="11" cm="1">
-        <f t="array" ref="E116:E127">TRANSPOSE(B$74:M$74)</f>
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="F116" s="11">
-        <f t="shared" si="8"/>
-        <v>-54.068576388888687</v>
-      </c>
-      <c r="G116" s="11">
-        <f t="shared" si="9"/>
         <v>3240.2230902777778</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A117" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B117" s="7">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A116" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" s="5">
         <f t="shared" si="11"/>
         <v>2883</v>
       </c>
-      <c r="C117" s="9">
+      <c r="C116" s="4">
         <f t="shared" si="11"/>
         <v>3340.3333333333335</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D116" s="2">
+        <f t="shared" si="9"/>
+        <v>-457.33333333333348</v>
+      </c>
+      <c r="E116" s="2">
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="F116" s="2">
+        <f t="shared" si="10"/>
+        <v>233.4418402777776</v>
+      </c>
+      <c r="G116" s="2">
         <f t="shared" si="7"/>
-        <v>-457.33333333333348</v>
-      </c>
-      <c r="E117" s="11">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F117" s="11">
-        <f t="shared" si="8"/>
-        <v>233.4418402777776</v>
-      </c>
-      <c r="G117" s="11">
-        <f t="shared" si="9"/>
         <v>3573.7751736111113</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A118" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B118" s="7">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A117" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B117" s="5">
         <f t="shared" si="11"/>
         <v>2850</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C117" s="4">
         <f t="shared" si="11"/>
         <v>3384.6666666666665</v>
       </c>
-      <c r="D118" s="11">
+      <c r="D117" s="2">
+        <f t="shared" si="9"/>
+        <v>-534.66666666666652</v>
+      </c>
+      <c r="E117" s="2">
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="F117" s="2">
+        <f t="shared" si="10"/>
+        <v>-169.31857638888869</v>
+      </c>
+      <c r="G117" s="2">
         <f t="shared" si="7"/>
-        <v>-534.66666666666652</v>
-      </c>
-      <c r="E118" s="11">
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="F118" s="11">
-        <f t="shared" si="8"/>
-        <v>-169.31857638888869</v>
-      </c>
-      <c r="G118" s="11">
-        <f t="shared" si="9"/>
         <v>3215.3480902777778</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A119" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B119" s="7">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A118" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B118" s="5">
         <f t="shared" si="11"/>
         <v>2555</v>
       </c>
-      <c r="C119" s="9">
+      <c r="C118" s="4">
         <f t="shared" si="11"/>
         <v>3433.5416666666665</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D118" s="2">
+        <f t="shared" si="9"/>
+        <v>-878.54166666666652</v>
+      </c>
+      <c r="E118" s="2">
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F118" s="2">
+        <f t="shared" si="10"/>
+        <v>-538.97482638888891</v>
+      </c>
+      <c r="G118" s="2">
         <f t="shared" si="7"/>
-        <v>-878.54166666666652</v>
-      </c>
-      <c r="E119" s="11">
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F119" s="11">
-        <f t="shared" si="8"/>
-        <v>-538.97482638888891</v>
-      </c>
-      <c r="G119" s="11">
-        <f t="shared" si="9"/>
         <v>2894.5668402777774</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A120" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B120" s="7">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A119" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" s="5">
         <f t="shared" si="11"/>
         <v>3346</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C119" s="4">
         <f t="shared" si="11"/>
         <v>3481.2916666666665</v>
       </c>
-      <c r="D120" s="11">
+      <c r="D119" s="2">
+        <f t="shared" si="9"/>
+        <v>-135.29166666666652</v>
+      </c>
+      <c r="E119" s="2">
+        <v>101.37065972222229</v>
+      </c>
+      <c r="F119" s="2">
+        <f t="shared" si="10"/>
+        <v>-236.6623263888888</v>
+      </c>
+      <c r="G119" s="2">
         <f t="shared" si="7"/>
-        <v>-135.29166666666652</v>
-      </c>
-      <c r="E120" s="11">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F120" s="11">
-        <f t="shared" si="8"/>
-        <v>-236.6623263888888</v>
-      </c>
-      <c r="G120" s="11">
-        <f t="shared" si="9"/>
         <v>3244.6293402777778</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A121" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B121" s="7">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A120" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120" s="5">
         <f t="shared" si="11"/>
         <v>4004</v>
       </c>
-      <c r="C121" s="9">
+      <c r="C120" s="4">
         <f t="shared" si="11"/>
         <v>3514.8333333333335</v>
       </c>
-      <c r="D121" s="11">
+      <c r="D120" s="2">
+        <f t="shared" si="9"/>
+        <v>489.16666666666652</v>
+      </c>
+      <c r="E120" s="2">
+        <v>282.49565972222217</v>
+      </c>
+      <c r="F120" s="2">
+        <f t="shared" si="10"/>
+        <v>206.67100694444434</v>
+      </c>
+      <c r="G120" s="2">
         <f t="shared" si="7"/>
-        <v>489.16666666666652</v>
-      </c>
-      <c r="E121" s="11">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F121" s="11">
-        <f t="shared" si="8"/>
-        <v>206.67100694444434</v>
-      </c>
-      <c r="G121" s="11">
-        <f t="shared" si="9"/>
         <v>3721.5043402777778</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A122" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B122" s="7">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A121" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B121" s="5">
         <f t="shared" si="11"/>
         <v>4078</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C121" s="4">
         <f t="shared" si="11"/>
         <v>3549.875</v>
       </c>
-      <c r="D122" s="11">
+      <c r="D121" s="2">
+        <f t="shared" si="9"/>
+        <v>528.125</v>
+      </c>
+      <c r="E121" s="2">
+        <v>366.9435763888888</v>
+      </c>
+      <c r="F121" s="2">
+        <f t="shared" si="10"/>
+        <v>161.1814236111112</v>
+      </c>
+      <c r="G121" s="2">
         <f t="shared" si="7"/>
-        <v>528.125</v>
-      </c>
-      <c r="E122" s="11">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F122" s="11">
-        <f t="shared" si="8"/>
-        <v>161.1814236111112</v>
-      </c>
-      <c r="G122" s="11">
-        <f t="shared" si="9"/>
         <v>3711.0564236111113</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A123" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B123" s="7">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A122" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B122" s="5">
         <f t="shared" si="11"/>
         <v>4199</v>
       </c>
-      <c r="C123" s="9">
+      <c r="C122" s="4">
         <f t="shared" si="11"/>
         <v>3567.7083333333335</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D122" s="2">
+        <f t="shared" si="9"/>
+        <v>631.29166666666652</v>
+      </c>
+      <c r="E122" s="2">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F122" s="2">
+        <f t="shared" si="10"/>
+        <v>304.76475694444434</v>
+      </c>
+      <c r="G122" s="2">
         <f t="shared" si="7"/>
-        <v>631.29166666666652</v>
-      </c>
-      <c r="E123" s="11">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F123" s="11">
-        <f t="shared" si="8"/>
-        <v>304.76475694444434</v>
-      </c>
-      <c r="G123" s="11">
-        <f t="shared" si="9"/>
         <v>3872.4730902777778</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A124" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B124" s="7">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A123" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B123" s="5">
         <f t="shared" si="11"/>
         <v>4053</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C123" s="4">
         <f t="shared" si="11"/>
         <v>3590.6666666666665</v>
       </c>
-      <c r="D124" s="11">
+      <c r="D123" s="2">
+        <f t="shared" si="9"/>
+        <v>462.33333333333348</v>
+      </c>
+      <c r="E123" s="2">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F123" s="2">
+        <f t="shared" si="10"/>
+        <v>138.68142361111131</v>
+      </c>
+      <c r="G123" s="2">
         <f t="shared" si="7"/>
-        <v>462.33333333333348</v>
-      </c>
-      <c r="E124" s="11">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F124" s="11">
-        <f t="shared" si="8"/>
-        <v>138.68142361111131</v>
-      </c>
-      <c r="G124" s="11">
-        <f t="shared" si="9"/>
         <v>3729.3480902777778</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A125" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B125" s="7">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A124" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" s="5">
         <f t="shared" si="11"/>
         <v>4169</v>
       </c>
-      <c r="C125" s="9">
+      <c r="C124" s="4">
         <f t="shared" si="11"/>
         <v>3672.125</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D124" s="2">
+        <f t="shared" si="9"/>
+        <v>496.875</v>
+      </c>
+      <c r="E124" s="2">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F124" s="2">
+        <f t="shared" si="10"/>
+        <v>129.70225694444446</v>
+      </c>
+      <c r="G124" s="2">
         <f t="shared" si="7"/>
-        <v>496.875</v>
-      </c>
-      <c r="E125" s="11">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F125" s="11">
-        <f t="shared" si="8"/>
-        <v>129.70225694444446</v>
-      </c>
-      <c r="G125" s="11">
-        <f t="shared" si="9"/>
         <v>3801.8272569444443</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A126" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B126" s="7">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A125" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B125" s="5">
         <f t="shared" si="11"/>
         <v>3757</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C125" s="4">
         <f t="shared" si="11"/>
         <v>3758.1666666666665</v>
       </c>
-      <c r="D126" s="11">
+      <c r="D125" s="2">
+        <f t="shared" si="9"/>
+        <v>-1.1666666666665151</v>
+      </c>
+      <c r="E125" s="2">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F125" s="2">
+        <f t="shared" si="10"/>
+        <v>-36.672743055555543</v>
+      </c>
+      <c r="G125" s="2">
         <f t="shared" si="7"/>
-        <v>-1.1666666666665151</v>
-      </c>
-      <c r="E126" s="11">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F126" s="11">
-        <f t="shared" si="8"/>
-        <v>-36.672743055555543</v>
-      </c>
-      <c r="G126" s="11">
-        <f t="shared" si="9"/>
         <v>3721.4939236111109</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A127" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B127" s="7">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A126" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126" s="5">
         <f t="shared" si="11"/>
         <v>3550</v>
       </c>
-      <c r="C127" s="9">
+      <c r="C126" s="4">
         <f t="shared" si="11"/>
         <v>3793.7916666666665</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D126" s="2">
+        <f t="shared" si="9"/>
+        <v>-243.79166666666652</v>
+      </c>
+      <c r="E126" s="2">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F126" s="2">
+        <f t="shared" si="10"/>
+        <v>-181.03732638888869</v>
+      </c>
+      <c r="G126" s="2">
         <f t="shared" si="7"/>
-        <v>-243.79166666666652</v>
-      </c>
-      <c r="E127" s="11">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F127" s="11">
-        <f t="shared" si="8"/>
-        <v>-181.03732638888869</v>
-      </c>
-      <c r="G127" s="11">
-        <f t="shared" si="9"/>
         <v>3612.7543402777778</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A128" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B128" s="7">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A127" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B127" s="5">
         <f t="shared" si="11"/>
         <v>3414</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C127" s="4">
         <f t="shared" si="11"/>
         <v>3804.8333333333335</v>
       </c>
-      <c r="D128" s="11">
+      <c r="D127" s="4">
+        <f t="shared" si="9"/>
+        <v>-390.83333333333348</v>
+      </c>
+      <c r="E127" s="2" cm="1">
+        <f t="array" ref="E127:E138">TRANSPOSE(B$74:M$74)</f>
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="F127" s="2">
+        <f t="shared" si="10"/>
+        <v>-45.610243055555657</v>
+      </c>
+      <c r="G127" s="2">
         <f t="shared" si="7"/>
-        <v>-390.83333333333348</v>
-      </c>
-      <c r="E128" s="11" cm="1">
-        <f t="array" ref="E128:E139">TRANSPOSE(B$74:M$74)</f>
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="F128" s="11">
-        <f t="shared" si="8"/>
-        <v>-45.610243055555657</v>
-      </c>
-      <c r="G128" s="11">
-        <f t="shared" si="9"/>
         <v>3759.2230902777778</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B129" s="7">
-        <f t="shared" ref="B129:C139" si="12">B52</f>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A128" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B128" s="5">
+        <f t="shared" ref="B128:C138" si="12">B52</f>
         <v>2792</v>
       </c>
-      <c r="C129" s="9">
+      <c r="C128" s="4">
         <f t="shared" si="12"/>
         <v>3816.625</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D128" s="2">
+        <f t="shared" si="9"/>
+        <v>-1024.625</v>
+      </c>
+      <c r="E128" s="2">
+        <v>-690.77517361111109</v>
+      </c>
+      <c r="F128" s="2">
+        <f t="shared" si="10"/>
+        <v>-333.84982638888891</v>
+      </c>
+      <c r="G128" s="2">
         <f t="shared" si="7"/>
-        <v>-1024.625</v>
-      </c>
-      <c r="E129" s="11">
-        <v>-690.77517361111109</v>
-      </c>
-      <c r="F129" s="11">
-        <f t="shared" si="8"/>
-        <v>-333.84982638888891</v>
-      </c>
-      <c r="G129" s="11">
-        <f t="shared" si="9"/>
         <v>3482.7751736111113</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A130" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B130" s="7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B129" s="5">
         <f t="shared" si="12"/>
         <v>3492</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C129" s="4">
         <f t="shared" si="12"/>
         <v>3830.9583333333335</v>
       </c>
-      <c r="D130" s="11">
+      <c r="D129" s="2">
+        <f t="shared" si="9"/>
+        <v>-338.95833333333348</v>
+      </c>
+      <c r="E129" s="2">
+        <v>-365.34809027777783</v>
+      </c>
+      <c r="F129" s="2">
+        <f t="shared" si="10"/>
+        <v>26.389756944444343</v>
+      </c>
+      <c r="G129" s="2">
         <f t="shared" si="7"/>
-        <v>-338.95833333333348</v>
-      </c>
-      <c r="E130" s="11">
-        <v>-365.34809027777783</v>
-      </c>
-      <c r="F130" s="11">
-        <f t="shared" si="8"/>
-        <v>26.389756944444343</v>
-      </c>
-      <c r="G130" s="11">
-        <f t="shared" si="9"/>
         <v>3857.3480902777778</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A131" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B131" s="7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A130" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B130" s="5">
         <f t="shared" si="12"/>
         <v>3868</v>
       </c>
-      <c r="C131" s="9">
+      <c r="C130" s="4">
         <f t="shared" si="12"/>
         <v>3853.2916666666665</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D130" s="2">
+        <f t="shared" si="9"/>
+        <v>14.708333333333485</v>
+      </c>
+      <c r="E130" s="2">
+        <v>-339.5668402777776</v>
+      </c>
+      <c r="F130" s="2">
+        <f t="shared" si="10"/>
+        <v>354.27517361111109</v>
+      </c>
+      <c r="G130" s="2">
         <f t="shared" si="7"/>
-        <v>14.708333333333485</v>
-      </c>
-      <c r="E131" s="11">
-        <v>-339.5668402777776</v>
-      </c>
-      <c r="F131" s="11">
-        <f t="shared" si="8"/>
-        <v>354.27517361111109</v>
-      </c>
-      <c r="G131" s="11">
-        <f t="shared" si="9"/>
         <v>4207.5668402777774</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B132" s="7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A131" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B131" s="5">
         <f t="shared" si="12"/>
         <v>4098</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C131" s="4">
         <f t="shared" si="12"/>
         <v>3875.5</v>
       </c>
-      <c r="D132" s="11">
+      <c r="D131" s="2">
+        <f t="shared" si="9"/>
+        <v>222.5</v>
+      </c>
+      <c r="E131" s="2">
+        <v>101.37065972222229</v>
+      </c>
+      <c r="F131" s="2">
+        <f t="shared" si="10"/>
+        <v>121.12934027777771</v>
+      </c>
+      <c r="G131" s="2">
         <f t="shared" si="7"/>
-        <v>222.5</v>
-      </c>
-      <c r="E132" s="11">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F132" s="11">
-        <f t="shared" si="8"/>
-        <v>121.12934027777771</v>
-      </c>
-      <c r="G132" s="11">
-        <f t="shared" si="9"/>
         <v>3996.6293402777778</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B133" s="7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B132" s="5">
         <f t="shared" si="12"/>
         <v>4107</v>
       </c>
-      <c r="C133" s="9">
+      <c r="C132" s="4">
         <f t="shared" si="12"/>
         <v>3899.8333333333335</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D132" s="4">
+        <f t="shared" si="9"/>
+        <v>207.16666666666652</v>
+      </c>
+      <c r="E132" s="2">
+        <v>282.49565972222217</v>
+      </c>
+      <c r="F132" s="2">
+        <f t="shared" si="10"/>
+        <v>-75.328993055555657</v>
+      </c>
+      <c r="G132" s="2">
         <f t="shared" si="7"/>
-        <v>207.16666666666652</v>
-      </c>
-      <c r="E133" s="11">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F133" s="11">
-        <f t="shared" si="8"/>
-        <v>-75.328993055555657</v>
-      </c>
-      <c r="G133" s="11">
-        <f t="shared" si="9"/>
         <v>3824.5043402777778</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A134" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B134" s="7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A133" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B133" s="5">
         <f t="shared" si="12"/>
         <v>4240</v>
       </c>
-      <c r="C134" s="7" t="str">
+      <c r="C133" s="5" t="str">
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="D134" s="11" t="str">
+      <c r="D133" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>NA</v>
+      </c>
+      <c r="E133" s="2">
+        <v>366.9435763888888</v>
+      </c>
+      <c r="F133" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>NA</v>
+      </c>
+      <c r="G133" s="2">
         <f t="shared" si="7"/>
-        <v>NA</v>
-      </c>
-      <c r="E134" s="11">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F134" s="11" t="str">
-        <f t="shared" si="8"/>
-        <v>NA</v>
-      </c>
-      <c r="G134" s="11">
-        <f t="shared" si="9"/>
         <v>3873.0564236111113</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B135" s="7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A134" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B134" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="C135" s="7" t="str">
+      <c r="C134" s="5" t="str">
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="D135" s="11" t="str">
+      <c r="D134" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>NA</v>
+      </c>
+      <c r="E134" s="2">
+        <v>326.52690972222217</v>
+      </c>
+      <c r="F134" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>NA</v>
+      </c>
+      <c r="G134" s="2">
         <f t="shared" si="7"/>
-        <v>NA</v>
-      </c>
-      <c r="E135" s="11">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F135" s="11" t="str">
-        <f t="shared" si="8"/>
-        <v>NA</v>
-      </c>
-      <c r="G135" s="11">
-        <f t="shared" si="9"/>
         <v>3993.4730902777778</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A136" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B136" s="7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B135" s="5">
         <f t="shared" si="12"/>
         <v>4276</v>
       </c>
-      <c r="C136" s="7" t="str">
+      <c r="C135" s="5" t="str">
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="D136" s="11" t="str">
+      <c r="D135" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>NA</v>
+      </c>
+      <c r="E135" s="2">
+        <v>323.65190972222217</v>
+      </c>
+      <c r="F135" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>NA</v>
+      </c>
+      <c r="G135" s="2">
         <f t="shared" si="7"/>
-        <v>NA</v>
-      </c>
-      <c r="E136" s="11">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F136" s="11" t="str">
-        <f t="shared" si="8"/>
-        <v>NA</v>
-      </c>
-      <c r="G136" s="11">
-        <f t="shared" si="9"/>
         <v>3952.3480902777778</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B137" s="7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B136" s="5">
         <f t="shared" si="12"/>
         <v>4482</v>
       </c>
-      <c r="C137" s="7" t="str">
+      <c r="C136" s="5" t="str">
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="D137" s="11" t="str">
+      <c r="D136" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>NA</v>
+      </c>
+      <c r="E136" s="2">
+        <v>367.17274305555554</v>
+      </c>
+      <c r="F136" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>NA</v>
+      </c>
+      <c r="G136" s="2">
         <f t="shared" si="7"/>
-        <v>NA</v>
-      </c>
-      <c r="E137" s="11">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F137" s="11" t="str">
-        <f t="shared" si="8"/>
-        <v>NA</v>
-      </c>
-      <c r="G137" s="11">
-        <f t="shared" si="9"/>
         <v>4114.8272569444443</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A138" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B138" s="7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B137" s="5">
         <f t="shared" si="12"/>
         <v>3977</v>
       </c>
-      <c r="C138" s="7" t="str">
+      <c r="C137" s="5" t="str">
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="D138" s="11" t="str">
+      <c r="D137" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>NA</v>
+      </c>
+      <c r="E137" s="2">
+        <v>35.506076388889028</v>
+      </c>
+      <c r="F137" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>NA</v>
+      </c>
+      <c r="G137" s="2">
         <f t="shared" si="7"/>
-        <v>NA</v>
-      </c>
-      <c r="E138" s="11">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F138" s="11" t="str">
-        <f t="shared" si="8"/>
-        <v>NA</v>
-      </c>
-      <c r="G138" s="11">
-        <f t="shared" si="9"/>
         <v>3941.4939236111109</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A139" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B139" s="13">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A138" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B138" s="5">
         <f t="shared" si="12"/>
         <v>3914</v>
       </c>
-      <c r="C139" s="13" t="str">
+      <c r="C138" s="5" t="str">
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="D139" s="11" t="str">
+      <c r="D138" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>NA</v>
+      </c>
+      <c r="E138" s="2">
+        <v>-62.754340277777828</v>
+      </c>
+      <c r="F138" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>NA</v>
+      </c>
+      <c r="G138" s="2">
         <f t="shared" si="7"/>
-        <v>NA</v>
-      </c>
-      <c r="E139" s="11">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F139" s="11" t="str">
-        <f t="shared" si="8"/>
-        <v>NA</v>
-      </c>
-      <c r="G139" s="11">
-        <f t="shared" si="9"/>
         <v>3976.7543402777778</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A66:M66"/>
-    <mergeCell ref="N71:N72"/>
-    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A65:M65"/>
+    <mergeCell ref="A77:G77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6627,6 +6738,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -6821,24 +6949,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6855,29 +6991,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>